--- a/La Trobe University (La Trobe)/latrobe.xlsx
+++ b/La Trobe University (La Trobe)/latrobe.xlsx
@@ -413,1686 +413,8428 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B140"/>
+  <dimension ref="A1:M140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>cricos</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>url</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>course_duration_per_week</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>offshore_tuition_fee</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>onshore_tuition_fee</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>enrolment_fee</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>materials_fee</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>intake</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>course_description</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>entry_requirements</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>002080A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>Bachelor of Arts</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-arts</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>156</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>107400</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>35800</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;With our flexible Bachelor of Arts, you can choose from an incredible array of majors and minors. You'll have access to around 50 majors and minors from humanities, social sciences, business, health and science, keeping your career options open. Pursue your passion and your profession.&lt;/p&gt;&lt;p&gt;Shape your own future with this interdisciplinary degree. You'll choose one arts major, then explore your interests or build an essential skill when you choose secondary majors, minors and electives from across the university. You'll graduate with your primary major on your academic transcript, so future employers can recognise your expertise.&lt;/p&gt;&lt;p&gt;Create your own path. Want to major in sociology, with a second major in psychology, then take Chinese as an elective? Go for it. Or perhaps you'd like to pair economics and English. Or crime, justice and legal studies with linguistics. Build your own future – we're here to help you achieve your dream. No matter which path you choose, you'll learn from world-class academics and leading researchers.&lt;/p&gt;&lt;p&gt;In your first year, you'll explore your interests and passions. Try a language; or get a taste for history, English, politics or creative writing. In your second and third years, you'll delve deeper while also choosing electives and minors that broaden your skills and knowledge. You may also choose to develop professional skillsets in areas like psychology, public health, marketing, science, sport management and more.&lt;/p&gt;&lt;p&gt;This flexible degree also offers a range of study options. You can choose to study face-to-face at our Melbourne Campus and enjoy our on-campus facilities, or you can study online – knowing your experience will mirror on-campus students, with tutorials delivered in a synchronous manner. Unlike many other online degrees, at La Trobe you can login to live sessions and engage directly with academics and your fellow students in real time.&lt;/p&gt;&lt;p&gt;Gain real-world experience and build valuable connections that will shape your career. Take on an industry placement at organisations like SBS Radio, the Asylum Seeker Resource Centre or the United Nations Association of Australia or travel overseas for an international sustainability experience.* Many of our exchange programs are financially supported. Your dedicated course advisor will help you to find your path and explore new opportunities.&lt;/p&gt;&lt;p&gt;The world is waiting for you. Step into it.&lt;/p&gt;&lt;p&gt;You'll learn:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Critical thinking&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Delve into complex problems. Experts say critical thinking will be a highly valued skill in the workforce of tomorrow.**&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Emotional intelligence&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand what drives our decisions. Learn how to connect to others with emotion and intelligence.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Creativity&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to see new possibilities and turn them into reality.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Communication&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to connect, communicate and collaborate with your university peers and future colleagues.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;*Please note: overseas programs may be impacted by travel restrictions.&lt;/p&gt;&lt;p&gt;**Forbes, 2019, &lt;a href="https://www.forbes.com/sites/bernardmarr/2019/04/29/the-10-vital-skills-you-will-need-for-the-future-of-work/#20a8c5df3f5b"&gt;&lt;em&gt;The 10 Vital Skills You Will Need For The Future Of Work&lt;/em&gt; &lt;/a&gt;; PwC, 2020, &lt;a href="https://www.pwc.com.au/careers/blog/future-employment.html"&gt;&lt;em&gt;10 skills you need for future employment&lt;/em&gt;&lt;/a&gt;&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>002915G</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Bachelor of Psychological Science</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-psychological-science</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>156</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>126000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Understand the human mind and how it drives behaviour.&lt;/p&gt;&lt;p&gt;La Trobe's Bachelor of Psychological Science will prepare you for a career as a professional psychologist, or in a psychology-related field across industries from clinical psychology to human services and marketing.&lt;/p&gt;&lt;p&gt;Elective subjects with a choice of minor sequences in Human Relationships and Neuroscience gives you the flexibility to work towards the career you want. &lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Analytical, research and communication skills&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn skills that are essential to your future career in psychology.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Clinical and health psychology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain an understanding of how to help people cope with mental and physical disorders.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Developmental and social psychology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand how environmental factors contribute to peoples' psychological makeup.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Psychological assessment, intervention and research&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Become familiar with methods to understand and measure people's psychological state.&lt;/li&gt;&lt;li&gt;Learn when and how to intervene and how to conduct research.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>006171K</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Bachelor of Biological Sciences</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-biological-sciences</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>156</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>129000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Turn your passion for biology into a diverse career. La Trobe's Bachelor of Biological Sciences gives you a strong scientific grounding plus the flexibility to specialise in an area that interests you.&lt;/p&gt;&lt;p&gt;Start with the basics. Build foundational skills in biology, chemistry, ecology and biodiversity, and explore the impacts of infection, epidemics and pandemics.&lt;/p&gt;&lt;p&gt;This degree is all about getting your hands dirty. You'll start practical classes from your first year – both in our on-campus labs and facilities, and out in the field. Get a glimpse into your professional future in science with industry-led workshops and seminars, as well as opportunities for work placements.&lt;/p&gt;&lt;p&gt;Customise your course with a major of your choice. Select from a range of areas, including biochemistry, botany, ecology, genetics, human physiological sciences, microbiology or zoology. This degree also gives you the option to take a double major or choose an additional minor.&lt;/p&gt;&lt;p&gt;All the way through your degree, you'll be building fundamental skills in experimental design, analysis, data interpretation and reporting. At the same time, you'll develop your expertise in problem-solving, teamwork, written and verbal communication and data presentation – skills that will serve you throughout whatever career you pursue.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Animal, plant and microbial biology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand the fundamentals of biology as well as the structure and function of living organisms, their life processes and diversity.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Data analysis and communication&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore experimental design issues and statistics to analyse data from experiments. Learn to effectively present information and data to different audiences.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Foundations of chemistry &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand atomic and molecular structures, chemical reactions and organic and physical chemistry and apply these principles to further study and employment.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Infections, epidemics and pandemics&lt;/strong&gt; &lt;ul&gt;&lt;li&gt;Discover how infections can threaten human wellbeing and the strategies available to prevent and cure disease.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Professional conduct and professional identify &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn about ethical conduct when working as a scientific professional and how to promote and communicate your professional identity to potential employers and peers&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Doctor of Philosophy (Education)</t>
+          <t>Low cost: 0100699; High cost: 0100698</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Doctor of Philosophy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/doctor-of-philosophy</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>208</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The Doctor of Philosophy (PhD) degree is an internationally-recognised advanced research qualification.&lt;/p&gt;&lt;p&gt;Each PhD candidate undertakes a substantial piece of independent and sustained research on an original topic under academic supervision and leading to the submission of a thesis for examination. The research is expected to make a significantly new and innovative contribution to the discipline.&lt;/p&gt;&lt;p&gt;Candidates are supported by at least two accredited supervisors with a demonstrated track record in the proposed area of investigation as outlined in the Graduate Research Supervision Policy. Progress throughout the degree is tracked and managed in keeping with the University's Graduate Research Progress Policy. Candidature may be undertaken on a full-time or part-time basis, subject to the restrictions of the student visa.&lt;/p&gt;&lt;p&gt;The thesis must be submitted within four years (or part-time equivalent) of commencement in the degree. All PhD programs are administered by the La Trobe Graduate Research School.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 10 - PhD.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>006277M</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Master of Clinical Psychology</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-clinical-psychology</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>104</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>89600</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>44800</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;You'll learn practical skills and knowledge essential for a career in professional clinical psychology. The curriculum covers areas such as cognitive behavioural therapy, child and adolescent mental health, psychopathology, counselling skills, psychological assessment and treatment, and advanced psychotherapy process skills.&lt;/p&gt;&lt;p&gt;You'll also explore the ethical and professional issues associated with work in this field, and develop skills in writing professional-standard assessment reports suitable for a range of referral agencies or contexts.&lt;/p&gt;&lt;p&gt;During your clinical placement practicum, you'll perform clinic intake assessments and conduct case work with clients including face-to-face assessment and intervention with adults and children.&lt;/p&gt;&lt;p&gt;During your program you'll be required to work on a research project. Working collaboratively with your research supervisor, you'll address a research question relevant to the field of clinical psychology and produce a research report. &lt;/p&gt;&lt;p&gt;As a graduate, you'll be equipped with the relevant skills and knowledge to work with adults and children in a range of clinical settings (such as community health centres, schools, hospitals, prisons, applied research facilities, and private practice).&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>0100037</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Bachelor of Business Analytics</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-business-analytics</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>156</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>129000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Join the La Trobe University Bachelor of Business Analytics to kick-start an exciting career that drives data, analytics, and artificial intelligence (AI) innovations for business, economic and social growth.&lt;/p&gt;&lt;p&gt;Co-designed with leading industry experts, this degree unpacks organisational and business complexities of data-driven decision-making. You will achieve this through developing knowledge and skills in the business value of data, data engineering and management, analytics technologies and application, responsible AI, and industry best practices.&lt;/p&gt;&lt;p&gt;Study with instructors who draw on their own industry and research expertise in building AI and analytics solutions to deliver an industry-oriented, future-ready learning experience. Learn in small, interactive classes that employ Gen AI teaching tools to ensure your learning journey is personalised and fully supported.&lt;/p&gt;&lt;p&gt;Build solid foundations in business fundamentals, then specialise in your business discipline of choice. You'll choose from a wide range of optional majors and minors, such as marketing, accounting, human resources, economics, so you can extend your expertise in your area of interest.&lt;/p&gt;&lt;p&gt;This degree provides pathways for industry placements, real-world projects, and international exchange opportunities, where you can apply and grow your technical and computational skills, professional and business competencies.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Business Analytics, you'll learn:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;data engineering and management, through understanding and interpreting complex, multimodal organisational data&lt;/li&gt;&lt;li&gt;descriptive, predictive, prescriptive analytics techniques, tools and applications&lt;/li&gt;&lt;li&gt;AI capabilities and adoption, such as generative and predictive AI, chatbots and agentic AI&lt;/li&gt;&lt;li&gt;AI and analytics communication, such as strategic communication of AI and analytics business value for organisational decision-making.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Master of Philosophy (High Cost)</t>
+          <t>Low cost: 0100701; High cost: 0100700</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Master of Philosophy</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/master-of-philosophy</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>104</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The Master of Philosophy (MPhil) degree is an internationally-recognised Master's (by research) degree. It is designed for students to develop advanced skills in carrying out independent and sustained research. It culminates in a thesis of up to 50,000 words or its practice-based equivalent. The thesis should demonstrate a critical application of specialist knowledge and make an independent contribution to existing scholarship in the area of research. Each candidate undertakes a piece of independent and sustained research on a topic under academic supervision and leading to the submission of a thesis for examination. Please note that some research areas require a higher fee, and you will need to apply for a different course code. &lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 – Masters Degree by Research.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>0100732</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Bachelor of Archaeology</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-archaeology</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>156</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>107400</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>35800</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're endlessly curious about the past, La Trobe's Bachelor of Archaeology is the perfect place to develop specialist skills and knowledge, and build a rewarding career as a professional archaeologist or heritage manager.&lt;/p&gt;&lt;p&gt;You'll learn from renowned researchers in La Trobe's world-class facilities and benefit from both a hands-on and academic perspective.&lt;/p&gt;&lt;p&gt;Exploring Australia's rich and varied Indigenous cultures, as well as peoples from other ancient and urban societies around the globe, you'll develop in-demand, specialist skills in contemporary archaeological practice.&lt;/p&gt;&lt;p&gt;For students interested in further study or a global career in archaeology, the Bachelor of Archaeology will give you strong field skills applicable anywhere in the world.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Archaeological fieldwork methods&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build the practical skills and knowledge you need to work in professional archaeology in Australia and overseas.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ethical heritage management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to collaborate and communicate respectfully with traditional owners and local communities.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ancient societies and civilisations&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how the human species evolved and spread across the world – adapting to new environments, transforming landscapes and developing new technologies.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Scientific methods of archaeological practice&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore a wide range of scientific techniques and methods, including geophysical survey, geographic information systems (GIS), archaeomagnetic dating, and ancient DNA.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>0100735</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Bachelor of Languages and Linguistics</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-languages-and-linguistics</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>156</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>170400</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Explore how language shapes communication, culture and global connection with La Trobe's Bachelor of Languages and Linguistics. &lt;/p&gt;&lt;p&gt;In this degree, you'll build proficiency in your chosen language while developing a deep understanding of how languages are structured, used and learned. You'll study key areas of linguistics, including phonetics, syntax, semantics, and pragmatics, and examine how language varies across social and cultural contexts. &lt;/p&gt;&lt;p&gt;Alongside your language major, you'll have the flexibility to tailor your studies through electives or a minor, allowing you to explore additional languages – including Auslan – or complementary disciplines. You'll gain real-world experience through industry-based learning, applying your knowledge in professional settings while building in-demand skills. You may also have the opportunity to study abroad and immerse yourself in the language and culture you are studying. &lt;/p&gt;&lt;p&gt;By studying the Bachelor of Languages and Linguistics, you will: &lt;/p&gt;&lt;ul&gt;&lt;li&gt;build speaking, reading and writing skills in Chinese, French, Greek, Hindi, Italian, Japanese or Spanish &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;develop AI literacy, learning to use language technologies critically and ethically while understanding their limits in real-world communication &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;analyse how languages work – from sound systems and sentence structure to meaning, and how these vary across languages and contexts &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;explore how language is acquired and how it varies across cultures, communities and social groups &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;gain real-world experience and build in-demand skills through industry-based learning, completing an industry placement or industry project in your second year &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;graduate with intercultural knowledge and communication skills to work effectively across global and diverse professional contexts. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;VCE: Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>0100796</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>Bachelor of Orthoptics (Honours)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-orthoptics-honours</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>208</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>189600</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>47400</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Make a real impact in the vision and visual function of others with La Trobe's Bachelor of Orthoptics (Honours).&lt;/p&gt;&lt;p&gt;In this degree, you'll study the anatomy and physiology of the eye to understand vision and visual function, and learn how to help people with eye disorders such as strabismus (eye turns), eye diseases and low vision. You'll gain clinical experiences from your second year, with placements in hospitals with dedicated eye clinics, private eye clinics, low vision rehabilitation organisations and our on-campus eye clinic.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Orthoptics (Honours), you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;explore the anatomy and physiology of the structures of the eye and the roles these structures play in various eye functions&lt;/li&gt;&lt;li&gt;understand the principles of optics (visible and invisible light) and how they impact the eye and visual system, including long and short-sightedness&lt;/li&gt;&lt;li&gt;undertake and interpret a clinical investigation for the diagnosis and management of various eye conditions, including strabismus, eye disease and associated vision impairment&lt;/li&gt;&lt;li&gt;learn how to use specialised technology such as retinal cameras and ultrasonography instruments with optical vision aids&lt;/li&gt;&lt;li&gt;complete an industry-based or research project, where you'll develop project management and research skills&lt;/li&gt;&lt;li&gt;get the opportunity to complete a placement beyond Melbourne in your final year with one of our partner agencies in regional Victoria, interstate or overseas – including in developing countries.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 25 in one of Biology, Chemistry, Health and Human Development, Physical Education, Physics, Psychology or any Mathematics.&lt;/p&gt; English Language Requirements&lt;p&gt;Please refer to our &lt;a href="https://www.latrobe.edu.au/study/apply/international/requirements"&gt;Language requirements&lt;/a&gt; page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;IELTS is the only English Proficiency test accepted for entry into this course.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>0100797</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>Bachelor of Podiatry (Honours)</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-podiatry-honours</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>208</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>184800</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>46200</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Take the first step towards helping others maintain and improve their mobility and independence with La Trobe's Bachelor of Podiatry (Honours).&lt;/p&gt;&lt;p&gt;In this degree, you'll benefit from being enrolled in the only podiatry program in Australia where graduates are qualified to prescribe scheduled medicines, enhancing your scope and impact in patient care. Learn from experienced podiatrists, world-leading researchers and teachers in sports medicine, biomechanics, hospital-based podiatry, private practice, paediatrics and foot surgery.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Podiatry (Honours), you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;explore topics such as human anatomy, physiology, medical conditions, pharmacology, paediatrics, biomechanics, and sport injuries and management&lt;/li&gt;&lt;li&gt;learn how to prescribe scheduled medicines, perform minor surgical procedures, refer for diagnostic imaging, and rehabilitate complex foot and ankle conditions&lt;/li&gt;&lt;li&gt;utilise specialised podiatry equipment such as gait analysis systems, 3D laser scanners to manufacture foot orthoses and doppler ultrasound to assess blood flow&lt;/li&gt;&lt;li&gt;design, manufacture and modify foot orthoses, and treat real patients at our on-campus clinic&lt;/li&gt;&lt;li&gt;benefit from placements in hospitals, specialist clinics and private practices around Australia, with optional overseas placements&lt;/li&gt;&lt;li&gt;complete a research or industry-based project in your final year – an opportunity to set yourself up for future study or the next step of your career.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 25 in one of Biology, Chemistry, Health and Human Development, Physical Education , Physics, Psychology or any Mathematics.&lt;/p&gt; English Language Requirements&lt;p&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;Please refer to our &lt;a href="https://www.latrobe.edu.au/study/apply/international/requirements"&gt;Language requirements&lt;/a&gt; page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>0100798</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>Bachelor of Prosthetics and Orthotics (Honours)</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-prosthetics-and-orthotics-honours</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>208</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>174400</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Make a real impact in treating the physical and functional limitations of others with La Trobe's Bachelor of Prosthetics and Orthotics (Honours).&lt;/p&gt;&lt;p&gt;In this degree, you'll explore topics such as anatomy, physiology, biomechanics, and prosthetic and orthotic prescription, design and fabrication. You'll hone your skills through clinical teaching at our purpose-built onsite clinic, then take what you've learned into the real world with clinical placements at external prosthetic and orthotic facilities and industry partners.&lt;/p&gt;&lt;p&gt;You'll choose from two minor options – an industry minor, or a research minor – and graduate with the skills you need to become a qualified health professional.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Prosthetics and Orthotics (Honours), you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;learn the theoretical basis and clinical practice of prosthetic and orthotic management, including treatment, assessment and prescriptions in children and adults&lt;/li&gt;&lt;li&gt;examine research and data, and how it relates to consumers&lt;/li&gt;&lt;li&gt;practice and apply the assessment, prescription, manufacture and fit of prostheses and orthoses&lt;/li&gt;&lt;li&gt;understand the importance of wellbeing in a person's healthcare journey, and how health professionals can work together to achieve the best outcome.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;IELTS (Academic) score of 7.0 with no individual band score less than 6.5. (increase in IELTS score due to a change in accreditation requirements)&lt;/p&gt;&lt;br/&gt;&lt;p&gt;IELTS is the only English Proficiency tests accepted for entry into this course.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;Please refer to our &lt;a href="https://www.latrobe.edu.au/study/apply/international/requirements"&gt;Language requirements&lt;/a&gt; page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>0100799</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Bachelor of Dental Science (Honours)</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-dental-science-honours</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>260</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>418000</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>83600</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Build a career helping others with La Trobe's Bachelor of Dental Science (Honours). Develop your professional practice at Australia's largest rural health school and be ready to practice after just five years in this accredited Honours degree.&lt;/p&gt;&lt;p&gt;Understand the foundations of dental science and get hands-on experience in clinical placements across regional Victoria. You'll treat patients under the supervision of experienced clinicians and work to improve oral health through prevention, education and clinical care.&lt;/p&gt;&lt;p&gt;If you'd like to explore further research and develop a specialisation, you can also complete a community-based project or research project, which can lead to a doctorate.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Preclinical oral health&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop your knowledge of preventive, periodontal and restorative procedures. On graduation, you'll be competent in basic preclinical skills including dental materials, infection control, OH&amp;amp;S, instrumentation and dental procedures.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Medicine for dentistry&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn to take a comprehensive medical history and understand its role in safe oral healthcare. Understand how therapeutic drugs are used to manage medical conditions.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Clinical practice&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover how to diagnose and plan care for patients. Improve your communication and treatment skills while learning to manage patients in a clinical setting.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Prosthodontics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the principles of fixed prosthodontics and apply them in practice during your clinical placement.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;IELTS is the only English Proficiency test accepted for entry into this course.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Scraped from data API (be/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>0100860</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>Bachelor of Cybersecurity/Bachelor of Commerce</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-cybersecurity-bachelor-of-commerce</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>208</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Learn how to shield companies and whole nations from malicious online threats and build the skills to run a successful enterprise with La Trobe's Bachelor of Cybersecurity/Bachelor of Commerce.&lt;/p&gt;&lt;p&gt;Decades of globalisation and technological innovation and the rise of artificial intelligence tools and cloud computing have made cybersecurity and commerce increasingly intertwined. Co-designed with industry leaders, our Bachelor of Cybersecurity/Bachelor of Commerce gives you a multidisciplinary set of skills and knowledge sought-after by employers and policymakers.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Cybersecurity/Bachelor of Commerce, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;explore topics such as cybersecurity fundamentals, financial management, strategic and crisis communications, programming and cyber algorithms, and economic analysis and innovation&lt;/li&gt;&lt;li&gt;learn the human factors involved in cybersecurity, information assurance, and cyber emergency response procedures&lt;/li&gt;&lt;li&gt;benefit from our partnerships with industry leaders like Cisco, Microsoft and Oracle&lt;/li&gt;&lt;li&gt;gain real-world experience through industry placements, work-integrated learning projects and overseas student exchange opportunities&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership into the Australian Computer Society (ACS) and, depending on your choice of majors, a range of business professional associations.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>0100861</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>Bachelor of Cybersecurity/Bachelor of Criminology</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-cybersecurity-bachelor-of-criminology</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>208</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>168000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Build the skills to understand, investigate and respond to cybercrime with La Trobe's Bachelor of Cybersecurity/Bachelor of Criminology. &lt;/p&gt;&lt;p&gt;In this double degree, you will explore crime as a social issue while learning how to manage and protect online information, systems and networks. You will study areas such as cybersecurity fundamentals, Python programming, cyber risk management and incident response, ethical hacking, criminal law, cyber law and policy, forensic science and justice systems. &lt;/p&gt;&lt;p&gt;Through labs, simulations, AI-informed threat detection activities, digital forensics activities and case-based learning, you will apply technical and investigative skills to real-world cybercrime challenges. &lt;/p&gt;&lt;p&gt;By studying the Bachelor of Cybersecurity/Bachelor of Criminology, you will learn how to: &lt;/p&gt;&lt;ul&gt;&lt;li&gt;analyse cybercrime through technical, legal, ethical and social perspectives &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;interpret the social, cultural, political and economic factors that shape crime &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;evaluate Australian and international cyber law, policy and justice systems &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;use Python programming, cyber algorithms, AI-informed threat detection and digital forensics to investigate cybersecurity challenges &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;assess how emerging technologies affect security, justice, privacy and digital regulation. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Master of Artificial Intelligence</t>
+          <t>0100864</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Master of Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/master-of-artificial-intelligence</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>104</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>87600</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Harness key AI technologies driving change and sparking innovation in a range of industries with La Trobe's Master of Artificial Intelligence.&lt;/p&gt;&lt;p&gt;Explore subjects in IT fundamentals, machine learning, data mining, computer vision, cybersecurity and natural language processing (NLP). Complement your AI expertise with transferable skills in entrepreneurship, professional practice and project management.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Master of Artificial Intelligence, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;explore deep-learning techniques and how they can aid AI functions such as image recognition, machine translation and speech synthesis&lt;/li&gt;&lt;li&gt;learn how to use research skills and deep-learning algorithms to develop AI-based solutions to real-world problems&lt;/li&gt;&lt;li&gt;gain an understanding of the moral and societal issues faced by today's IT industry and the impact of how AI technology is used&lt;/li&gt;&lt;li&gt;choose an industry development project or work-based placement to cement your learning and launch your career, or pursue an applied research project or industry-based thesis&lt;/li&gt;&lt;li&gt;benefit from the first-hand knowledge and experience of your teachers, including world-renowned AI researchers&lt;/li&gt;&lt;li&gt;have the flexibility to exit early with a Graduate Diploma after one year or a Graduate Certificate after six months or, depending on your previous computer science or IT qualifications, complete your Master's in only 1.5 years.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>0101141</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>Doctor of Midwifery</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/doctor-of-midwifery</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>208</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>170400</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>42600</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;You will graduate from this degree as a midwife who is qualified to provide leadership in advanced clinical, management, research and academic aspects of the provision of health services.&lt;/p&gt;&lt;p&gt;You will possess a unique blend of abilities stemming from clinical experience, rigorous intellectual development and participation in the study of issues significant to midwifery. The degree offers an integrated program of research with supporting coursework in the first year. Through a combination of core and elective subjects, you will gain knowledge and skills in designing and conducting research, literature review techniques, critical analysis and writing for publication, as well as opportunities to apply these skills in clinical or professional projects of relevance to nursing.&lt;/p&gt;&lt;p&gt;The research component requires you to pursue an independent and sustained investigation into a research problem that will culminate in the submission of a thesis for examination of 60,000 words.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 10 – Professional Doctorate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>0101261</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>Bachelor of Occupational Therapy (Honours)</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-occupational-therapy-honours</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>208</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>184800</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>46200</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Help people maximise their quality of life and reach their full potential with La Trobe's Bachelor of Occupational Therapy (Honours).&lt;/p&gt;&lt;p&gt;Discover the science behind human activity and get the know-how to conduct evidence-based occupational therapy assessments and interventions for people of all ages and backgrounds. Learn with a combination of face-to-face tutorials and workshops, online learning and hands-on experience, including 1,000 hours of professional placements.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Bachelor of Occupational Therapy (Honours), you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;gain essential knowledge in occupational science, anatomy, physiology and psychology&lt;/li&gt;&lt;li&gt;uncover the best treatment options for people with special needs and chronic conditions&lt;/li&gt;&lt;li&gt;explore communication as a foundation to your practice as a health professional&lt;/li&gt;&lt;li&gt;learn about group theory, process and development&lt;/li&gt;&lt;li&gt;understand cultural identity and responsiveness in relation to health and wellbeing, including First Nations' perspectives&lt;/li&gt;&lt;li&gt;apply your learning with individuals and families and collaborate with employers, policymakers and other health professionals&lt;/li&gt;&lt;li&gt;build skills in both qualitative and quantitative research design, then pursue an applied research project or industry-based thesis in your embedded Honours year&lt;/li&gt;&lt;li&gt;graduate eligible to apply for registration with the Occupational Therapy Board of Australia (OTBA).&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;Please refer to our &lt;a href="https://www.latrobe.edu.au/study/apply/international/requirements"&gt;Language requirements&lt;/a&gt; page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;IELTS, TOEFL, PTE, OET are the only English Proficiency tests accepted for entry into this course.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>0101262</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>Bachelor of Physiotherapy (Honours)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-physiotherapy-honours</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>208</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>232800</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>58200</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Become a fully-qualified physiotherapist.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Movement is essential to our health, happiness and connection to others - and physios help us move better. Get ready to use exercise and movement to improve the lives of athletes, children, adults and people recovering from surgery, injury or illness.&lt;/p&gt;&lt;p&gt;With La Trobe's Bachelor of Physiotherapy (Honours) you'll get a detailed understanding of the human body and develop the practical skills to launch your career in this rewarding and dynamic field of health. At La Trobe, not only will you learn from industry leaders and world-class researchers, you'll experience unique industry opportunities with our broad range of partners.&lt;/p&gt;&lt;p&gt;Start building your practical skills as soon as you start first year and finish your degree with clinical training equivalent to six months of workplace experience. Graduate work ready and in-demand as a fully-qualified physiotherapist and step into your first job.&lt;/p&gt;&lt;p&gt;Throughout the course you'll gain quality hands-on experience with placements at leading hospitals and private practices. You could find yourself in acute hospital units, rehabilitation facilities, community health clinics, private practice, sporting organisations, educational facilities or research centres.&lt;/p&gt;&lt;p&gt;Choose to take your physiotherapy degree global with international placement or study opportunities - like students before you who've experienced Denmark, Italy, Vietnam and India. Or keep it local with placements throughout Melbourne and regional Victoria.&lt;/p&gt;&lt;p&gt;In your Honours year, you'll undertake research or industry-based project work where you'll solve real problems relating to human health and physical performance.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Bioscience&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain an intricate understanding of the human body through the study of anatomy, physiology, pathology, biomechanics of human movement and pharmacology.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Physiotherapy skills&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover how to assess, diagnose and improve people's movement, health and quality of life.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Specialised areas&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to apply your physiotherapy skills to help people with a variety of conditions which relate to cardiorespiratory, musculoskeletal, sports, neurological, women's, men's, paediatric and aged care health.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 25 in two of Biology, Chemistry, Physics, General Mathematics, Mathematics Methods, Specialist Mathematics or Physical Education.&lt;/p&gt; English Language Requirements&lt;p&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;Please refer to our &lt;a href="https://www.latrobe.edu.au/study/apply/international/requirements"&gt;Language requirements&lt;/a&gt; page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>0101263</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Bachelor of Social Work (Honours)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-social-work-honours</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>208</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>145600</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>36400</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;As a social worker, you'll provide support and assistance to people and families in need. La Trobe's Bachelor of Social Work (Honours) gives you the clinical knowledge and hands-on skills to launch your career.&lt;/p&gt;&lt;p&gt;You'll learn from world-renowned academics about promoting human rights and the importance of social justice. Our diverse range of subjects provide foundations in both psychology and sociology. Two 14-week placements enable you to put your knowledge and skills into practice and gain professional experience within leading health and welfare organisations in Victoria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sociology and society&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover the cultural changes that shaped Australian society and how individuals connect with each other.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Introductory psychology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Study they key areas of psychology and explore how diverse contexts affect individuals in different ways. Discover how your brain helps to create your behaviour, and how your brain and behaviour change across your lifespan.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Human services&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the values, ethics and practice of social work and human services.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Social work and inequality&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Study the issues of inequality and their impact on people's wellbeing.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Please refer to our Language requirements page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/li&gt;&lt;li&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>0101264</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>Bachelor of Speech Pathology (Honours)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-speech-pathology-honours</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>208</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>209600</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>52400</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Help others find their voice.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Our ability to communicate clearly and enjoy food or drink are things we can take for granted. But people of all ages can experience difficulties and the effects can be devastating. Speech pathologists work to improve a person's abilities, they also work to improve quality of life. Launch your career in this rewarding field of health with La Trobe's Bachelor of Speech Pathology (Honours).&lt;/p&gt;&lt;p&gt;You'll develop an understanding of the anatomy behind speech and swallowing impairments and provide therapeutic treatment and management options. Build hands-on skills with approximately 1,000 hours of placement on-campus and in clinics across Victoria. You'll also learn how to improve speech pathology services and policies by tackling a fourth-year industry project or research thesis.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Therapeutic intervention and management&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;&lt;ul&gt;&lt;li&gt;Design and manage the best course of treatment for patients with communication and swallowing impairments.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Anatomy and neurophysiology&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;&lt;ul&gt;&lt;li&gt;Gain an understanding of the functional anatomy and neurophysiology relevant to communication and swallowing and their role in impairment.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;The science of speech and hearing&lt;/strong&gt;&lt;/li&gt;&lt;li&gt;&lt;ul&gt;&lt;li&gt;Discover the latest techniques for investigating sound, speech, and hearing, including the analysis of sound waves and speech, and the psychology of sound perception.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 25 in one of Biology, Chemistry, any Mathematics, Physical Education, Physics or Health and Human Development.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;IELTS is the only English Proficiency test accepted for entry into this course.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;Please refer to our &lt;a href="https://www.latrobe.edu.au/study/apply/international/requirements"&gt;Language requirements&lt;/a&gt; page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;7.5 IELTS (Academic) with no individual band less than 7.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>0101684</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>Master of Digital Health</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-digital-health</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>104</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>82800</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>41400</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>May, March, July, September, November</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Gain an in-demand skill set to design, implement and manage digital health solutions that meet the evolving healthcare needs of individuals and communities with La Trobe's Master of Digital Health.&lt;/p&gt;&lt;p&gt;Advance your knowledge in new and emerging areas of digital health, including health analytics, virtual care, the Internet of Medical Things (IoMT), websites, apps and social media. Explore these technologies and their applications by examining benefits, risks and their ethical and legal implications. Tailor your degree to your career goals with a range of practical specialisations and electives, from data analytics, cybersecurity and artificial intelligence (AI) to management, strategy, policy and opportunities to apply your learning by working on real-world digital health solutions with industry.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Master of Digital Health, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;embrace a design-thinking mindset, using data-driven, human-centered and experience-based approaches to solutions&lt;/li&gt;&lt;li&gt;gain an understanding of big data health analytics and explore how it can be applied to real-world applications&lt;/li&gt;&lt;li&gt;discover powerful tools to effectively communicate health information to different audiences in the digital age &lt;/li&gt;&lt;li&gt;assess organisational preparedness for digital transformation and know how to plan and conduct successful digital transformation programs&lt;/li&gt;&lt;li&gt;graduate ready to work at the forefront of a progressive and secure healthcare system.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Master of Education (By Coursework)</t>
+          <t>011412M</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Master of Education</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/master-of-education</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>104</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>76000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>38000</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Harness educational best practice and advance your career as a seasoned educator or professional in a related field to move into leadership or specialist positions with La Trobe's Master of Education.&lt;/p&gt;&lt;p&gt;Experiment, innovate, adapt and address the important challenges of our sector. Learn how to engage with curriculum reforms and design educational programs. Explore the science of language and literacy, and understand how to use data to inform evidence-based practice.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By studying La Trobe's Master of Education, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;study core subjects in educational leadership, psychology, research and digital technologies, each designed and structured to meet the evolving needs of educators and professionals&lt;/li&gt;&lt;li&gt;choose your specialisation – inclusion and diversity, language and literacy, or leadership and management – and graduate with it on your academic transcript so employers can recognise your expertise&lt;/li&gt;&lt;li&gt;explore diversity in educational contexts, plan for socially-just education, and immerse yourself in school, community and cultural learning environments&lt;/li&gt;&lt;li&gt;benefit from access to the latest research, teaching and professional networks through our partnerships with schools, communities and governments&lt;/li&gt;&lt;li&gt;balance your studies around your professional and personal commitments, with the option to study online, on campus or a mix of both.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Note&lt;/strong&gt;: The Master of Education is not an initial teacher education (ITE) course and does not lead to a Victorian Institute of Teaching (VIT) registration. If you're looking to start your career as a teacher, see our &lt;a href="https://www.latrobe.edu.au/courses/master-of-teaching-primary"&gt;Master of Teaching (Primary)&lt;/a&gt; or &lt;a href="https://www.latrobe.edu.au/courses/master-of-teaching-secondary"&gt;Master of Teaching (Secondary)&lt;/a&gt;.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>019479E</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Bachelor of Business</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-business</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>156</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>129000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Develop solid foundations in modern business. La Trobe's Bachelor of Business is an AI-integrated course, embedding artificial intelligence concepts and tools across the curriculum to prepare students for the evolving demands of the business world, ensuring you'll graduate with future-ready skills to enhance your employability in an increasingly digital workplace.&lt;/p&gt;&lt;p&gt;In this flexible degree, you'll explore the fundamentals of business with the option to pair your major with a minor, take two minors instead of a second major, or combine a minor with four electives – giving you plenty of options to shape your degree around your interests.&lt;/p&gt;&lt;p&gt;The Bachelor of Business equips you to tackle current and future business challenges. This course places a strong emphasis on entrepreneurship and core business principles, equipping you with the skills and mindset to lead teams, drive innovation, or start your own business.&lt;/p&gt;&lt;p&gt;Study a business degree that empowers you to make a positive social impact and contribute to a sustainable future with a course curriculum guided by the Principles for Responsible Management Education (PRME) and integrates the United Nation's Sustainable Development Goals (SDGs).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By studying La Trobe's Bachelor of Business, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;apply your learning into the real world through industry placements and work-integrated learning projects.&lt;/li&gt;&lt;li&gt;fit study around your life with the flexibility to study online, on campus, or a mix of both through StudyFlex&lt;/li&gt;&lt;li&gt;gain a strong foundation in core business disciplines in marketing, management, economics, accounting, and finance&lt;/li&gt;&lt;li&gt;develop a blended fundamentals and technical skillset in leadership, communication, critical thinking, digital literacy, business structures, modern business software, business strategies and more&lt;/li&gt;&lt;li&gt;depending on your campus, choose from majors in agribusiness, digital business, economics, finance, human resource management, international business, management, marketing, or tourism and event management&lt;/li&gt;&lt;li&gt;get taught by academics and teachers with a mix of theoretical knowledge and practical experience in smaller class sizes, giving you more personalised support and stronger connections to your peers and teachers.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Bachelor of Nursing (Pre-Registration)</t>
+          <t>113570D</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>Bachelor of Nursing</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-nursing</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>156</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>133800</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>44600</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Get the skills and confidence to care for people of all ages in all clinical situations while building your resilience to navigate a rapidly evolving healthcare sector with La Trobe's future-focused Bachelor of Nursing.&lt;/p&gt;&lt;p&gt;Learn from leading clinicians and academics and gain hands-on experience in our state-of-the-art simulation labs. Move into real-world environments in hospitals and healthcare agencies in your first year, reaping the benefits of our long-standing partnerships with top-tier health providers like Austin Health, The Royal Women's Hospital and Bendigo Health.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By completing La Trobe's Bachelor of Nursing, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop a strong foundation in acute care, chronic illness, Indigenous health, mental health, rehabilitation, community and emergency care, biosciences and research&lt;/li&gt;&lt;li&gt;gain in-demand employability skills in leadership, time management, critical thinking and communication, giving you the confidence to make ethical clinical decisions with empathy and compassion&lt;/li&gt;&lt;li&gt;tailor your skills with minors in mental health, child, family and community health or rural health&lt;/li&gt;&lt;li&gt;benefit from placements with our partners, preparing you to step into employment once you graduate&lt;/li&gt;&lt;li&gt;graduate ready to apply to become a registered nurse (RN) with the Australian Health Practitioner Regulation Agency (AHPRA).&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Note:&lt;em&gt; Completion of this course is subject to core participation requirements, essential requirements, and additional costs. Please see the &lt;a href="https://www.latrobe.edu.au/courses/bachelor-of-nursing#/entry-requirements"&gt;Entry requirements &amp;amp; pathways &lt;/a&gt;and &lt;a href="https://www.latrobe.edu.au/courses/bachelor-of-nursing#/fees"&gt;Fees &amp;amp; scholarships&lt;/a&gt; tabs for more information.&lt;/em&gt;&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;IELTS, TOEFL and PTE are the only English Proficiency tests accepted for entry into this course.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Please note:&lt;br/&gt;&lt;/strong&gt;&lt;a href="http://pearsonpte.com/"&gt;&lt;strong&gt;Pearson Test of English &lt;/strong&gt;&lt;/a&gt;(PTE) Academic. &lt;br/&gt;Applicants must achieve a minimum overall score of 65 and a minimum score of 65 in each of the four communicative skills (listening, reading, writing and speaking).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;em&gt;NOTE:&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;We will only accept test results:&lt;/strong&gt;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;&lt;em&gt;from one test sitting, or&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;a maximum of two test sittings in a six month period only if:&lt;/em&gt;&lt;/li&gt;&lt;/ol&gt;&lt;ul&gt;&lt;li&gt;&lt;em&gt;a minimum overall score of 65 is achieved in each sitting, and&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;you achieve a minimum score of 65 in each of the communicative skills across the two sittings, and&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;no score in any of the communicative skills is below 58&lt;/em&gt;&lt;/li&gt;&lt;/ul&gt;&lt;br/&gt;&lt;p&gt;IELTS of 7.0 with no individual band score less than 7.0 (can be across 2 sittings in a 6-month period, but no score can be below 6.5 and overall score must be 7 in both sittings)&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>118149K</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>Bachelor of Computer Science</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-computer-science</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>156</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>126000</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Step into an in-demand career at the frontlines of an increasingly complex digital landscape with La Trobe's Bachelor of Computer Science.&lt;/p&gt;&lt;p&gt;At La Trobe, you'll get more than a basic technical foundation. We'll prepare you to face the challenges of a networked society by building a solid foundation in programming, algorithms, databases, networks, cybersecurity, and AI — the essential skills every modern computer scientist needs.&lt;/p&gt;&lt;p&gt;Designed in partnership with industry leaders like Cisco, Optus, and ANZ, you'll translate theory into professional practice with industry-informed, real-world projects and assessments that prepare you for in-demand careers locally and globally.&lt;/p&gt;&lt;p&gt;This course is designed for students seeking a robust, future-ready education in computer science, particularly those aiming for careers in high-demand fields such as artificial intelligence (AI), data science, software engineering, and cybersecurity.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Bachelor of Computer Science, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;sharpen your thinking with computational, logical, and analytical thinking skills through modern tools and updated subject content&lt;/li&gt;&lt;li&gt;personalise your learning journey with StudyFlex. Choose to study on campus, online, or a mix of both to suit your lifestyle&lt;/li&gt;&lt;li&gt;choose from majors in Artificial Intelligence, Data Science, or Software Engineering to align your studies with your career goals&lt;/li&gt;&lt;li&gt;access to state-of-the-art research centres and labs, gaining practical experience with technologies in AI, cybersecurity, data analytics, and software engineering&lt;/li&gt;&lt;li&gt;join a network of successful graduates with strong employment outcomes, high satisfaction rates, and skills that employers actively seek worldwide.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Units 3 and 4: a study score of at least 20 in any Mathematics&lt;/li&gt;&lt;li&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>022039C</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>Bachelor of Science</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-science</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>156</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>129000</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Build a strong foundation in science while exploring disciplines, majors and career pathways with La Trobe University's Bachelor of Science. &lt;/p&gt;&lt;p&gt;In this degree, you will study scientific concepts and learn how scientists think, work, test ideas and share their findings. You will explore areas such as data analysis, research, sustainability and emerging technologies, including artificial intelligence. You will then apply your learning through laboratories, fieldwork, industry projects and work-integrated learning opportunities. &lt;/p&gt;&lt;p&gt;You can shape your degree through majors, minors or a double major, with pathways into Honours, postgraduate study, research and science-related careers. Depending on your campus and study mode, you could choose from up to 18 majors, 24 minors and a wide range of electives. &lt;/p&gt;&lt;p&gt;Along the way, you'll develop transferable skills in critical thinking, data analysis and applying scientific methods with precision, preparing you for science-related careers, roles beyond traditional science fields and opportunities across a wide range of industries. &lt;/p&gt;&lt;p&gt;&lt;strong&gt;By studying the Bachelor of Science, you will learn how to:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;analyse scientific problems using evidence, data and discipline knowledge &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;apply laboratory, fieldwork and research skills in practical scientific contexts &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;interpret data and communicate findings for professional and non-specialist audiences &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;evaluate scientific approaches across areas such as biotechnology, environmental science, pharmaceuticals and research &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;design solutions to real-world problems through collaboration, projects and applied learning &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;assess your study direction through majors, minors, double-major options and further study pathways. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/li&gt;&lt;li&gt;Units 3 and 4: a study score of at least 20 in any Mathematics.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bachelor of Arts / Bachelor of Health Sciences</t>
+          <t>025959E</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>Bachelor of Arts/Bachelor of Health Sciences</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-arts-bachelor-of-health-sciences</t>
         </is>
       </c>
+      <c r="D29" t="n">
+        <v>208</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>163200</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>40800</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Pursue your curiosity, passion and profession and make the world a healthier and fairer place with La Trobe's interdisciplinary Bachelor of Arts/Bachelor of Health Sciences.&lt;/p&gt;&lt;p&gt;Examine the way social, environmental and political structures affect the health of individuals, families and communities at local, national and international levels. At the same time, explore your interests and pursue your passion, with a diverse range of majors, minors and electives.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Arts/Bachelor of Health Sciences, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;create your own path with humanities and social sciences majors, including psychological science, sociology, crime justice and legal studies, creative and professional writing, and more&lt;/li&gt;&lt;li&gt;choose from nine health sciences majors including allied health, digital health, environmental health, food and nutrition, health promotion, health wellbeing and performance, public health and rehabilitation counselling&lt;/li&gt;&lt;li&gt;gain real-world experience through internships, overseas experiences and health placements&lt;/li&gt;&lt;li&gt;study how it suits you with the option to study online or at our Melbourne Campus&lt;/li&gt;&lt;li&gt;depending on your health sciences major, graduate with a pathway into postgraduate allied health and other health degrees, including audiology, physiotherapy, speech pathology and occupational therapy.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Master of Health Administration</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-health-administration</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>104</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>May, March, July, September, November</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The Master of Health Administration will help you develop the skills and experience you need to lead and manage projects, health agencies, services and programs. We'll prepare you to advance into leadership and management in the public and private sectors in general management and in specialist roles in areas such as project management, quality management and the management of particular health professions.&lt;/p&gt;&lt;p&gt;Our teaching staff have clinical qualifications in areas such as medicine, physiotherapy, nursing, organisational psychology and statistics, and in health administration research. They've worked in senior healthcare management roles in Australia and overseas, with organisations such as the Toronto Hospital (Canada), Inner and Eastern Healthcare Network (Melbourne) and various consulting firms, as well as having extensive governance experience.&lt;/p&gt;&lt;p&gt;The range of electives allows you to further explore health economics and finance, health law and ethics, and process redesign.&lt;/p&gt;&lt;p&gt;The subject timetable is designed to give you the flexibility you need to successfully balance study with your other commitments: the combination of evening, block and online study modes means that you can choose when and how you study.&lt;/p&gt;&lt;p&gt;HM002CI is the traditional Master of Health Administration with the choice of face-to-face or online study. HM002O is the fully online version.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Offshore applicants are considered for admission based on the stated course entry requirements.&lt;/li&gt;&lt;li&gt;IELTS may be considered.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Scraped from data API (on/2026/international)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>037928B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>Master of Information Technology</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-information-technology</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>104</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>87600</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Build your technical expertise and gain an IT skillset future-proofed for industry needs with La Trobe's Master of Information Technology.&lt;/p&gt;&lt;p&gt;Get essential skills in database logic and data structures, programming, cybersecurity, network engineering and artificial intelligence. Complement your IT know-how with transferable skills in entrepreneurship, professional practice and project management.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Master of Information Technology, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop software engineering skills and master full-stack, front-end and software development&lt;/li&gt;&lt;li&gt;improve your Java and Python knowledge in programming, algorithms and data structures&lt;/li&gt;&lt;li&gt;tailor your degree to your career goals with specialisations in artificial intelligence, cloud analytics, cybersecurity, internet of things (IoT), networking, quantum information technology or software engineering, plus a range of electives&lt;/li&gt;&lt;li&gt;supplement your skills with certifications through our partnership with Microsoft and get hands-on experience in our on-campus Cisco labs&lt;/li&gt;&lt;li&gt;choose an industry development project or work-based placement to cement your learning and launch your career, or pursue an applied research project or industry-based thesis&lt;/li&gt;&lt;li&gt;have the flexibility to exit early with a Graduate Diploma after one year or a Graduate Certificate after six months or, depending on your previous computer science or IT qualifications, complete your Master's in only 1.5 years&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>049582B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>Graduate Diploma in Information Technology</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-in-information-technology</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>52</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>May, March, July, September</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The Graduate Diploma in Information Technology aims to provide you with a general professional qualification in information technology (IT). Broaden or deepen your knowledge of using computers. The core subjects provide you with a foundation in information systems, software development and computer networking. &lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Technology assessment&lt;/strong&gt; &lt;ul&gt;&lt;li&gt;Evaluate the capacity and capability of different technologies to select the most appropriate technology solution for each situation. &lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Software testing&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Use research and technical skills to test your IT solutions and learn how to prevent bugs, reduce development costs and improve performance.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Communication and ethics&lt;/strong&gt; &lt;ul&gt;&lt;li&gt;Learn how to communicate professionally within the IT sector to ensure you operate aligned to the ethical and cultural values of the IT profession. &lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Critical thinking&lt;/strong&gt; &lt;ul&gt;&lt;li&gt;Understand and critique proposed IT solutions with technical and theoretical knowledge to plan and implement IT solutions effectively. &lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Offshore applicants are considered for admission based on the stated course entry requirements.&lt;/li&gt;&lt;li&gt;IELTS may be considered.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>049585K</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>Master of Biotechnology and Bioinformatics</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-biotechnology-and-bioinformatics</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>104</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>90800</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>45400</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;In La Trobe's Master of Biotechnology and Bioinformatics, you'll learn to harness new and emerging technologies in human health, diagnostics, sustainability, food security and renewable energy.&lt;/p&gt;&lt;p&gt;Develop the human skills and technical expertise to launch a career in a range of exciting industries. From biological products to pharmaceuticals, agriculture to nutrition: you'll be prepared to work in the fields that rely on this fast-growing area of science.&lt;/p&gt;&lt;p&gt;This degree gives you more than flexibility in your career – it also gives you flexibility in how you study. In your final year, you could take an advanced bioinformatics pathway. Or you could choose the research project pathway instead, enjoying unrivalled access to industry networks and researchers in the field and benefiting from 25-30 hours of laboratory time each week.&lt;/p&gt;&lt;p&gt;If you decide you want to head straight into the workforce, you could even exit with a Graduate Diploma in Biotechnology and Bioinformatics after successfully completing the first year of this degree.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Bioinformatics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Use industry-standard bioinformatics software to address biological problems.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Practical biotechnology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain practical skills in PCR, cloning, protein expression, protein purification and immunoblotting laboratory techniques.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Scientific communication skills&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build your expertise in writing reports and presenting data.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Proteomics and genomics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore advanced technologies such as CRISPR-mediated gene editing, next generation sequencing and mass spectrometry.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Protein chemistry&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Practice the laboratory techniques used in purifying and characterising protein preparations.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>049940G</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>Bachelor of Information Technology</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-information-technology</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>156</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>126000</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Designed to help you build our digital future, La Trobe's Bachelor of Information Technology equips you with skills across programming, networking, databases, systems analysis and design, and project management.&lt;/p&gt;&lt;p&gt;Along with building a strong set of core IT skills you can choose to major in one of several areas aligned to future industry growth including artificial intelligence, cloud analytics, cybersecurity, network engineering or information systems.&lt;/p&gt;&lt;p&gt;Broaden your knowledge and capabilities further through a wide range of electives. Combine your core IT skills with business, social sciences, humanities, web engineering, computer technology, security and information systems analysis subjects. Plus you could develop a software program of your own, which you could present at the annual Engineering and IT Showcase to potential employers.&lt;/p&gt;&lt;p&gt;With industry-based projects and CISCO certification embedded in the course, you'll receive professional mentoring opportunities as you build career ready skills. You'll also gain access to our expert research centres, including the Centre for Technology Infusion and our state-of-the-art Technology Innovation Lab for the Internet of Things – developed in collaboration with Microsoft and CISCO.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Web and software development&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop and build websites and software. Administer the front end, back end and server side of websites and IT systems.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;IT systems analysis and design&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand and analyse IT systems to deliver more efficient and effective IT solutions for your organisation.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Design&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn about software, system and network design so you can contribute to making better programs and infrastructure.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Programming and networking&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the language of computers and how they communicate with one another to create working code and smarter systems.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Project management, estimation, documentation and report evaluation&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;IT is more than just computers. Learning to manage projects and communicate effectively is a must in any organisational environment.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Doctor of Clinical Science (Clinical Speech Pathology, Clinical Vision Sciences, Family Therapy, Occupational Therapy, Prosthetics and Orthotics, Counselling and Psychotherapy)</t>
+          <t>054041M</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>Doctor of Clinical Science</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/doctor-of-clinical-science</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>208</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're a practitioner in clinical sciences in: Occupational Therapy, Physiotherapy, Prosthetics and Orthotics, Podiatry, Speech Pathology, Audiology, Orthoptics, or Food, Nutrition and Dietetics, this degree provides you with an opportunity to extend your professional practice through an integrated program of theory, practice and research.&lt;/p&gt;&lt;p&gt;The degree offers an integrated program of research with supporting coursework in the first year. Through a combination of core and elective subjects, you'll gain knowledge and skills in designing and conducting research, literature review techniques, critical analysis and writing for publication, as well as opportunities to apply these skills in clinically-based professional projects.&lt;/p&gt;&lt;p&gt;You'll pursue an independent and sustained investigation into a research problem that will culminate in the submission of a thesis for examination of 60,000 words.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 10 – Professional Doctorate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Master of Social Work (Research)</t>
+          <t>110240B</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Master of Social Work</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/master-of-social-work</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>104</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>77000</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>38500</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Master of Social Work gives you the skills and knowledge to turn your passion for social justice into a thriving career. Whether you're looking to advance your career or move into a rewarding new field, you'll gain the hands-on expertise to help people in need.&lt;/p&gt;&lt;p&gt;Learn from world-class academics with extensive backgrounds in social work practice, including specialists in areas such as addiction, child and family welfare, disability, and mental health. Explore the various roles undertaken by social workers, including direct practice, social policy, education and research, community development, counselling, organisational planning.&lt;/p&gt;&lt;p&gt;Under the supervision of an experienced social worker, you'll put your knowledge into practice by completing two 70-day placements. Through our partnerships with Eastern Health, Northern Health and Alfred Health, and community partners, you'll work in real industry settings and gain valuable insights into the day-to-day experiences of social workers.&lt;/p&gt;&lt;p&gt;Graduate ready to work effectively in a range of social policy, community and direct practice areas in government, community, and the private sector. Social workers are in high demand across the globe, meaning your career could take you anywhere. You can also choose to extend your professional practice and undertake research in professional or community settings through a &lt;a href="https://www.latrobe.edu.au/courses/doctor-of-social-work-professional-doctorate"&gt;Social Work Professional Doctorate&lt;/a&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Human rights, law and ethics in social work&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the legal context of Australian social work practices and the ethical principles that guide them.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Social policy analysis and advocacy&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain an understanding of key social welfare ideologies and apply this knowledge to analyse and evaluate contemporary social policy.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Social work with individuals, families and groups&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover the theoretical frameworks used to assess and build relationships with clients, including casework theory and preparing an intervention plan.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Program design and evaluation&lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;Develop the knowledge and skills needed to design and implement programs that help address social welfare issues.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>English Language Requirements&lt;p&gt;Please refer to our &lt;a href="https://www.latrobe.edu.au/study/apply/international/requirements"&gt;Language requirements&lt;/a&gt; page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>060348G</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>Bachelor of Animal and Veterinary Biosciences</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-animal-and-veterinary-biosciences</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>156</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>44000</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;With La Trobe's Bachelor of Animal and Veterinary Biosciences, you can turn your love of animals into a fulfilling career. Study the basics of animal science, including breeding, nutrition and animal welfare. You'll also delve into global issues such as food security, epidemics and pandemics, and the environmental impacts of animal agriculture. In later years you'll explore animal physiology, biochemistry and immunology.&lt;/p&gt;&lt;p&gt;Theory is vital, but we know you can only learn so much in the classroom. That's why your theoretical studies will be supported by robust hands-on learning. Each year of your degree will include practical elements, such as real-life animal case studies which give you the chance to work closely with our industry partners. Placements – both compulsory and elective – allow you to take your learning out of the classroom and into the real world. Industry experts will present lectures and workshops throughout your degree, giving you first-hand insights into your future. You'll graduate with experience under your belt and the foundations of a strong professional network.&lt;/p&gt;&lt;p&gt;Already know how you want your career to look? There's scope for you to make this degree what you want it to be. A wide range of electives in areas like zoology, wildlife and agriculture science give you the opportunity to tailor your studies to your career goals.&lt;/p&gt;&lt;p&gt;You'll graduate ready for the workplace, or you can use this course as a pathway into a veterinary medicine degree.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll get the opportunity to learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Animal science&lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;Build important foundations in all aspects of animal science, including animal health, nutrition, physiology, welfare, reproduction and management.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Microbiology&lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;Learn about microorganisms, how they live, how they work and how they cause disease.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Metabolic biochemistry&lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;Become familiar with the underlying biochemical processes that occur in animals, including those used to generate energy to maintain body function&lt;strong&gt;.&lt;/strong&gt;&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>062549E</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>Bachelor of Biomedical Science</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-biomedical-science</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>156</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>137400</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>45800</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Explore human biology, disease processes and biomedical science with La Trobe's Bachelor of Biomedical Science. &lt;/p&gt;&lt;p&gt;In this degree, you will study foundational and applied biomedical sciences, with the flexibility to shape your degree through open electives that help you explore your interests and future study or career goals. &lt;/p&gt;&lt;p&gt;You will build core knowledge in anatomy, physiology, chemistry, bioscience, statistics, microbiology and epidemiology. Then you will deepen your understanding of physiology, pharmacology and biochemistry, while connecting biomedical science concepts to human body systems, health and disease. &lt;/p&gt;&lt;p&gt;You will apply your knowledge to clinically focused areas, including pathophysiology, biotechnology, pharmacology and diseases affecting major body systems. You can also extend your practical experience through elective placement opportunities. &lt;/p&gt;&lt;p&gt;By studying the Bachelor of Biomedical Science, you will learn how to: &lt;/p&gt;&lt;ul&gt;&lt;li&gt;analyse anatomy and physiology to understand how major body systems support health and respond to disease &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;apply chemistry, biochemistry and molecular biology to biomedical science and human health &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;interpret microbiology, epidemiology and statistics to examine infection, health and disease &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;evaluate how diseases develop and progress across major body systems &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;assess how medicines interact with the body to prevent, manage and treat disease &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;apply biomedical science knowledge across diagnostics, biotechnology, haematology, infectious disease and chronic disease. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Scraped from data API (be/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>062598G</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>Bachelor of Health Sciences</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-health-sciences</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>156</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>122400</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>40800</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Create a rewarding career in Australia's fastest-growing sector by changing the lives of individual people and whole populations with La Trobe's Bachelor of Health Sciences.&lt;/p&gt;&lt;p&gt;Examine the way our minds, society, environment and political structures affects the health of individuals, families and communities at local, national and international levels. Broaden your expertise with a choice of nine majors and the option of second majors and minors in health sciences or a range of other disciplines.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Health Sciences, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;build your skills in scientific thinking, lab and fieldwork, problem solving, collaboration, professional conduct and scientific communication&lt;/li&gt;&lt;li&gt;study how it suits you with options to study on campus or online, as well as Diploma and Associate Degree early exit options&lt;/li&gt;&lt;li&gt;choose from majors in allied health, digital health, environmental health, food and nutrition, health promotion, health, wellbeing and performance, psychological science, public health, and rehabilitation counselling&lt;/li&gt;&lt;li&gt;graduate ready to make real impact on health policy and practice in areas such as digital health, environmental health, nutrition or health promotion – or, depending on your choice of major, gain a pathway into postgraduate allied health and other health degrees, including audiology, physiotherapy, speech pathology and occupational therapy.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;*Please be aware that the digital health, health promotion and public health majors in this course include mandatory in-person placement requirements. Students are expected to complete these placements in Australia.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>062795B</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Master of Occupational Therapy Practice</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-occupational-therapy-practice</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>104</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>101200</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>50600</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Help individuals and communities to maximise productivity, wellbeing and quality of life with La Trobe's Master of Occupational Therapy Practice.&lt;/p&gt;&lt;p&gt;Open to students from any undergraduate discipline, you'll graduate with a competitive edge through a combination of coursework and 1000 hours of hands-on, industry-responsive placements. Designed to meet the competencies for safe and effective practice, you'll develop advanced knowledge and skills in assessment and intervention, the therapeutic use of occupation and the adaptation of environments.&lt;/p&gt;&lt;p&gt;Get hands-on with a six-week, full-time professional practice block in your first year, then two eight-week, full-time professional practice blocks and a ten-week project-based learning placement in your second year.&lt;/p&gt;&lt;p&gt;Subject to completion of local requirements, graduates may be eligible to apply to practice in other countries including the UK, North America and Sweden.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Master of Occupational Therapy Practice, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;benefit from an integrated learning approach that reflects modern occupational therapy practice expectations&lt;/li&gt;&lt;li&gt;focus on four key themes: First Nations' knowledge and cultural safety, evidence-based practice, occupation, and professionalism.&lt;/li&gt;&lt;li&gt;explore the theoretical foundations of occupational therapy, recognising the relationship between occupational participation, health and well-being&lt;/li&gt;&lt;li&gt;develop advanced skills in searching, appraising and integrating research evidence into practice&lt;/li&gt;&lt;li&gt;understand how to describe, critique and apply the principles of engagement, assessment, intervention and case management&lt;/li&gt;&lt;li&gt;learn how to integrate specialised knowledge, professional reasoning and professional behaviour within practice.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;IELTS, TOEFL, PTE are the only English Proficiency tests accepted for entry into this course.&lt;/li&gt;&lt;li&gt;Refer to Language requirements page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/li&gt;&lt;li&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>111850A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>Master of Physiotherapy Practice</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-physiotherapy-practice</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>104</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>122400</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>57600</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>January</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Physiotherapists assess, diagnose and treat patients with movement disorders or disabilities, including those with temporary or long-term injuries and musculoskeletal, neurological, and cardiorespiratory conditions. Physiotherapists use a range of skills, including education and advice, movement or exercise prescription and manual therapy with the aim of assisting people to achieve their goals for recovery, activity, participation and quality of life. Physiotherapists may work independently or as members of multidisciplinary healthcare teams. They are active in the prevention of illness and injury and in the promotion of health, and are also involved in clinical research, movement rehabilitation, ergonomics and the management of healthcare organisations.&lt;br/&gt;Following an applied anatomy subject in Term 1 (Jan-Feb), the first year of the course will develop core knowledge and skills required for effective physiotherapy practice in a range of healthcare settings, across a variety of practice areas, and work with clients from across the lifespan. The second year of the course comprises integrated theory and clinical practice subjects, where advanced physiotherapy knowledge and skills will be developed and applied to clinical environments. &lt;/p&gt;&lt;p&gt;The clinical practice and theory subjects extend outside official University semester dates. The course includes small-group learning to master the practical aspects of physiotherapy practice. You will be expected to assess and treat patients in hospitals and other clinical settings under the supervision of a qualified clinician.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>English Language Requirements&lt;p&gt;Please refer to our &lt;a href="https://www.latrobe.edu.au/study/apply/international/requirements"&gt;Language requirements&lt;/a&gt; page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;IELTS, TOEFL and PTE are the only English Proficiency tests accepted for entry into this course.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>062804F</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>Master of Health Information Management</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-health-information-management</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>104</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>87200</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>33400</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Combine the clinical and business sides of healthcare and use data to enhance the quality of patient care with La Trobe's multidisciplinary Master of Health Information Management.&lt;/p&gt;&lt;p&gt;Excel in a specialised profession that ensures patient health information is accurate, complete, accessible and secure. Hone your skills in clinical classification, data analytics, health informatics, health systems and workforce management. Expand professional networks with placements in healthcare agencies and management training to help you step straight into senior healthcare roles.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Master of Health Information Management, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;master IT skills to implement and manage health information systems in the context of cybersecurity, identifier and interoperability requirements&lt;/li&gt;&lt;li&gt;analyse and interpret health data for safety and quality reporting, health service benchmarking and population health&lt;/li&gt;&lt;li&gt;build skills in health classification and data application to address funding reimbursement, organisational planning and research practice&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership of the Health Information Management Association of Australia (HIMAA), the Australasian Institute of Digital Health (AIDH) and the Clinical Coders' Society of Australia (CCSA).&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;*Please be aware that this course includes mandatory in-person placement requirements. Students are expected to complete these placements in Australia.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>066343J</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Bachelor of Accounting</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-accounting</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>156</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>129000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Shape the future of business with skills that matter.&lt;/p&gt;&lt;p&gt;Want to turn your passion for business and problem-solving into a career with real impact? La Trobe's Bachelor of Accounting is your launchpad. Developed in close collaboration with industry partners, this degree doesn't just teach accounting — it prepares you to lead in a world driven by data, digital innovation, and ethical decision-making.&lt;/p&gt;&lt;p&gt;Learn by doing — not just listening. From your first year, you'll work with industry-standard cloud-based software and tackle real-world business challenges through immersive simulations and projects. You'll explore how accounting shapes smart decisions in every part of a business — and why it's at the heart of every successful organisation.&lt;/p&gt;&lt;p&gt;Small, supportive classes mean you'll connect closely with your lecturers and peers, building confidence through active learning and real collaboration. With flexible majors, minors, and electives, you can customise your degree to suit your passions — whether that's finance, tech, sustainability, or strategy.&lt;/p&gt;&lt;p&gt;Get industry-ready with hands-on experience. You could complete a work placement with leading firms, government agencies, or social enterprises. Many students have already made their mark with top-tier multinationals, regional firms, and international businesses — gaining skills, networks, and career clarity.&lt;/p&gt;&lt;p&gt;By graduation, you won't just understand accounting — you'll know how to use it to drive performance, solve problems, and lead with purpose.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Digital accounting systems&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand tech-driven processes, internal controls, and governance&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Accounting processes&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Record, report and analyse transactions using cloud-based tools&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Financial accounting&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Tackle complex reporting and evaluate real-world financial practices&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Management accounting&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Use data to plan, measure and optimise business performance&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Audit &amp;amp; forensic accounting&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore assurance services and fraud detection techniques&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Taxation&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how income tax impacts individuals and businesses, including Capital Gains Tax and Fringe Benefit Tax&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>069379F</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Bachelor of Psychological Science with Honours</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-psychological-science-with-honours</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>52</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Build on your successes in the Bachelor of Psychological Science by completing Honours to enhance essential employability skills or take your first step to a career in research, academia and beyond.&lt;/p&gt;&lt;p&gt;You'll gain a deeper understanding of research theory, design and practice principles introduced in your undergraduate degree. You'll study advanced theory in psychology and take part in a tailored psychology research methodology seminar. To apply your research knowledge and skills, you'll undertake an original research project under the supervision of expert staff from La Trobe's School of Psychology and Public Health to produce evidence-based solutions to current issues in psychology.&lt;/p&gt;&lt;p&gt;By graduating with Honours, you'll not only gain an edge in an increasingly competitive job market, you'll also have the opportunity to advance to further coursework or research at Master's level or, for high achievers, direct entry into a PhD.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>069561G</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>Bachelor of Pharmacy (Honours)</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-pharmacy-honours</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>208</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>200800</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>50200</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Take the first steps on your path to playing a vital role in your community and a successful career as a pharmacist with La Trobe's accredited Bachelor of Pharmacy (Honours).&lt;/p&gt;&lt;p&gt;Build your understanding of how medicines treat diseases and impact people's lives, and the importance of patient-centred and individualised care. Access our on-campus training pharmacy and get work-ready by participating in a range of community and hospital placements.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Pharmacy (Honours), you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;understand biochemistry, haematology and pharmacology and how systems of the body work, and how diseases and medicines affect these systems&lt;/li&gt;&lt;li&gt;learn counselling and communication techniques that equip you to deliver patient-centred care&lt;/li&gt;&lt;li&gt;explore the evolving use of digital technologies in healthcare and the technological, clinical, social, legal and ethical impacts of digital health&lt;/li&gt;&lt;li&gt;develop expertise in the practical applications of pharmaceutical care, including drugs used in respiratory and cardiovascular diseases, infections, endocrinology, psychiatry, oncology and palliative care&lt;/li&gt;&lt;li&gt;examine issues in public health, including rural and remote Australia and across Indigenous communities&lt;/li&gt;&lt;li&gt;graduate eligible to complete a one-year internship and take the Pharmacy Board of Australia exams to qualify as a professional pharmacist.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.5.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Scraped from data API (be/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>071896M</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>Master of Psychological Science</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-psychological-science</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>104</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>89200</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>071897K</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>Master of Science</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-science</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>104</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>89200</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>44600</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The Master's by research degree requires you to deepen your knowledge of your discipline area and develop advanced skills in the conduct of independent and sustained research. As a Master's by research candidate, you will undertake a supervised research project that culminates in the submission of a thesis for examination. Upon completion of your candidature you must demonstrate through your thesis that you have acquired an advanced and integrated understanding of a complex body of knowledge in one or more disciplines.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 – Masters Degree by Research.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t xml:space="preserve"> 071901G</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>Bachelor of Politics, Philosophy and Economics</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-politics-philosophy-and-economics</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>156</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>35800</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>35800</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Gain a multi-disciplinary perspective on the political and economic systems that shape our world with La Trobe's Bachelor of Politics, Philosophy and Economics.&lt;/p&gt;&lt;p&gt;Grasp the interconnections between three disciplines, equipping you with a distinctive and well-rounded combination of transferable skills that can be applied to a range of policy contexts, enhancing your employability in a range of sectors.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Bachelor of Politics, Philosophy and Economics, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;expand your understanding of politics and the evolution of governmental structures, discovering how different groups are impacted by current systems and learning how to pinpoint opportunities for innovative policy-making&lt;/li&gt;&lt;li&gt;engage with deep, foundational questions in philosophy, address challenging ethical puzzles and sharpen your critical thinking and reasoning, empowering you to reflect clearly on complex issues&lt;/li&gt;&lt;li&gt;gain insights into the economic forces that shape markets and influence decision-making, build crucial quantitative skills, and learn how to evaluate economic models so you can apply your knowledge to real-world scenarios&lt;/li&gt;&lt;li&gt;make a positive social impact in urgent issues such as inequality, climate change and human rights&lt;/li&gt;&lt;li&gt;apply your knowledge with a range of placement and networking opportunities at organisations like the Victorian Parliament, Trades Hall, the Grattan Institute and more.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>073116F</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>Master of Speech Pathology</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-speech-pathology</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>104</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>105200</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>52600</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Master of Speech Pathology gives you the knowledge and skills to help people realise their communication and swallowing potential. Learn how to observe communication and mealtimes in everyday settings, conduct assessments, interpret clinical data and develop interventions. You'll also gain hands-on experience working with a range of individual clients.&lt;/p&gt;&lt;p&gt;As you learn, you'll take part in clinical workshops, guided demonstration sessions and simulation activities. You'll also work with service providers to help people with communication and swallowing needs participate and feel included in their community.&lt;/p&gt;&lt;p&gt;Graduate ready to help people live their best lives.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Speech pathology practice&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the roles and functions of speech pathologists and how to optimise communication and swallowing in a variety of social and clinical contexts.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Assessment of communication and swallowing&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain theoretical and practical experience in conducting and interpreting speech pathology assessments.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Therapeutic intervention and management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover how to use assessment information, clinical experience and client observation to formulate intervention and management strategies in partnership with others.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Clinical management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop your clinical and workplace skills by undertaking placements in a range of community health, school, hospital and private practice settings.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;7.5 IELTS (Academic) with no individual band less than 7.0.&lt;/li&gt;&lt;li&gt;IELTS and TOEFL and are the only English Proficiency tests accepted for entry into this course.&lt;/li&gt;&lt;li&gt;Please refer to our Language requirements page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>075422B</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>Graduate Diploma in Business Administration</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-in-business-administration</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>52</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>49200</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>May, March, July, September, November</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Graduate Diploma in Business Administration will give you the edge your career needs.&lt;/p&gt;&lt;p&gt;Explore the issues facing global businesses and develop lifelong leadership skills. You'll tackle real-world business problems, learning from experienced academics and guest industry lecturers who'll explain the foundations of good corporate governance.&lt;/p&gt;&lt;p&gt;Looking for flexible learning options? This one-year course lets you fit your study around work and lifestyle commitments. You'll keep your career moving forwards, even while you prepare to step up to the next level.&lt;/p&gt;&lt;p&gt;You'll study subjects from La Trobe's prestigious &lt;a href="https://www.latrobe.edu.au/courses/master-of-business-administration"&gt;Master of Business Administration&lt;/a&gt; (MBA) – which is an accredited degree, co-designed by leading industry professionals.&lt;/p&gt;&lt;p&gt;Tackle the big issues shaping modern business and develop lifelong networks through our outstanding industry links and global alumni network.&lt;/p&gt;&lt;p&gt;This Graduate Diploma also provides a pathway to our MBA should you decide to further your studies.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Responsible leadership and corporate governance&lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;Understand how to manage people and operations, and achieve ethical and sustainable outcomes.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Financial management&lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;Understand financial management policy and application, and how financial management decision-making affects the risk, growth and profitability of firms.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Business analysis&lt;/strong&gt; &lt;br/&gt;&lt;ul&gt;&lt;li&gt;Explore how data can shape strategies and inform smarter decision-making.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Accounting &lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;Refine your skills in accounting and finance to better analyse business practices.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Offshore applicants are considered for admission based on the stated course entry requirements.&lt;/li&gt;&lt;li&gt;IELTS may be considered.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>075423A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Business Administration</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-business-administration</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>26</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>24600</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>May, March, July, September, November</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The La Trobe Graduate Certificate in Business Administration is an AI-first, fully online qualification from La Trobe University designed for professionals who want to develop contemporary management capability for an AI-driven economy. Delivered in flexible six-week study blocks, you can study from anywhere while building practical expertise in strategy, financial analysis, innovation and AI-enabled decision-making. The course provides a direct pathway into the La Trobe MBA.&lt;/p&gt;&lt;p&gt;You will complete four subjects from La Trobe University's online MBA curriculum, studying alongside MBA students and gaining exposure to postgraduate-level management learning.&lt;/p&gt;&lt;p&gt;Through subjects including Generative AI for Business, Navigating the AI Economy, Entrepreneurial Thinking and Innovation, and Strategy, you will learn how to apply generative AI and analytical frameworks to managerial decision-making, innovation and organisational performance. You will develop the ability to evaluate opportunities, design responsible innovation initiatives and formulate value-creating strategies in global, technology-driven markets.&lt;/p&gt;&lt;p&gt;The course emphasises evidence-informed managerial judgement, ethical and responsible leadership, and the integration of environmental, social and governance (ESG) considerations into business transformation. Fully credited into the La Trobe MBA, the qualification allows you to progress with advanced standing while building practical leadership capability for organisations adopting AI and advanced analytics.&lt;/p&gt;&lt;p&gt;Through a curriculum co-designed with global industry leaders and supported by La Trobe University's collaboration with OpenAI, you will develop human-centred leadership capability alongside AI-enabled business expertise.&lt;/p&gt;&lt;p&gt;By studying the Graduate Certificate of Business Administration, you'll learn how to:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;apply generative AI and analytical tools to interpret economic, financial and organisational information&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;use AI insights and evidence to support managerial decision-making in complex business environments&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;analyse opportunities and design strategic responses using structured frameworks, financial analysis and risk assessment&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;apply ethical, environmental, social and governance (ESG) and responsible AI principles in management decisions&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;communicate AI-informed strategies clearly to diverse organisational stakeholders.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Master of Art therapy</t>
+          <t>077479B</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>Master of Art Therapy</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/master-of-art-therapy</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>104</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>86000</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Prepare for a unique career combining art and counselling in clinical, therapeutic, or community settings with the only postgraduate specialist degree of its kind in Australia, La Trobe's accredited Master of Art Therapy.&lt;/p&gt;&lt;p&gt;Get the right mix of technical and people skills to meet both industry and client needs with evidence-based learning aligned with global benchmarks of art therapy practice. Learn from leading practitioners, academics, and researchers in immersive and interactive face-to-face workshops in our purpose-built art therapy studio. Benefit from our long-established industry partnerships and work-integrated learning opportunities with prestigious organisations like the Peter MacCallum Cancer Centre, Austin Health, and The Royal Children's Hospital.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By completing La Trobe's Master of Art Therapy, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;master a balance of theoretical and practical approaches, including a critical awareness of current issues in art therapy practice&lt;/li&gt;&lt;li&gt;gain expertise across clinical mental health, counselling, treatment planning, program design and evaluation, leadership, communication and cultural sensitivity&lt;/li&gt;&lt;li&gt;understand the different approaches to art therapy for adults, children and groups&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership with the Australian Counselling Association (ACA) and the Australian, New Zealand and Asian Creative Arts Therapies Association (ANZACATA).&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;7.5 IELTS (Academic) with no individual band less than 7.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>078469G</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>Bachelor of Civil Engineering (Honours)</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-civil-engineering-honours</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>208</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>172000</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Take the first step in your engineering career with La Trobe's Bachelor of Civil Engineering (Honours).&lt;/p&gt;&lt;p&gt;Become an expert as you build your knowledge in a wide range of engineering specialties. Understand the technical aspects of geotechnics and hydraulic systems. Develop strong foundations in structural and electrical engineering. And explore the countless possibilities of mechanical engineering.&lt;/p&gt;&lt;p&gt;You'll also develop a specialised skillset that's focused on creating sustainable, efficient and durable systems. Understand the importance of high-quality infrastructure design, civil construction and computer-aided design.&lt;/p&gt;&lt;p&gt;You'll learn from leading academics in small classes, giving you an invaluable intimate learning experience. As you progress, you'll have the opportunity to undertake research in sustainability, urban irrigation, and advances in concrete technologies.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sustainable infrastructure&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the fundamentals of the design and production of renewable energy systems.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Civil construction&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop your knowledge of design, and explore both practical and project management perspectives.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Water resources&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn about fluid dynamics, hydraulic systems, hydrological cycles, water quality, water management and water treatment.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Transport engineering&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Analyse and design multimodal transport facilities, road and pavement structures.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Computer-aided design&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Use computers and software to design, improve and assess projects.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 20 in one of Maths: General Mathematics, Mathematical Methods or Specialist Mathematics.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>079546B</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Business</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-business</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>26</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The Graduate Certificate in Business is a foundational postgraduate program designed for individuals seeking to develop essential business knowledge and skills. It is ideal for professionals aiming to broaden their understanding of core business disciplines or those considering a pathway into further postgraduate study, such as a Graduate Diploma in Business or Global Master of Business Administration.&lt;/p&gt;&lt;p&gt;This flexible and practical program introduces key areas including management, economics, accounting and finance, and artificial intelligence for business. It emphasises analytical thinking, problem-solving, and effective communication—skills that are highly valued across industries and sectors.&lt;/p&gt;&lt;p&gt;Whether you're looking to enhance your career prospects, transition into a new field, or gain a formal business qualification, the Graduate Certificate in Business offers a fast-track and focused option to achieve your goals.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Management and organisational behaviour&lt;ul&gt;&lt;li&gt;Understanding organisational behaviour in a global context, including team dynamics, conflict resolution, and motivation strategies&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;Financial management&lt;ul&gt;&lt;li&gt;Acquiring financial skills, including financial analysis, introductory accounting, and investment strategies.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;Artificial intelligence (AI) in business&lt;ul&gt;&lt;li&gt;Apply prompting techniques, build and evaluate AI chatbots, construct and articulate AI strategies.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;Economics&lt;ul&gt;&lt;li&gt;Apply economic concepts and frameworks to current issues of concern for organisations and society.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>080775A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>Master of Engineering Management</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-engineering-management</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>104</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>94400</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>47200</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Master of Engineering Management will develop your commercial acumen and help you set yourself apart. You'll undertake specialist subjects in management, innovation and sustainability – all designed for engineers. Back up your specialist skills with a strong foundation in business, so you can confidently address issues relating to marketing, finance, organisational behaviour, and the analysis of business data.&lt;/p&gt;&lt;p&gt;In your second year, you'll discover advanced subjects in risk and cost, project management, strategic management and computer-aided engineering. You'll also advance your knowledge in an engineering specialisation – choose from 12 disciplines.&lt;/p&gt;&lt;p&gt;Learn from experts in both engineering and management. Graduate ready to advance your career as a leader and manager in your field.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Advanced engineering management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop specialist skills in project management, innovation, risk and cost engineering, environmental sustainability, marketing, finance and more.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Business acumen&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to lead and develop organisations, teams and individuals, interpret and develop financial documents and take a strategic approach to management decisions.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Environmental sustainability practices&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand Australian industry best practices so you can lead engineers to create a more sustainable future.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Specialist engineering skills&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Get the latest knowledge with specialist electives from 12 engineering disciplines and take it back into your practice.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>080780D</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>Master of Clinical Audiology</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-clinical-audiology</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>104</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>102400</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>51200</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Whether you're building on your existing study in health or seeking specialised skills for the next stage of your career, La Trobe's Master of Clinical Audiology is your springboard to a rewarding career as an audiologist.&lt;/p&gt;&lt;p&gt;With class sizes that ensure you'll receive personal support, we'll equip you with knowledge and skills in advanced audiology. You'll develop a fundamental understanding of the nature of sound, as well as speech and auditory perception.&lt;/p&gt;&lt;p&gt;Your teachers will be leading academics and industry professionals with current knowledge of audiology best practice. They'll guide you through pre-clinical and clinical study so you understand the practical aspects of audiology.&lt;/p&gt;&lt;p&gt;What's more, you'll undertake extensive professional clinical placements with local and interstate clinical placement partners – so you build the confidence to practice upon graduation.&lt;/p&gt;&lt;p&gt;Be ready to change lives. Start building the skills now to make a difference well into the future.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Diagnostics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the foundational clinical assessment procedures used in the audiological evaluation of adult and child patients, including otoscopy, tympanometry, audiometry, otoacoustic emissions and electrophysiological assessments.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Acoustics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand the nature of sound (acoustics) and auditory perception (psychoacoustics), then apply your knowledge to practical areas of audiology.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Hearing loss and rehabilitation&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to select an appropriate hearing aid and/or assistive listening device. Understand the impact of hearing loss and how to manage and rehabilitate complex clients, and explore hearing loss prevention.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Paediatric audiology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn about causes of hearing loss in children, auditory processing disorders and the impact of childhood hearing impairment.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/li&gt;&lt;li&gt;Please refer to our Language requirements page for details of other accepted English proficiency tests and additional recognised English language proficiency measures, such as English as the language of instruction.&lt;/li&gt;&lt;li&gt;IELTS, TOEFL and PTE are the only English Proficiency tests accepted for entry into this course.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>084537E</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>Bachelor of Commerce/Bachelor of Arts</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-commerce-bachelor-of-arts</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>208</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Gain a comprehensive understanding of commercial and policy areas, combined with the essential human skills of an arts degree, with La Trobe's Bachelor of Commerce/Bachelor of Arts.&lt;/p&gt;&lt;p&gt;Co-designed with industry leaders, our double degree gives you a multidisciplinary set of skills and knowledge, sought-after by employers and policymakers. You'll learn to take advantage of the synergies between the two disciplines and successfully solve complex problems by merging technical skills and strategic analysis with experimentation and instinctive imaginative thinking.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Commerce/Bachelor of Arts, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;learn how to identify practical solutions to real-world challenges, improve your ability to negotiate with stakeholders and communicate your solutions&lt;/li&gt;&lt;li&gt;prepare to become an effective leader who can meet the challenges of automation, AI-driven technologies and big data&lt;/li&gt;&lt;li&gt;make your degree your own by choosing from hundreds of majors and minors in commerce, arts and other disciplines, including business analytics, finance, marketing, psychology, international studies and languages&lt;/li&gt;&lt;li&gt;gain real-world experience through industry placements, work-integrated learning projects and overseas student exchange opportunities.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>084539C</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>Bachelor of Commerce</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-commerce</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>156</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>135000</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Become a leader in the rapidly evolving commercial world with La Trobe's Bachelor of Commerce.&lt;/p&gt;&lt;p&gt;Designed for ambitious and future-focused students, this degree gives you a powerful mix of skills and knowledge that employers are actively looking for. Learn the latest in commercial technologies such as automation, AI and big data, then apply it in the real world through industry placements, work-integrated learning projects and overseas student exchange opportunities. You'll graduate with a work-ready portfolio that showcases your skills and helps you stand out to employers.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By completing La Trobe's Bachelor of Commerce, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Choose from six majors: accounting, business analytics, economics, finance, management, and marketing – and you have the opportunity to combine your commerce major with an additional 2nd business major or business minor(s).&lt;/li&gt;&lt;li&gt;Enhance your employability with the option to add a double degree in law, arts, health sciences, computer science, science or psychological science.&lt;/li&gt;&lt;li&gt;Depending on your major, graduate ready to apply for membership to a range of professional business associations.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>085379F</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>Bachelor of Commerce/Bachelor of Science</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-commerce-bachelor-of-science</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>208</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Explore how the world of science interacts with the commercial sphere and how to build business structures that power scientific innovation with La Trobe's Bachelor of Commerce/Bachelor of Science.&lt;/p&gt;&lt;p&gt;Co-designed with industry leaders, our double degree gives you a multidisciplinary set of skills and knowledge sought after by employers and policymakers – from learning how to successfully manage research and development projects to commercialising intellectual property from a scientific breakthrough.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Commerce/Bachelor of Science, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop critical capabilities in independent research, innovative thinking, cultural intelligence, oral and written communication, teamwork and leadership&lt;/li&gt;&lt;li&gt;study alongside researchers at our Centre for AgriBioscience and La Trobe Business School, and benefit from facilities like the La Trobe Institute for Molecular Science and finance trading room&lt;/li&gt;&lt;li&gt;choose from five majors in commerce – including business analytics, finance and marketing – and sixteen majors across a wide range of scientific interest areas – including artificial intelligence, chemistry, ecology, genetics and physics.&lt;/li&gt;&lt;li&gt;gain real-world experience through industry placements, work-integrated learning projects and overseas exchange opportunities.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Units 3 and 4: a study score of at least 20 in any Mathematics.&lt;/li&gt;&lt;li&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>086278C</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>Bachelor of Media and Communication</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-media-and-communication</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>156</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>115800</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>38600</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Tell stories across any medium and graduate with a portfolio of work, industry experience and specialised media knowledge with La Trobe's Bachelor of Media and Communication.&lt;/p&gt;&lt;p&gt;Become a specialist with your first major in creative and professional writing, journalism, sports media or marketing, then tailor your degree with a choice from hundreds of second majors, minors or electives across La Trobe's diverse disciplines. Get hands-on production and broadcast experience in our purpose-built, industry-grade Upstart newsroom – including a three-camera television studio, professional radio broadcast spaces, a dedicated audio recording studio and digital editing suites – or via work-based learning with our prestigious industry partners.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Media and Communication, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop foundational skills in digital media, storytelling, communication and critical thinking&lt;/li&gt;&lt;li&gt;master the tools and channels used to research, create, distribute and promote content to different audiences&lt;/li&gt;&lt;li&gt;experience the adrenaline of live broadcasting as a presenter, producer and technician, all under the mentorship of our experienced teachers&lt;/li&gt;&lt;li&gt;look behind the headlines and investigate the social, ethical, legal and technological questions that confront producers every day&lt;/li&gt;&lt;li&gt;graduate with your first major on your academic transcript, so future employers can recognise your expertise.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>087774A</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>Master of Business Analytics</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-business-analytics</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>104</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>87600</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;In the Age of Artificial Intelligence (AI), knowledge and skills in organisational data, analytics techniques and AI capabilities are foundational for driving business success, economic growth and development. Codesigned with leading industry experts, the Master of Business Analytics is a specialised postgraduate degree that equips you with the technical, analytical, and business skills necessary to build solutions that address the complexity of data and information in modern businesses.&lt;/p&gt;&lt;p&gt;In this course, disciplinary knowledge in data, analytics and AI are aligned with industry leading tools and technologies to provide a hands-on learning experience of practical skills for solving real-world business problems. The teaching team draw on their own industry and research expertise in building AI and analytics solutions to deliver a future-focused learning experience. They teach in small, interactive classes and use Gen AI teaching tools to ensure the student learning journey is personalised and fully supported.&lt;/p&gt;&lt;p&gt;Build and grow your analytics and AI capabilities through industry placements and business case studies that foster critical thinking, ethical reasoning, strategic communication and leadership. Become a well-balanced technology professional with data, analytics, and AI capabilities that are highly sought after by AI-first organisations of the future.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You will learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Data Analytics: &lt;/strong&gt;professional knowledge and skills to build and use analytics dashboards, predictive models, cloud applications for real-world business problems&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Artificial Intelligence: &lt;/strong&gt;industry-ready skillset in AI to drive productivity, innovation and decision-making across the business ecosystem&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Business Innovation:&lt;/strong&gt; AI, analytics and data-driven innovations in business settings to create value, solve problems, and improve performance&lt;/li&gt;&lt;li&gt;&lt;strong&gt;ICT Ethics and Cybersecurity:&lt;/strong&gt; knowledge of local and international regulatory frameworks and guidelines for addressing enterprise ethics and cybersecurity challenges&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Professional ICT Practice: &lt;/strong&gt;power skills essential for collaboration and teamwork in modern workplaces, including communication, critical thinking, emotional intelligence, and adaptability.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>089313C</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>Bachelor of Oral Health Science</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-oral-health-science</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>156</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>144600</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>48200</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Learn how to provide essential oral healthcare with La Trobe's accredited Bachelor of Oral Health Science. Studying in an inter- and intradisciplinary setting, you'll develop your professional practice at Australia's largest rural health school.&lt;/p&gt;&lt;p&gt;Develop your understanding of oral health promotion, and the prevention and treatment of oral diseases. Get hands-on experience in clinical placements across regional Victoria and treat patients under the supervision of experienced clinicians. Your scope of practice includes dental therapy treatments to patients of all ages.&lt;/p&gt;&lt;p&gt;Note: You'll need to complete your Level 1 First Aid/CPR certification, get your required vaccinations, and provide a current police check and Working with Children Check before starting this degree.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Preventive oral health&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop your knowledge of preventive, periodontal and restorative procedures.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Medicine for dentistry&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn to take a comprehensive medical history, understand its role in safe oral healthcare, and the link between oral and general health.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Clinical practice&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover how to diagnose and plan care for patients. Improve your communication and treatment skills while learning to manage patients in a clinical setting.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Global perspectives in oral health&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain insight into different cultures and explore your role as an oral health therapist in a multicultural society. Further develop your cultural competence through an elective rural, interstate or overseas placement.*&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;*Subject to government restrictions on international travel.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Scraped from data API (be/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>089314B</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>Bachelor of Criminology</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-criminology</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>156</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>118800</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>39600</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Create innovative solutions to social issues and build a safer community with La Trobe's Bachelor of Criminology.&lt;/p&gt;&lt;p&gt;Understand crime in its broader social context and how our responses are shaped by gender, race, power and money. Address real-world problems while gaining a deeper understanding of issues such as family violence, international crime, youth justice, imprisonment and deaths in custody.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By studying La Trobe's Bachelor of Criminology, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;investigate the complex causes of crime, principles of crime prevention and policy, and how social factors intersect with our criminal justice system&lt;/li&gt;&lt;li&gt;explore the role of courts, police, prisons and how deviance and crime are understood by different parts of society&lt;/li&gt;&lt;li&gt;learn how to critically analyse the Australian legal system in its historical, ethical, economic and social context&lt;/li&gt;&lt;li&gt;understand international crimes like genocide and crimes against humanity, and how they differ from domestic crimes&lt;/li&gt;&lt;li&gt;enhance your graduate job potential by undertaking electives in case management or an industry internship, including on-the-job opportunities at organisations like the Victims of Crime Tribunal&lt;/li&gt;&lt;li&gt;have the flexibility to study online, on campus or a mix of both&lt;/li&gt;&lt;li&gt;build the foundations to transfer with credit into our Bachelor of Laws (Honours) or our range of double law degrees.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>091417K</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>Master of Biotechnology Management</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-biotechnology-management</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>104</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>90800</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>45400</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Our Master of Biotechnology Management helps you build a unique skillset for the future by combining biotechnology and business management expertise. Work in state-of-the-art facilities, then graduate with the skills and experience to launch your global career.&lt;/p&gt;&lt;p&gt;In your first year, you'll learn the fundamentals of management and marketing, exploring real-life examples in a diverse range of organisational contexts. From there, you'll explore the area of bio-business management and discover how to produce and market a virtual product.&lt;/p&gt;&lt;p&gt;You'll be taught by leading industry experts as you examine areas such as molecular modelling software, proteomics and genomics. Gain theoretical knowledge in a range of advanced scientific technologies, including CRISPR-mediated gene editing, next generation sequencing and mass spectrometry. You'll also harness bioinformatics software programs to address biological problems.&lt;/p&gt;&lt;p&gt;As you learn, you'll develop valuable scientific communication and research skills, including data representation, use of scientific journals, scientific databases, writing literature reviews and presenting. You'll also build your communication, team working, problem solving and analytical skills, which experts suggest will be highly sought after by the workplaces of tomorrow.*&lt;/p&gt;&lt;p&gt;Your studies will take place in the heart of the La Trobe Institute for Molecular Sciences (LIMS). Access world-class research facilities and laboratories devoted to biotech, biomedicine and biosecurity.&lt;/p&gt;&lt;p&gt;Graduate ready to lead the way in vital areas such as human health, diagnostics, environmental sustainability, food security and renewable energy.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Bioinformatics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Apply technical skills to collect, store and analyse complex biological data, including genome and protein sequence information.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Principles of economics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore a variety of economic concepts and how they can be applied in real-world business and policy-making.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Bio-business management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Examine organisational structure, intellectual property, scientific reasoning, market research and ethics.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Sustainable management and marketing&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand how the need for sustainable value creation in contemporary organisations influences management and marketing behaviour.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;*Forbes, 2019, &lt;a href="https://www.forbes.com/sites/bernardmarr/2019/04/29/the-10-vital-skills-you-will-need-for-the-future-of-work/#20a8c5df3f5b"&gt;The 10 Vital Skills You Will Need For The Future Of Work &lt;/a&gt;; PwC, 2020, &lt;a href="https://www.pwc.com.au/careers/blog/future-employment.html"&gt;10 skills you need for future employment&lt;/a&gt;&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>091422B</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>Graduate Certificate of Archaeology</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-of-archaeology</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>26</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>20100</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>20100</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Graduate Certificate of Archaeology is the perfect place to build your career in archaeology and heritage management. You'll be equipped with specialist skills in contemporary archaeological practice and learn from renowned researchers in La Trobe's world-class facilities.&lt;/p&gt;&lt;p&gt;You'll acquire comprehensive knowledge of Australian and Australian Indigenous archaeology and get hands-on experience as you choose from a wide range of specialised subjects.&lt;/p&gt;&lt;p&gt;Upon successful completion of the Graduate Certificate of Archaeology, you may be eligible for advanced standing for four subjects in the Graduate Diploma or Master of Archaeology, should you choose to continue with your studies.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Indigenous and historic archaeology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Delve into Indigenous Australian and historic archaeology. Examine past practice and contemporary advances and findings.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cultural heritage management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn to navigate and guide others in the ethical and regulatory requirements of managing sites and objects of cultural importance.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Archaeological field methods&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build the practical skills and knowledge you need to conduct archaeological fieldwork in Australia and overseas.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>092396B</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>Master of Data Science</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-data-science</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>104</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>87600</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Data science professionals are in high demand in today's data-driven world. Whether you're already working in data science, or you're ready to make a career change, our Master of Data Science prepares you for a successful career in this exciting field.&lt;/p&gt;&lt;p&gt;Designed in collaboration with our industry partners, this degree gives you the knowledge, skills and hands-on experience to transition from university to the workplace. And with two early exit points along the way, you can be sure that every subject is contributing to your career.&lt;/p&gt;&lt;p&gt;You'll build fundamental skills in programming, databases, probability, statistics, data exploration and analysis. Got a particular interest in artificial intelligence, bioinformatics or sport analytics? This degree allows you to specialise in these areas and others, such as big data and cloud computing, business applications and data modelling and analytics.&lt;/p&gt;&lt;p&gt;As you study, you'll have opportunities to work with our industry partners on real-world projects and take on an industry work placement. If your sights are set on a research career, you can choose to undertake a thesis in computer science or statistics.&lt;/p&gt;&lt;p&gt;Every step of the way, our supportive and highly qualified teaching staff will be there to offer ongoing support and advice.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Data science&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Get practical experience with open-source software and platforms, including Python, R and Hadoop.&lt;/li&gt;&lt;li&gt;Understand database fundamentals, programming languages such as Java and Python, and cloud-based services offered by Amazon, Google, IBM and Microsoft.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Mathematics and statistics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to create complex models and use powerful tools for advanced analysis and problem-solving.&lt;/li&gt;&lt;li&gt;Build your skills using real data sets from our industry partners and learn how to solve data challenges facing businesses and organisations.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Project management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to manage large-scale IT projects and work in a team to develop a small-scale, industry-based system.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Complementary skills in other disciplines&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Boost your knowledge through electives in business, health sciences, artificial intelligence and cybersecurity.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>092917D</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>Bachelor of Commerce/Bachelor of Computer Science</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-commerce-bachelor-of-computer-science</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>208</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Take advantage of the interconnected worlds of commerce and technology through La Trobe's Bachelor of Commerce/Bachelor of Computer Science.&lt;/p&gt;&lt;p&gt;Co-designed with industry leaders, our Bachelor of Commerce/Bachelor of Computer Science gives you a a multidisciplinary set of skills and knowledge sought-after by employers and policymakers. You'll develop a comprehensive understanding of the principles underpinning the tech market, as well as the scientific principles behind computer hardware and software.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Commerce/Bachelor of Computer Science, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;learn how to identify practical solutions to real-world challenges, improve your ability to negotiate with stakeholders and communicate your solutions&lt;/li&gt;&lt;li&gt;explore topics such as programming, mathematics, statistics and data analytics&lt;/li&gt;&lt;li&gt;prepare to become an effective leader who can meet the challenges of automation, AI-driven technologies and big data&lt;/li&gt;&lt;li&gt;build critical skills in independent research, innovative thinking, cultural intelligence, oral and written communication, teamwork and leadership&lt;/li&gt;&lt;li&gt;gain real-world experience through industry placements, work-integrated learning projects and overseas student exchange opportunities&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership into the Australian Computer Society (ACS) and, depending on your choice of majors, a range of business professional associations.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 20 in any Mathematics &lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>093259C</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>Bachelor of Commerce/Bachelor of Health Sciences</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-commerce-bachelor-of-health-sciences</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>208</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Develop valuable skills in business and health while remaining grounded in an entrepreneurial core with La Trobe's Bachelor of Commerce/Bachelor of Health Sciences.&lt;/p&gt;&lt;p&gt;Co-designed with industry leaders, our double degree prepares you to solve key healthcare, business and economic challenges in a responsible and sustainable manner. You'll understand how to independently research, think innovatively and use digital technologies to effectively identify and execute managerial and policy solutions.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Commerce/Bachelor of Health Sciences, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;analyse the complex challenges confronting business and society, as well as emerging developments in the field of health sciences&lt;/li&gt;&lt;li&gt;develop cultural intelligence, leadership skills, stakeholder negotiation and communication skills that help you to thrive in any work environment&lt;/li&gt;&lt;li&gt;be ready to meet the challenges of automation, AI-driven technologies and big data&lt;/li&gt;&lt;li&gt;choose from a range of majors and minors to build a unique set of multidisciplinary skills&lt;/li&gt;&lt;li&gt;gain real-world experience through industry placements, work-integrated learning projects and overseas exchange opportunities&lt;/li&gt;&lt;li&gt;depending on your choice of majors, graduate ready to apply for membership into a range of business professional associations.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>093383K</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>Master of Marketing</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-marketing</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>104</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>94400</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bachelor of Education (Secondary)</t>
+          <t>110999K</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
+          <t>Bachelor of Education</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-education</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>208</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>147200</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>36800</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Get the skills, experience and confidence you need to make a real impact as a qualified teacher from your first day with La Trobe's accredited Bachelor of Education.&lt;/p&gt;&lt;p&gt;Offered at every campus in Victoria, our flexible degree lets you explore your options before deciding what you'll teach – early childhood and primary, primary, or secondary – at the end of your first year. You'll learn how to manage classrooms, design class plans and guide students by spending at least 80 days in schools and education centres across metropolitan, regional and rural Victoria.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By studying La Trobe's Bachelor of Education, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;build your skillset in digital learning, learning contexts, literacy and numeracy, student development and classroom readiness&lt;/li&gt;&lt;li&gt;learn how to design learning environments that meets the needs of a wide range of students inclusive of race, gender, ethnicity, socioeconomic and Indigenous status&lt;/li&gt;&lt;li&gt;explore the most up-to-date and proven approaches to teaching, then put it into practice with placements embedded into the degree&lt;/li&gt;&lt;li&gt;benefit from a supportive learning environment where you'll be mentored by teaching staff and learn from leading researchers who are changing the way people learn to read&lt;/li&gt;&lt;li&gt;graduate with an accredited degree and the in-demand skills you need to launch your teaching career.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt;&lt;p&gt;Units 1 and 2: satisfactory completion in one of Maths: General Mathematics, Maths: Mathematical Methods or Maths: Specialist Mathematics or Units 3 and 4: any Mathematics&lt;/p&gt; English Language Requirements&lt;p&gt;7.0 IELTS (Academic) with no individual band less than 7.0 and a score of no less than 7.5 in Speaking and Listening.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>094173A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>Graduate Diploma in Sport Analytics</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-in-sport-analytics</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>52</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>42200</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>42200</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Graduate Diploma in Sport Analytics is a formal qualification with hands-on experience with real sport datasets, and in-demand technical training in programming, databases, machine learning, and statistical analysis— all delivered flexibly with a mix of online and on-campus study suited to working professionals.&lt;/p&gt;&lt;p&gt;Learn how to use data to boost athlete performance and wellbeing. You'll get hands-on experience with industry-standard technologies and cutting-edge sport analytics technology like Catapult GPS and LPS, Hudl SportsCode and IMeasureU (Inertial measurement units).&lt;/p&gt;&lt;p&gt;The course aims to prepare you for roles in the field of sport analytics or for currently employed sport and exercise professionals looking to advance into higher roles through a formal education and qualification in sports analytics. You'll graduate with a direct pathway into the Master of Sport Analytics or ready to use your new data analytics skills in the sport industry you're passionate about.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Graduate Diploma in Sport Analytics, you'll learn:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;Sport analytics in practice&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;Learn about contemporary technology applications, and apply theoretical understanding of analytics processes and methodologies to authentic sport-related data sets.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;Advanced analytics&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;Develop enhanced skills in data warehousing, and analytical skills including coding (R and Python), machine learning and statistical modelling.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;Analytical methods in sport&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;Learn how to perform various data handling techniques, statistical tests and explore data visualisation techniques within a sport and exercise science context.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;p&gt;Database management&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;Gain an overview of the architecture and management of database systems and explore programming foundations to design and create software solution.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Bachelor of Biomedicine (Honours)</t>
+          <t>114827J</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
+          <t>Bachelor of Biomedicine</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-biomedicine</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>156</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>137400</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>45800</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Get the technical and applied expertise you need to establish your biomedical career with La Trobe's Bachelor of Biomedicine.&lt;/p&gt;&lt;p&gt;Start with how the body works as you build fundamental knowledge in chemistry, bioscience and health. Take a close look at infectious diseases, including the factors that drive epidemics and pandemics. Then tailor your degree with a combination of up to two majors or electives aligned to your personal career goals and industry demand.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By completing La Trobe's Bachelor of Biomedicine, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop strong foundational knowledge in topics such as biochemistry, molecular and cell biology, human physiology, infectious and non-communicable disease&lt;/li&gt;&lt;li&gt;choose from majors in cancer, heart and brain diseases; immunology and infectious disease; physiology and pharmacology; or molecular and cellular biochemistry&lt;/li&gt;&lt;li&gt;gain hands-on experience from day one with lab work, internship opportunities, overseas exchange opportunities and more&lt;/li&gt;&lt;li&gt;be prepared for your future career at every stage of the course, with the flexibility to exit early with a Diploma after one year or an Associate Degree after two years&lt;/li&gt;&lt;li&gt;graduate with your majors on your academic transcript and a pathway to specialist postgraduate studies in research, medicine, physiotherapy and more.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>095558J</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>Bachelor of Sport and Exercise Science</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-sport-and-exercise-science</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>156</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>130800</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Help people reach peak performance with La Trobe's Bachelor of Sport and Exercise Science.&lt;/p&gt;&lt;p&gt;You'll gain a detailed understanding of the science behind training, explore the strengths and limitations of the human body, and build strong foundations in physiology, anatomy and biomechanics. You'll use data and scientific principles and techniques to help people build strength, regain movement, prevent injuries and perform at their peak.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Sports and Exercise Science, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;choose from our recommended majors – human performance, nutrition science and sport and recreation development in Melbourne or food and nutrition,* health promotion and rural health in Bendigo – or tailor your degree with open access majors from a range of disciplines&lt;/li&gt;&lt;li&gt;get out of the classroom and on to the field with practical learning and access to our elite athlete performance spaces&lt;/li&gt;&lt;li&gt;build real-world experience and connections with 150 placement hours with organisations like Carlton Football Club, Rugby Victoria and Bendigo Spirit&lt;/li&gt;&lt;li&gt;join a university of choice for studying and playing sport in Australia – alongside our community delivery partners and major partnerships, we're proudly the official home of the CommBank Matildas&lt;/li&gt;&lt;li&gt;graduate ready to launch your career or pursue postgraduate study in areas such as sport analytics, strength and conditioning, and other allied health disciplines.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;*The food and nutrition major is offered online only.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 20 in one of Health And Human Development, Physical Education, any Mathematics (General mathematics, Mathematical Methods, Specialist Mathematics, Further Mathematics), or in one of Biology, Chemistry, Physics, Psychology.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>095691D</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>Bachelor of Paramedic Practice with Honours</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-paramedic-practice-with-honours</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>208</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>167200</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>41800</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Bachelor of Paramedic Practice with Honours gives you the knowledge and skills to launch a career in this important field of health. You'll develop a strong foundation in biosciences and paramedic practice for trauma, respiratory, cardiac, paediatric and obstetric management.&lt;br/&gt;&lt;br/&gt;Kickstart your career with first-hand paramedic experience. Build the experience and resilience to tackle this exciting career with work-based learning opportunities in hospitals, community settings and with Ambulance Victoria. You can also practice in the Paramedicine Practical Laboratory equipped with industry-standard medical equipment and an outdoor emergency simulation space.&lt;br/&gt;&lt;br/&gt;As a graduate, you will be ready to apply your practical skills when you're needed most. The course also offers a research honours pathway, which can facilitate direct entry into postgraduate studies. &lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Human biosciences&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the fundamentals of anatomy while exploring the nervous, endocrine, and other major organ systems of the body.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Communication skills in healthcare&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain an understanding of counselling and communication skills and how they are applied in a range of healthcare settings.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Trauma, cardiac and paediatric management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover the pathophysiology of specific trauma conditions and the assessment and management procedures you will need to treat patients presenting with these conditions.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Pharmacology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the key role drugs play in the treatment and prevention of diseases, including drug classification, administration, and basic pharmacokinetics.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 20 in two of Biology, Chemistry, Health And Human Development, any Mathematics, Physical Education, Physics or Psychology.&lt;/p&gt; English Language Requirements&lt;p&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Scraped from data API (be/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>096350F</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>Bachelor of Criminology/Bachelor of Psychological Science</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-criminology-bachelor-of-psychological-science</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>208</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>168000</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Explore the close connections between crime and the human mind and its effects on behaviour with La Trobe's multidisciplinary Bachelor of Criminology/Bachelor of Psychological Science.&lt;/p&gt;&lt;p&gt;Understand crime in its broader social context and how individual and social responses are shaped by gender, race, power and money. Establish a grounding in psychology, exploring theories on individuals, groups and whole societies. Learn how experiences and incentives impact behaviour and how this knowledge can be applied to key issues in criminal justice.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Criminology/Bachelor of Psychological Science, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;investigate the complex causes of crime, principles of crime prevention and policy, and how social factors intersect with our criminal justice system&lt;/li&gt;&lt;li&gt;explore the role of courts, police, prisons and how deviance and crime are understood by different parts of society&lt;/li&gt;&lt;li&gt;develop valuable expertise in cognitive, developmental, social, abnormal, clinical and health psychology&lt;/li&gt;&lt;li&gt;get on-the-job experience with work placement opportunities at organisations like the Victims of Crime Tribunal&lt;/li&gt;&lt;li&gt;have the flexibility to study online, on campus or a mix of both&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership of the Australian Psychological Society (APS) and the prerequisites to apply for Honours in psychology, with potential to pursue postgraduate study and registration as a psychologist.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>096351E</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>Bachelor of Cybersecurity</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-cybersecurity</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>156</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>126000</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Bachelor of Cybersecurity offers you the opportunity to step into the rapidly evolving digital world of cybersecurity.&lt;/p&gt;&lt;p&gt;You'll build a highly specialised technical skillset as you learn about the history of hacking, build your coding expertise, and access industry-based projects and mentoring opportunities with major corporations.&lt;/p&gt;&lt;p&gt;You'll also have the opportunity to complement your industry-focused learning with a choice of advanced electives in IT, business, law, policy and strategic communication.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Cybersecurity fundamentals&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the basic principles and best practices of cybersecurity. Understand how it mitigates cyber vulnerabilities and protects confidential information.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ethical hacking and defence&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain evaluation techniques to assess the security of network configuration and apply these skills to defend against network-based threats.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Programming and cyber algorithms&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the widely used Python programming language and learn how algorithms are used to solve cybersecurity challenges.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Network engineering&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Study the architecture of computer networks and the internet, and examine protocols and services used in the defence of online information.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cyber governance and risk management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the frameworks for cybersecurity governance and risk mitigation based on your emerging understanding of business strategy and risk appetite.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>096858M</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>Bachelor of Cybersecurity/Bachelor of Psychological Science</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-cybersecurity-bachelor-of-psychological-science</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>208</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>168000</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;In La Trobe's Bachelor of Cybersecurity/Bachelor of Psychological Science, you'll build a career at the nexus of two rapidly evolving sciences and learn how to combat the constantly evolving threat of cybercrime.&lt;/p&gt;&lt;p&gt;In this distinctive combination of study areas, you can pursue a career as a professional psychologist (after further postgraduate study) or build a career within the growing field of cybersecurity.&lt;/p&gt;&lt;p&gt;Learn from experts in world-class facilities, including our Cyber Security Research Hub - one of the largest cybersecurity research hubs in Victoria. &lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Cybersecurity fundamentals&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the basic principles and best practices of cybersecurity.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Psychological science&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the clinical foundations of psychological science, including psychological conditions and treatments for mental illness.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Programming and cyber algorithms&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Become an expert in Python and learn how algorithms are used to solve cybersecurity challenges.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Psychological research methods&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the research methods used in contemporary psychological investigations.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Human factors in cybersecurity&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand human behaviour and explore the psychology of hackers, victims and defenders.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Ethical hacking and defence&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to assess security risks and defend against network-based threats.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>099396A</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>Bachelor of Commerce/Bachelor of Psychological Science</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-commerce-bachelor-of-psychological-science</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>208</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Learn how to innovate and shape behaviour with La Trobe's accredited Bachelor of Commerce/Bachelor of Psychological Science.&lt;/p&gt;&lt;p&gt;Co-designed with industry leaders, our double degree gives you commercial knowledge and skills, as well as a deep understanding of the human mind. Understand what drives human choices and how businesses can meet consumer needs. Establish a grounding in psychology, exploring theories on individuals, groups and whole societies. Learn how experiences and incentives impact individual and group behaviour and how this knowledge can be applied in business.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Commerce/Bachelor of Psychological Science, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;explore our commercial environment and learn how to create better systems and solutions for people and the planet&lt;/li&gt;&lt;li&gt;develop critical skills in independent research, innovative thinking, cultural intelligence, oral and written communication, and teamwork&lt;/li&gt;&lt;li&gt;learn how to identify practical solutions to real-world challenges, improve your ability to negotiate with stakeholders and communicate your solutions&lt;/li&gt;&lt;li&gt;gain real-world experience through industry placements, work-integrated learning projects and overseas student exchange opportunities&lt;/li&gt;&lt;li&gt;graduate with the prerequisites to apply for Honours in psychology, with the potential to pursue postgraduate study and registration as a psychologist.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>102426C</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Digital Health</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-digital-health</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>26</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>20700</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>20700</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>May, March, July, September, November</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Gain an in-demand skill set to design, implement and manage digital health solutions that meet the evolving healthcare needs of individuals and communities with La Trobe's Graduate Certificate in Digital Health.&lt;/p&gt;&lt;p&gt;Advance your knowledge in new and emerging areas of digital health, including health analytics, virtual care, the Internet of Medical Things (IoMT), websites, apps and social media. Explore these technologies and their applications by examining benefits, risks and their ethical and legal implications.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Graduate Certificate in Digital Health, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;embrace a design-thinking mindset, using data-driven, human-centered and experience-based approaches to solutions&lt;/li&gt;&lt;li&gt;gain an understanding of big data health analytics and explore how it can be applied to real-world applications&lt;/li&gt;&lt;li&gt;understand how virtual care can provide accessible, equitable and effective healthcare &lt;/li&gt;&lt;li&gt;discover powerful tools to effectively communicate health information to different audiences in the digital age, including healthcare professionals, government bodies, IT vendors, and patients &lt;/li&gt;&lt;li&gt;assess organisational preparedness for digital transformation and know how to develop strategies for successful implementation of evidence-based digital health programs&lt;/li&gt;&lt;li&gt;have the opportunity to apply for 60 credit points of advanced standing for our Master of Digital Health.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>102578J</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Information Technology Fundamentals</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-information-technology-fundamentals</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>26</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>21900</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>May, March, July, September</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Providing a pathway into a range of postgraduate IT degrees, La Trobe's Graduate Certificate in Information Technology Fundamentals is your first step to a successful career in IT.&lt;/p&gt;&lt;p&gt;With technology taking a front-and-centre role in modern business, IT professionals are in high demand. Industries from media and government to health and education are scrambling to recruit specialists in computing, diagnosis, service and maintenance.&lt;/p&gt;&lt;p&gt;Whether you're working in IT already and want to deepen your knowledge, or you're new to IT and want to break into this fast-growing industry, La Trobe's Graduate Certificate in Information Technology Fundamentals gives you a strong foundation you can use to launch the rest of your career.&lt;/p&gt;&lt;p&gt;Not sure exactly how to secure your dream job? No need to worry – our supportive academic staff will work with you to understand your career goals and help you make them happen.&lt;/p&gt;&lt;p&gt;Delivered in just six months full-time, this course provides you with a solid foundation in IT fundamentals, programming and statistics – highly transferable skills you can apply in a wide range of industries.&lt;/p&gt;&lt;p&gt;From there, you'll be ready to apply for one of our IT Master's degrees, choosing from specialist qualifications in artificial intelligence, cybersecurity, data science, digital media, information technology or the Internet of Things&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Programming 101&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand how to design and create software solutions using Python. Learn how to tackle practical problems using real-life scenarios.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Information technology fundamentals&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build foundational skills in computer operation, hardware components, data storage and retrieval, system software, operating systems, file management systems, security and more.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Database basics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the architecture and management of different database systems and models. Design and implement your own commercial standard database system to meet specifications.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Offshore applicants are considered for admission based on the stated course entry requirements.&lt;/li&gt;&lt;li&gt;IELTS may be considered.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bachelor of Wildlife and Conservation Biology</t>
+          <t>103743D</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
+          <t xml:space="preserve">Bachelor of Wildlife and Conservation Biology </t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-wildlife-and-conservation-biology</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>156</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>132000</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>44000</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're passionate about the environment and want the skills and knowledge to make a difference, this could be the degree for you.&lt;/p&gt;&lt;p&gt;La Trobe's Bachelor of Wildlife and Conservation Biology draws on many areas of science including botany, genetics and zoology. You'll learn to apply ecological concepts to the conservation of species and ecosystems and explore the legal framework for conservation.&lt;/p&gt;&lt;p&gt;Your curriculum will cover biology fundamentals – including how organisms, the environment and human populations interact with each other – as well as climate change and sustainability. As you progress in your studies, you'll advance your understanding of conservation issues, learn to use different technologies to collect and process data, and design your own detailed conservation management plan. You'll be taught by La Trobe experts involved in conservation projects, and who work with partners in state and federal government departments and non-government organisations such as Bush Heritage and Trust for Nature. &lt;/p&gt;&lt;p&gt;To truly understand wildlife and real-world conservation, you need to experience it first-hand. Throughout your degree you'll spend plenty of time immersed in the environment – previous field trip destinations include Wilsons Promontory, Heron Island, Falls Creek, the Mallee, Buchan and the Ovens River. These trips will give you the opportunity to interact with a range of flora and fauna, apply your knowledge in real settings and get hands-on experience using remote sensing and geographic information system (GIS) technology to collect and analyse data.&lt;/p&gt;&lt;p&gt;The practical side of your degree isn't limited to off-campus experiences. Our on-campus Wildlife Sanctuary is your very own 30-hectare laboratory, where you can study the behaviour of bat species and mosquito fish, and help preserve the natural habitats of species including the long-nosed potoroo, brolga, black wallaby and sugar glider.&lt;/p&gt;&lt;p&gt;With the Bachelor of Wildlife and Conservation Biology, you can study what you're passionate about. In addition to your core biology, conservation and quantitative skills subjects, you can choose from a range of electives – including anthropology, Indigenous studies, and environmental and resource economics – and tailor your study experience to suit your career aspirations.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Ecology and biodiversity&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the relationships between living organisms, including humans, and their physical environment. Learn how to protect the earth's biodiversity.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Climate change and sustainability&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how our actions and choices affect the natural, economic, social, political and cultural systems – both now and in the future.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Environmental law&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand the scope, structure and regulatory tools of environmental law and how to research, analyse, discuss and evaluate specific areas of Australian environmental law.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Endangered species biology and management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand the theory, concepts and issues of species conservation and how to review or prepare your own environmental management plan.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Research&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to draw conclusions from data, design surveys and experiments, and critically evaluate the statistical arguments made in scientific reports and journal articles.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>103840C</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>Master of Sport Analytics</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-sport-analytics</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>104</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>84400</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>42200</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Get the skills and experience needed to meet the growing demand for sports insights and performance analysis with La Trobe's Master of Sport Analytics.&lt;/p&gt;&lt;p&gt;Learn how to use data and artificial intelligence to boost athlete performance and wellbeing. Get hands-on experience with industry-standard technologies and advanced analytics tools, including R, Python and SQL, computer vision and video annotation software, machine-learning platforms and other athlete management systems.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Master of Sport Analytics, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;understand the basic practices for sport analytics methods and how to clearly communicate these outcomes&lt;/li&gt;&lt;li&gt;learn how to use data to develop insights into talent identification, athlete management, injury management and fan engagement&lt;/li&gt;&lt;li&gt;complete an industry project in your second year, partnering with professional sports teams like Carlton Football Club, sports technology companies like Champion Data, or national sporting bodies like Cricket Australia, the AFL and the Australian Institute of Sport (AIS).&lt;/li&gt;&lt;li&gt;take advantage of flexible study options, mixing in-person subjects with online and blended study, and the opportunity to exit early with a Graduate Certificate after six months, or a Graduate Diploma after one year.&lt;/li&gt;&lt;li&gt;graduate ready to use your new data analytics skills in the sport industry you're passionate about.&lt;/li&gt;&lt;li&gt;&lt;p&gt;learn to apply large language models and generative AI to sport analytics workflows, preparing you to work with the technologies reshaping how sport organisations collect, interpret and act on data.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Graduate Certificate in Sport Analytics</t>
+          <t>103841B</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
+          <t xml:space="preserve">Graduate Certificate in Sport Analytics </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-sport-analytics</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>26</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>21100</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>21100</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>February</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The Graduate Certificate in Sport Analytics is a six-month degree for those seeking to improve their knowledge and capacity to collect, manage, analyse and present large data sets captured from sport. Learn how to use data to boost athlete performance and wellbeing. You'll get practical learning using real sport datasets and technical training in the core tools of data analysis – all delivered flexibly with a mix of online and on-campus study ideal for busy professionals.&lt;/p&gt;&lt;p&gt;The course aims to prepare you for roles in the field of sport analytics or for currently employed sport and exercise professionals looking to progress in their career with a qualification in sports analytics. You'll graduate with a direct pathway into the Graduate Diploma in Sport Analytics or Master of Sport Analytics, or ready to use your new data analytics skills in the sport industry you're passionate about.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Graduate Certificate in Sport Analytics, you'll learn:&lt;/p&gt;&lt;p&gt;Sport analytics in practice&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Learn about contemporary technology applications, and apply theoretical understanding of analytics processes and methodologies to authentic sport-related data sets&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Database management&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Gain an overview of the architecture and management of database systems and the different database models, including relational database analysis, design, and implementation.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Data and analytical methods&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Learn how to perform various data handling techniques, develop enhanced skills in data warehousing, explore predictive analytics or gain the foundations of programming with Python through a selection of core choice subjects.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>104735G</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>Master of Engineering</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-engineering</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>104</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>92000</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Prepare for the rich opportunities of the future workforce with La Trobe's accredited Master of Engineering.&lt;/p&gt;&lt;p&gt;&lt;br/&gt;Developed in consultation with industry leaders, our Master's gives you advanced skills for a successful career, including design, engineering management, research and innovation. You'll learn how to adapt to the emerging technologies that are changing the engineering landscape like artificial intelligence and robotics. You'll also have the opportunity to experience engineering practice first-hand and build valuable industry connections with the option of an 800-hour work-integrated learning (WIL) program.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By completing La Trobe's Master of Engineering, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;explore engineering challenges through research, ideation and sustainable product design &lt;/li&gt;&lt;li&gt;understand the latest concepts in data and software to model, analyse and implement effective engineering systems &lt;/li&gt;&lt;li&gt;build engineering management skills across business strategy, legal, marketing, management and finance to lead projects, motivate teams and drive success&lt;/li&gt;&lt;li&gt;develop socially conscious decision-making processes by examining sustainable workplace practices in the Australian engineering industry&lt;/li&gt;&lt;li&gt;choose from two specialisations in electronics or telecommunications and networking&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership of Engineers Australia.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Graduate Diploma in Artificial Intelligence</t>
+          <t>104800C</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
+          <t xml:space="preserve">Graduate Diploma in Artificial intelligence </t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-in-artificial-intelligence</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>52</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>May, March, July, September</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Learn to use AI technology in a wide range of contexts, including digital healthcare, smart manufacturing, smart cities, sustainable energy infrastructure, precision agriculture and more. You'll learn from world-renowned lecturers who are leading the advancement of virtual reality and computer engineering.&lt;/p&gt;&lt;p&gt;Get a hands-on approach. Use your AI skills to solve real-world problems when you take on an industry-based project with leading organisations including Microsoft, Optus, 4Pi Labs, Aerion, Quantum Victoria, Nanjing University of Information Science and Technology, Pivot Maritime International and Axicor.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Problem-solving with AI&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover how research skills and deep learning algorithms are used to develop AI-based solutions to real-world problems.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Machine learning&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to analyse data to design, implement and evaluate machine learning techniques for solving real-world problems.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Deep learning techniques&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore deep learning techniques and apply them to AI functions like image recognition, machine translation and speech synthesis.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Social, legal and ethical impact of AI&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain an understanding of the legal, moral and societal issues faced by today's IT industry and their impact on how AI technology is used.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Offshore applicants are considered for admission based on the stated course entry requirements.&lt;/li&gt;&lt;li&gt;IELTS may be considered.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Master of Cybersecurity</t>
+          <t>104801B</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t xml:space="preserve"> Master of Cybersecurity</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/master-of-cybersecurity</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>104</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>87600</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Get the ethical hacking and defence strategies you need for an in-demand career with La Trobe's Master of Cybersecurity.&lt;/p&gt;&lt;p&gt;Build fundamental skills in system design, implementation, testing and documentation. Develop technical expertise in pen testing, blockchain and cyber forensics. Complement your cybersecurity expertise with transferable skills in entrepreneurship, professional practice and project management.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By studying La Trobe's Master of Cybersecurity, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;master ethical hacking and defence techniques to evaluate the security of network configurations and how to defend network-based threats&lt;/li&gt;&lt;li&gt;learn a procedural language that identifies and analyses common coding practices that avoid security vulnerabilities&lt;/li&gt;&lt;li&gt;explore the psychology of hacking and cybercrime, its legal and ethical frameworks and approaches to governance and risk management&lt;/li&gt;&lt;li&gt;supplement your skills with certifications through our partnership with Microsoft and get hands-on experience in our on-campus Cisco labs&lt;/li&gt;&lt;li&gt;choose an industry development project or work-based placement to cement your learning and launch your career, or pursue an applied research project or industry-based thesis&lt;/li&gt;&lt;li&gt;have the flexibility to exit early with a Graduate Diploma after one year or a Graduate Certificate after six months or, depending on your previous computer science or IT qualifications, complete your Master's in only 1.5 years&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>115616A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>Bachelor of Agriculture</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-agriculture</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>156</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>138000</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Prepare for a successful career tackling the big issues in farming, food production and farming systems. with La Trobe's Bachelor of Agriculture.&lt;/p&gt;&lt;p&gt;Build foundational skills and knowledge in plant and animal sciences, agricultural systems, agribusiness, land and soil management, and sustainable agricultural practice. Get a true, practical understanding with real-world case studies that address productivity and sustainability issues locally, nationally and globally.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By completing La Trobe's Bachelor of Agriculture, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;explore the leading business practices, technologies and innovations transforming farming to meet the food security challenges of the 21st century while reducing their environmental impacts&lt;/li&gt;&lt;li&gt;gain hands-on experience in soil science, disease identification, cropping and livestock management, entrepreneurship and innovation, and logistics and supply chain management&lt;/li&gt;&lt;li&gt;integrate theory with practice via work-based learning with agriculture industry leaders&lt;/li&gt;&lt;li&gt;benefit from learning with experts in industry including world-leading researchers in agricultural and veterinary sciences&lt;/li&gt;&lt;li&gt;have the flexibility choose from majors in agribusiness, animal science, or plant and soil science along with optional majors in climate change or open access majors and minors from a range of disciplines&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership with Ag Institute Australia.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/li&gt;&lt;li&gt;Units 3 and 4: a study score of at least 20 in any Mathematics.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>104807G</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>Diploma of Science</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/diploma-of-science</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>52</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Diploma of Science is a supported pathway into the Bachelor of Science – or the qualification you need to kickstart a career in entry-level roles in the science industry.&lt;/p&gt;&lt;p&gt;Explore basic scientific concepts and learn how to harness collaboration in the laboratory. Consolidate your new knowledge and skills through practical, laboratory-based classes where you'll have opportunities for hands-on experience. And build skills in scientific communication – an essential skill for sharing outcomes with different audiences.&lt;/p&gt;&lt;p&gt;Already know where you want to steer your career? Our wide range of electives allow you to take specialist subjects right away. Depending on your campus, choose from biochemistry, zoology, physics, molecular biology, data science and more.&lt;/p&gt;&lt;p&gt;You'll learn alongside Bachelor's students in the same subjects, while you map out your transition to further university study. Depending on your subject selection, after successfully completing your Diploma you can transfer directly into the second year of La Trobe's Bachelor of Science. That's all thanks to the one year's worth of course credit (also called advanced standing) you could receive for the subjects you study in your Diploma.&lt;/p&gt;&lt;p&gt;We'll be with you every step of the way. Receive tailored advice from a dedicated Senior Support Adviser and connect with discipline-based peer mentors. We'll help you enrol, choose your subjects and navigate university systems and requirements. You can also access La Trobe's Careers Service to help you shape your future.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Core scientific skills&lt;/strong&gt;&lt;br/&gt;Understand science fundamentals and the basic concepts of how science works.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Communicating as a scientist&lt;/strong&gt;&lt;br/&gt;Learn how to communicate basic scientific ideas in written and verbal formats to various audiences.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Collaboration and teamwork&lt;br/&gt;&lt;/strong&gt;Discover how to collaborate and work effectively in teams to solve problems and achieve shared goals.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 5 - Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 20 in any Mathematics.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>104936J</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>Diploma of Information Technology</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/diploma-of-information-technology</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>52</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>9210</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Diploma of Information Technology is designed to be a supported pathway into your dream IT degree or set you up to enter the industry in an entry level role.&lt;/p&gt;&lt;p&gt;Build a strong foundation in core IT subjects – think programming and cybersecurity – that'll prepare you for your next degree. You'll study alongside Bachelor's degree students from day one and get a taste of university life.&lt;/p&gt;&lt;p&gt;Depending on the subjects you've studied, you could graduate from the Diploma of Information Technology with up to one year's worth of course credit – known as advanced standing. This could allow you to transfer directly into the second year of your chosen IT degree. Choose from La Trobe's Bachelor of Computer Science, Bachelor of Cybersecurity or Bachelor of Information Technology. Alternatively, you may prefer to take your new skills directly into the workforce. It's up to you.&lt;/p&gt;&lt;p&gt;Prepare to succeed. We empower you to achieve great results in your Diploma and beyond. You'll have access to a range of support services – including a dedicated Senior Support Adviser who'll give you one-on-one advice and discipline-based peer mentors. We'll help you navigate day-to-day university processes from enrolment, to subject choice, to transferring to your Bachelor's degree. You can also take advantage of the Careers Service for help with your resume, interview skills and more.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Programming&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to design and implement software solutions using a range of popular programming languages such as C, Java and Python.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Information technology fundamentals&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Gain insight into how computers function across both hardware and software systems. Learn how data storage and retrieval, communications, networking, security and information systems are critical to our everyday lives.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cybersecurity&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Equip yourself with the knowledge to defend against cyber threats and attacks. Cover topics including information security, the ethical and legal implications of online information systems, and dynamic practices for incident analysis and response.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Data-based critical thinking&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop your evaluation and numeracy skills through interactive learning that covers data gathering, turning data into information, probability, and how to use data to drive critical business decisions.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 5 - Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;VCE: Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>106398C</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>Bachelor of Health Information Management</t>
         </is>
       </c>
-      <c r="B90" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-health-information-management</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>156</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>121200</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>40400</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Combine the clinical and business sides of healthcare and use data to make a difference to the quality of patient care with La Trobe's Bachelor of Health Information Management.&lt;/p&gt;&lt;p&gt;Develop a comprehensive skillset covering areas like anatomy and physiology, health classification, data analytics, health informatics and health systems management. Build foundations in your first year, then deepen your expertise throughout your degree, including 55 days of supervised professional placement with our prestigious health partners.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Bachelor of Health Information Management, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;learn the language of medicine, understanding the fundamental structures of human anatomy and physiology and how they function.&lt;/li&gt;&lt;li&gt;develop skills in health informatics and data analysis, including how to implement and manage health information systems – such as security, access and integration requirements – and how to analyse, interpret and disseminate complex health data&lt;/li&gt;&lt;li&gt;build knowledge in health classification and the coding of complex clinical data so it can be used to inform and evaluate health services&lt;/li&gt;&lt;li&gt;investigate the ethical challenges and legal requirements of working with health data, including ways to ensure patients can control their health information.&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership of the Health Information Management Association of Australia (HIMAA).&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;*Please be aware that this course includes mandatory in-person placement requirements. Students are expected to complete these placements in Australia.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>106400C</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>Bachelor of Laws (Honours)</t>
         </is>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>208</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>174400</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Stand out with a law degree committed to social impact and community engagement. Our dedicated four-year Law (Honours) degree gives you a strong academic and professional foundation with the ability to match your legal career to your area of interest through a range of specialised electives.&lt;/p&gt;&lt;p&gt;Put your legal skills to the test with hands-on practical learning opportunities through our Legal Internship Program, work-based learning, the Law Clinic, overseas study programs, and leading mooting program.&lt;/p&gt;&lt;p&gt;You'll also apply your training into the real world with internships, clerkships, and practical placements at legal firms, government bodies, and community legal centres – giving you enhanced employability and professional readiness through our network of industry and community partnerships.&lt;/p&gt;&lt;p&gt;Combine intellectual and skills-based legal training with a progressive approach to law. With a strong focus on practical skills like dispute resolution, criminal procedure, and contract law, you'll learn what it is like to work on real cases and develop the professional skills to meet the demands of legal practice.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Bachelor of Laws (Honours), you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop key skills in negotiation and examine the processes of arbitration, conciliation and mediation in private and commercial disputes&lt;/li&gt;&lt;li&gt;build your understanding of the criminal justice system, apply criminal law to real-world scenarios and provide legal advice&lt;/li&gt;&lt;li&gt;apply the legal principles governing the creation, interpretation and termination of a contract&lt;/li&gt;&lt;li&gt;hone your skills in critical thinking, research, writing and teamwork, then apply them with work-integrated learning opportunities in community legal centres, law firms and government agencies.&lt;/li&gt;&lt;li&gt;join our leading moot court program, with opportunities to take part in competitions both nationally and internationally.&lt;/li&gt;&lt;li&gt;benefit from a supportive learning environment that prioritises student wellbeing and academic success.&lt;/li&gt;&lt;li&gt;complete the subjects required by the Victorian Legal Admissions Board (VLAB) to meet the requirements for admission to the legal profession in Victoria.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Bachelor of Laws (Honours) /Bachelor of Psychological Science</t>
+          <t>106403M</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>Bachelor of Laws (Honours)/Bachelor of Psychological Science</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours-bachelor-of-psychological-science</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>260</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>218000</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;In La Trobe's Bachelor of Laws (Honours)/Bachelor of Psychological Science, you'll build an adaptable skillset that combines skills-based legal training with expertise in psychological science, preparing you for a rewarding career.&lt;/p&gt;&lt;p&gt;As you study law, you can tailor your degree to your personal career aspirations with a wide range of elective subjects and opportunities for hands-on professional experience. We combine outstanding legal training with a progressive approach that prepares you for employment. You'll build legal expertise in key areas of law and develop skills that are highly valued by all employers, like advocacy, negotiation, and dispute resolution.&lt;/p&gt;&lt;p&gt;In your accredited psychological science degree, you'll enjoy the full benefits of having access to academics who are experts in their fields. Explore the environmental factors that affect our mental health and understand how community members cope with mental and physical disorders. Thanks to our electives and specialised minors, you'll be able to further ensure your study meets your specific career goals.&lt;/p&gt;&lt;p&gt;With access to real-world placement opportunities in both law and psychology, you'll also have opportunities put your knowledge into practice – whether it's working at a community legal centre, law firms and government agencies, or undertaking a psychology-related field placement.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Evidence and criminal procedure&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build your understanding of the criminal legal system and procedure. Learn how to apply criminal law to real-world scenarios and provide legal advice.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Private and public law&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to apply the legal principles underpinning contract law, develop the skills to specialise as a corporate legal expert and discover how government power is distributed, exercised and controlled.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Clinical, health, developmental and social psychology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand how to help people cope with mental and physical disorders and investigate how environmental factors contribute to our psychological makeup.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Psychological assessment, intervention and research&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Become familiar with methods used to understand and measure people's psychological state, and learn when and how to intervene or conduct research.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bachelor of Laws (Honours) /Bachelor of Criminology</t>
+          <t>106404K</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>Bachelor of Laws (Honours)/Bachelor of Criminology</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours-bachelor-of-criminology</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>260</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>218000</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Build a rewarding legal career and a safer community for all with La Trobe's Bachelor of Laws (Honours)/Bachelor of Criminology.&lt;/p&gt;&lt;p&gt;Develop the knowledge and expertise to establish yourself as a forward-thinking legal professional while investigating the complex causes of crime. Gain a powerful skillset in dispute resolution, evidence and criminal procedure, contract law, company law and public law. Explore principles in crime prevention and policy, and how social factors intersect with our criminal justice system.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Bachelor of Laws (Honours)/Bachelor of Criminology, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop key skills in negotiation and examine the processes of arbitration, conciliation and mediation in private and commercial disputes&lt;/li&gt;&lt;li&gt;build your understanding of the criminal justice system, how to apply criminal law to real-world scenarios and provide legal advice&lt;/li&gt;&lt;li&gt;explore how deviance and crime are understood by different parts of society, and the role of courts, police and prisons in the criminal justice system&lt;/li&gt;&lt;li&gt;put your knowledge into practice with placement opportunities in law firms, community legal centres, courts and other government agencies&lt;/li&gt;&lt;li&gt;complete the subjects required by the Victorian Legal Admissions Board (VLAB) to meet the requirements for admission to the legal profession in Victoria&lt;/li&gt;&lt;li&gt;graduate with two degrees in only five years to gain a competitive career edge, with options in a wide range of industries.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>106465H</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>Bachelor of Global Studies</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-global-studies</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>156</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>107400</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>35800</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Bachelor of Global Studies gives you a strong grounding in the issues facing key regions and countries around the world. We've designed this degree to introduce you to global problems and their policy responses, so you'll develop the tools to tackle the challenges of the future.&lt;/p&gt;&lt;p&gt;Study core subjects examining the history of international relations and geopolitics, contemporary security issues – such as American power, the rise of China, contemporary armed conflict and terrorism – and the emerging challenges of human and environmental security.&lt;/p&gt;&lt;p&gt;Look at international cooperation and conflict. Analyse the dynamics of power, sovereignty and security, exploring transformational changes in 21st century international relations. Investigate the powerful role of international law – including humanitarian, environmental and refugee law.&lt;/p&gt;&lt;p&gt;Whatever your ambition, tailor your degree with specially curated majors and minors that allow you to explore the geopolitical and humanitarian forces shaping our world. Choose from majors such as international relations, human rights, conflict and negotiation, Asian politics and security, government and policy, sustainability and development, Chinese, Japanese, Hindi, Spanish, Greek, French and Italian.&lt;/p&gt;&lt;p&gt;Global experiences are a vital part of global studies. Get out of the classroom and into the real world with a study experience at one of our overseas partner universities and build both your skills and your professional network. You'll also have the opportunity to do an internship, either in Australia or overseas, that's tailored to your career goals.&lt;a href="#_ftn1"&gt;[1]&lt;/a&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Global issues and organisations&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;&lt;p&gt;Explore the complex systems, structures, laws and practices that shape global issues. Broaden your understanding and consider a range of political, social, legal and cultural perspectives.&lt;/p&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Problem solving and critical thinking&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to identify and analyse international and global problems and formulate responses to them.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Theory and practice of politics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build your understanding of political systems, actors and processes. Understand how they work at a local, national and global level.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Grassroots development and sustainability&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore how global decisions can impact individual communities and the environments we all depend on.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;a href="#_ftnref1"&gt;[1]&lt;/a&gt; Subject to government restrictions on international travel.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>106466G</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>Bachelor of Outdoor and Sustainability Education</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-outdoor-and-sustainability-education</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>156</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>110400</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>36800</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Bachelor of Outdoor and Sustainability Education takes you beyond the classroom. Get hands-on outdoor experience and build a deeper understanding of sustainability and environmental education.&lt;/p&gt;&lt;p&gt;Enjoy opportunities to build and enrich your outdoor adventuring skills while you explore nature. You could spend more than 70 days on field trips* and extended outdoor journeys while building a vital understanding of research on climate change and experiential learning. From bushwalking to kayaking, you'll prepare to lead groups while they explore outdoor environments and you develop your skill in outdoor learning.&lt;/p&gt;&lt;p&gt;You'll also be ready to help foster respect and appreciation for the world around you. Explore the social and scientific aspects of sustainability, including Indigenous understandings of our environment, and learn how to manage and teach outdoor education programs.&lt;/p&gt;&lt;p&gt;Whether you want to guide adventures or educate the community, we'll help you be ready for your future. You'll develop the skills and confidence to lead, teach and communicate in any situation.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Natural environment knowledge and sustainability&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn about Australia's diverse range of native flora and fauna and our complex relationship with it.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Educational skills&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore how to successfully create and deliver educational experiences about sustainability and the natural environment.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Outdoor adventure guiding&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the outdoors and build your skills in leading groups on adventure experiences.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Outdoor safety and risk management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover how to safely plan for leading groups of people in natural environments.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leadership, teamwork, and communication&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn by experience as you develop strong transferable skills that are applicable in any career.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;*The number of field trip days is dependent on the major selected.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Scraped from data API (be/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>106754K</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>Diploma of Teacher Education</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/diploma-of-teacher-education</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>52</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>36800</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're looking for a pathway to an accredited teaching degree, La Trobe's Diploma of Teacher Education is the perfect opportunity to take your first step towards a rewarding career in teaching.&lt;/p&gt;&lt;p&gt;When you successfully complete the Diploma of Teacher Education, you could progress to a Bachelor of Education (Primary), Bachelor of Education (Secondary) or Bachelor of Education (Early Childhood and Primary). You'll also receive advanced standing for up to one year of full-time study.&lt;/p&gt;&lt;p&gt;You'll develop solid foundations in digital learning, literacy, numeracy and learning contexts – skills that will serve you throughout your teaching career. Immerse yourself in the full university experience, studying alongside Bachelor students in the same subjects.&lt;/p&gt;&lt;p&gt;We're at your side every step of the way. Receive personalised advice from a dedicated Student Adviser and connect with discipline-based peer mentors. We'll help you enrol, choose your subjects and navigate university systems and requirements. You can also access the university-wide careers service for advice and assistance on your resume, interview skills and career planning.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Digital learning&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the world of digital learning in a way that's creative, collaborative and innovative.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Learning contexts&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to create safe, diverse learning environments for people of all ages and backgrounds.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Literacy and numeracy&lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;Understand key concepts and conventions of the English language and numeracy.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 5 - Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;VCE: Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/li&gt;&lt;li&gt;HSC: One of English Standard, English Advanced (Band 2), English as an Additional Language or Dialect (Band 3).&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>106755J</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>Associate Degree of Teacher Education</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/associate-degree-of-teacher-education</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>104</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>73600</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>36800</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're looking for a rewarding career in education, La Trobe's Associate Degree of Teacher Education is a perfect pathway to an accredited teaching degree.&lt;/p&gt;&lt;p&gt;When you successfully complete the Associate Degree of Teacher Education, you could progress to a Bachelor of Education (Primary), Bachelor of Education (Secondary) or Bachelor of Education (Early Childhood and Primary). You'll also receive advanced standing for up to two years of full-time study.&lt;/p&gt;&lt;p&gt;You'll develop strong foundational skills in professional literacy and numeracy, as well as knowledge of contemporary approaches to learning.&lt;/p&gt;&lt;p&gt;You'll also start specialising in your chosen field – primary, secondary, or early childhood and primary – and build discipline-specific knowledge, choosing from electives in science, languages, arts, health, psychology, physical education and more.&lt;/p&gt;&lt;p&gt;We're at your side every step of the way. Receive personalised advice from a dedicated Student Adviser and connect with discipline-based peer mentors. We'll help you enrol, choose your subjects and navigate university systems and requirements. You can also access the university-wide careers service for advice and assistance on your resume, interview skills and career planning.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Digital learning&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the world of digital learning in a way that's creative, collaborative and innovative.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Learning contexts&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to create safe, diverse learning environments for people of all ages and backgrounds.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Literacy and Numeracy&lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;Understand key concepts and conventions of the English language and numeracy.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 6 - Associate Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;IELTS (Academic) score of 7.5 with no individual band score less than 7.0&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>106756H</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>Graduate Diploma in Education</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-in-education</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>52</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>38000</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>38000</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Advance your career and stay up-to-date with current best practice with La Trobe's Graduate Diploma in Education. You'll develop your networks and grow your career as an educator and leader.&lt;/p&gt;&lt;p&gt;Deepen your foundations with core subjects on educational leadership, how humans learn and digital technologies. Then add a specialisation of your choosing, such as curriculum design, or inclusion and diversity.&lt;/p&gt;&lt;p&gt;This flexible course is designed for people who're working. Many subjects are delivered in intensive or blended modes, making it easier to fit study into your life. You can also study at your own pace, undertaking one to four subjects per semester.&lt;/p&gt;&lt;p&gt;If you'd like the option to further extend your skills, the Graduate Diploma in Education can also provide a fully credited pathway to the Master of Education.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Contemporary educational practice&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop your understanding of educational best practice.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Diversity&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore diversity in educational contexts and plan for socially just and inclusive education.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Research&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore educational research and learn how to incorporate it into your practice.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Learning sciences&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn about the science of language and reading and how to apply this across primary and secondary classrooms.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Leadership and team building&lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;Learn how to evaluate current practice and manage diversity in educational organisations.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>106758F</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>Master of Professional Accounting</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-professional-accounting</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>78</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>70800</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>47200</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Become an expert with in-demand skills when you study La Trobe's Master of Professional Accounting.&lt;/p&gt;&lt;p&gt;In this accredited degree, you'll build expertise in existing and emerging accounting information systems and data analytics tools. Investigate the fields underpinning modern accounting, including business law, taxation, finance and economics. Connect with industry and professional accounting bodies during your studies and prepare for career success.&lt;/p&gt;&lt;p&gt;Learn how to solve accounting problems across a diverse variety of business contexts. With lectures delivered by leading academics and guest industry experts, you'll get a well-rounded perspective on contemporary accounting issues – ranging from industry-specific measurement issues to the impact of global harmonisation on financial reporting practices.&lt;/p&gt;&lt;p&gt;La Trobe's Master of Professional Accounting is a direct pathway to becoming a qualified professional accountant. If you have limited exposure to accounting or are forging a new path, this degree will develop your theoretical and technical knowledge and skills to build your dream career.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Accounting principles, information systems and analytics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand how to record business transactions, prepare financial statements and evaluate business performance. Use the accounting and data analytics tools to analyse data and assist decision making.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Management accounting&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand how to provide organisational decision-makers with relevant accounting information to assist with strategic planning, controlling and performance management.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Financial accounting and reporting&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Apply international and Australian accounting standards involving measurement and professional judgement in a variety of practical scenarios.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Auditing and assurance&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the nature and purpose of auditing and assurance. Understand the responsibilities of auditors in the context of reporting quality information.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Taxation&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the fundamentals of the taxation system and its implications for individuals and businesses. &lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>106759E</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>Master of Extended Professional Accounting</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-extended-professional-accounting</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>104</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>94400</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>47200</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Want to become an accounting expert with career options beyond the traditional roles of accounting? La Trobe's Master of Extended Professional Accounting offers you the flexibility to extend your study into a range of specialist business areas.&lt;/p&gt;&lt;p&gt;In this accredited degree, you'll build the skills and knowledge to create, analyse and interpret the accounting information that's essential in all businesses and public enterprises. Be ready to help evaluate business models, advise on strategy and decision-making, audit accounts and manage tax issues.&lt;/p&gt;&lt;p&gt;Gain a valuable blend of technical expertise and hands-on experience that'll broaden your career opportunities. What's more, you'll further hone the human skills that employers are looking for, like communication and personal development.&lt;/p&gt;&lt;p&gt;Prepare for career success with this degree – we've designed it with industry input to build the skills you need in the workplace. Hear guest lectures from industry experts and enjoy opportunities to connect with industry and professional accounting bodies.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Accounting principles, information systems and analytics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand how to record business transactions, prepare financial statements and evaluate business performance. Use the accounting and data analytics tools to analyse data and assist decision making.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Management accounting&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand how to provide organisational decision-makers with relevant accounting information to assist with strategic planning, controlling and performance management.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Advanced financial accounting and reporting issues&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Apply international and Australian accounting standards involving measurement and professional judgement in a variety of practical scenarios. Develop a systematic knowledge of contemporary issues in accounting.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Auditing and assurance&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the nature and purpose of auditing. Understand the responsibilities of auditors in the context of reporting quality information.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Taxation&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the fundamentals of the taxation system and its implications for individuals and businesses.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>106768D</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>Bachelor of Commerce/Bachelor of Global Studies</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-commerce-bachelor-of-global-studies</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>208</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>180000</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Explore the complex social, commercial and sustainability challenges faced by multinational corporations and diverse communities through La Trobe's Bachelor of Commerce/Bachelor of Global Studies.&lt;/p&gt;&lt;p&gt;Co-designed with industry leaders, our double degree gives you a strong grounding in the issues facing key regions and countries around the world. You'll understand global problems and policy responses, and how to develop tools to tackle the challenges of the future. You'll be prepared for the globalised world and the complex web of relationships negotiated by governments and multinationals every day.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Commerce/Bachelor of Global Studies, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;learn how to identify practical solutions to real-world challenges, improve your ability to negotiate with stakeholders and communicate your solutions&lt;/li&gt;&lt;li&gt;explore the history of international relations and geopolitics, contemporary security issues, human and environmental security, international cooperation and conflict, and more.&lt;/li&gt;&lt;li&gt;choose from majors in commerce – including accounting, business analytics, economics, finance, management and marketing – and global studies – such as human rights, international relations, sustainability and development, or a language&lt;/li&gt;&lt;li&gt;gain real-world experience through an industry placement, work-integrated learning project or overseas student exchange.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>106769C</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>Master of Logistics and Supply Chain Management</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="C102" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-logistics-and-supply-chain-management</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>104</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>94400</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>47200</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Tackle real-world logistics and supply chain challenges while using emerging analytics technologies to transform business practice with La Trobe's Master of Logistics and Supply Chain Management.&lt;/p&gt;&lt;p&gt;Designed and delivered in consultation with industry professionals, you'll gain direct exposure to the logistics and supply chain sector through field trips to ports and distribution centres, guest lectures, hands-on assessments, and optional industry placements.&lt;/p&gt;&lt;p&gt;Explore topics across AI, blockchain, Internet of Things, cybersecurity governance and applied data analytics, covering the technical skills while exploring the ethical, environmentally responsible supply chain innovation through integrated circular economy and carbon accountability practices — preparing you for future-ready roles at the forefront of Industry 5.0 innovations.&lt;/p&gt;&lt;p&gt;You'll benefit from tailored pathways depending on your professional experience and prior learning with options to complete your Master's degree in 1 or 1.5 years or exit early with a Graduate Certificate or Graduate Diploma. You'll also study through a combination of online and on campus classes with full-or part-time study options – giving you greater flexibility to balance work and life commitments.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Master of Logistics and Supply Chain Management, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;master sustainable and responsible business practice and the circular economy in a national and global context&lt;/li&gt;&lt;li&gt;build strong foundational expertise across all key areas of supply chain strategy, including logistics, sourcing, marketing, ICT, and customer service&lt;/li&gt;&lt;li&gt;develop broad managerial skills in human resource management, project management, and quality control to prepare for leadership roles in complex, global supply networks&lt;/li&gt;&lt;li&gt;gain hands-on data analytics skills using real-world tools and techniques, such as data visualisation, predictive analytics, and business analytics applications specific to logistics and supply chain contexts&lt;/li&gt;&lt;li&gt;understand the impact of digitalisation and technologies like artificial intelligence (AI), digital twins and cloud computing to unlock valuable insights&lt;/li&gt;&lt;li&gt;engage in industry-led experiential and work-integrated learning, including coaching and networking opportunities and access to graduate programs with our partners.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>106770K</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>Graduate Diploma in Logistics and Supply Chain Management</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-in-logistics-and-supply-chain-management</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>52</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>47200</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>106771J</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Logistics and Supply Chain Management</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-logistics-and-supply-chain-management</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>26</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Logistics and Supply Chain Management is a thriving field with exponential growth. Our Graduate Certificate in Logistics and Supply Chain Management course equips you with the knowledge, skills, and strategic acumen needed to tackle real-world industry challenges and leverage emerging technologies for transformative logistics and supply chain practices. This course is designed to rapidly upskill individuals in just one (1) semester, offering a fundamental understanding of end-to-end supply chains. The course focuses on three core pillars:&lt;/p&gt;&lt;ol&gt;&lt;li&gt;&lt;strong&gt;Applied Analytics and Digitalisation:&lt;/strong&gt; You will explore the application of emerging technologies like AI, digital twins, and cloud computing to unlock valuable logistics and supply chain insights. We prioritise enhancing your practical skills in logistics and supply chain analytics, encompassing visual, predictive, and big data analytics.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Circular Economy and Sustainability: &lt;/strong&gt;Learn how to integrate Circular Economy principles into logistics and supply chain management strategies, aligning with the United Nations Sustainable Development Goals (SDGs), particularly SDG 9: Industry, Innovation, and Infrastructure, and SDG 12: Responsible Consumption and Production.&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Employability Skills: &lt;/strong&gt;Develop your professional and business skills that enhance your employability.&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;&lt;strong&gt;&lt;em&gt;Is this course for me?&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;This course is tailor-made for individuals seeking comprehensive knowledge and practical skills in logistics and supply chain management. To maximise your employability, this course incorporates various practical elements. Our course advisory committee, composed of industry professionals, along with our extensive industry connections, provide additional opportunities such as graduation programs, coaching, and mentorship throughout your studies. &lt;/p&gt;&lt;p&gt;The program offers flexibility and serves as a pathway to building expertise in the logistics and supply chain field. Upon successful completion of the course, you can choose to exit with a Graduate Certificate or continue your education by pursuing our Graduate Diploma or Master of Logistics and Supply Chain Management programs. You will be eligible for advanced standing for four subjects in these programs, providing a seamless upskilling journey.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Bachelor of Laws (Honours) /Bachelor of Global Studies</t>
+          <t>106772H</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
+          <t>Bachelor of Laws (Honours)/Bachelor of Global Studies</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours-bachelor-of-global-studies</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>260</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>218000</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Bachelor of Laws (Honours)/Bachelor of Global Studies is an immersive and flexible double degree giving you the skills and knowledge to succeed.&lt;/p&gt;&lt;p&gt;Become a legal expert with valuable expertise in global affairs. You'll develop your legal knowledge and skills as you build a deep understanding of global issues, diplomacy, politics, and international trade.&lt;/p&gt;&lt;p&gt;Your law degree will introduce you to the fundamentals of legal practice and build your skills in advocacy, negotiation, and dispute resolution – all highly valued by employers across a range of industries.&lt;/p&gt;&lt;p&gt;At the same time, your global studies degree will immerse you in a wide range of global issues, including international relations and geopolitics, contemporary security issues, the proliferation of weapons of mass destruction, and contemporary armed conflict and terrorism. Tailor your studies to your interests with a choice of five curated majors – international relations, conflict and negotiation, Asian politics and security, government and policy, and human rights.&lt;/p&gt;&lt;p&gt;When it comes to learning, there's no substitute for hands-on experience. You'll have the opportunity to take on real-world work placements in settings such as community legal centres, law firms, government agencies, and with judges and magistrates (subject to availability) and bolster your education with a practical global studies placement subject. You could also put your legal skills to the test in law competitions, both locally and internationally.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Dispute resolution&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build key skills in negotiation and mediation to support your future practice. Learn about the processes of arbitration, conciliation, mediation, and negotiation in international disputes.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Private and public law&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to apply the legal principles underpinning contract law, develop the skills to specialise as a corporate legal expert, and discover how government power is distributed, exercised, and controlled.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Global issues and organisations&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand the complex systems, structures, laws, and practices that shape global issues from a range of political, social, legal, and cultural perspectives.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Theory and practice of politics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build your understanding of political systems, actors, and processes at local, national, and global levels.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Grassroots development and sustainability&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Global decisions have impacts on individual communities and environments. You'll explore how the big decisions impact the human quality of life and the environments we all depend on.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Bachelor of Laws (Honours) /Bachelor of Commerce</t>
+          <t>106773G</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
+          <t>Bachelor of Laws (Honours)/Bachelor of Commerce</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours-bachelor-of-commerce</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>260</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>218000</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Gain a prestigious double degree that prepares you to be a change-maker in business and law with La Trobe's Bachelor of Laws (Honours)/Bachelor of Commerce.&lt;/p&gt;&lt;p&gt;Develop a sophisticated understanding of legal process, advanced negotiation, and complex legal and regulatory frameworks that will give you an edge in commercial settings and corporate legal practice. You'll hone your skills in financial literacy and master digital business tools, with opportunities to learn in legal placements across government and corporate sectors.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Laws (Honours)/Bachelor of Commerce, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;specialise as a corporate legal expert through studies in incorporation, corporate governance and methods of financing&lt;/li&gt;&lt;li&gt;build key skills in dispute resolution, negotiation and mediation&lt;/li&gt;&lt;li&gt;develop cultural intelligence, leadership skills, stakeholder negotiation and communication skills that help you to thrive in any work environment&lt;/li&gt;&lt;li&gt;choose from a wide range of commerce majors, including accounting, business analytics, economics, finance, management and marketing&lt;/li&gt;&lt;li&gt;be ready to meet the legal and commercial challenges of automation, AI-driven technologies and big data&lt;/li&gt;&lt;li&gt;depending on your choice of majors, graduate ready to apply for membership of a range of business professional associations.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Bachelor of Laws (Honours) /Bachelor of Media and Communication</t>
+          <t>106774F</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
+          <t>Bachelor of Laws (Honours)/Bachelor of Media and Communication</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours-bachelor-of-media-and-communication</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>260</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>218000</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Get the the skills and experience to broaden your legal career in an evolving media landscape with La Trobe's Bachelor of Laws (Honours)/Bachelor of Media and Communication.&lt;/p&gt;&lt;p&gt;Gain a powerful skillset in dispute resolution, evidence and criminal procedure, contract law, company law and public law. Build media expertise as you hone your understanding of contract management, regulation and representation. Get hands-on experience in our purpose-built, industry-grade Upstart newsroom or via work-based learning with our prestigious media industry partners or a range of legal settings, including community legal centres, law firms and government agencies.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Laws (Honours)/Bachelor of Media and Communication, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop key skills in negotiation and examine the processes of arbitration, conciliation and mediation in private and commercial disputes&lt;/li&gt;&lt;li&gt;develop foundational skills in digital media, storytelling, communication and critical thinking&lt;/li&gt;&lt;li&gt;look behind the headlines and investigate the social, ethical, legal and technological questions that confront media producers every day&lt;/li&gt;&lt;li&gt;complete the subjects required by the Victorian Legal Admissions Board (VLAB) to meet the requirements for admission to the legal profession in Victoria&lt;/li&gt;&lt;li&gt;graduate with two degrees in only five years to gain a competitive career edge, with options in a wide range of industries.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>106835J</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>Associate Degree in Engineering Technology</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/associate-degree-in-engineering-technology</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>104</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>86000</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're keen to launch your career in engineering, La Trobe's Associate Degree in Engineering Technology will give you solid foundations for success and a pathway to a world-class Bachelor's degree in engineering.&lt;/p&gt;&lt;p&gt;Learn how to tackle the big problems faced by engineers every day. Develop essential skills in maths, physics and computer programming. Then set yourself apart from other graduates when you learn valuable human skills in innovation, business management and leadership.&lt;/p&gt;&lt;p&gt;In this highly practical degree, you'll collaborate with multidisciplinary teams and develop your problem-solving skills. Explore the impacts of climate change and find innovative engineering solutions to help create sustainable societies. You'll work with real-world engineering systems and learn current best practice from leading engineering experts.&lt;/p&gt;&lt;p&gt;Develop your written and oral communication skills. You'll build your confidence in relaying complex technical information and explore the technical, financial, legal and environmental impacts of engineering innovations.&lt;/p&gt;&lt;p&gt;Get a degree that's recognised by industry. Graduates can apply for membership with Engineers Australia as an Engineering Associate.&lt;/p&gt;&lt;p&gt;Once you've completed your Associate Degree, you'll be eligible to apply to La Trobe's Bachelor of Civil Engineering (Honours) you will then be able to apply for advanced standing to commence Bachelor studies at third year where you can further enhance your industry knowledge and experience by undertaking large-scale projects and work placements.&lt;/p&gt;&lt;p&gt;Get ready for a bright career in engineering.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Programming for engineers and scientists &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Design and create software solutions to real-life problems, using programming languages such as Python.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Computer-aided design (CAD) &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Harness the computer tools to design, simulate and model an engineered product.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Engineering enterprise &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to become an engineering business leader. Explore business strategies for engineers, management tools and resources, the legal system, marketing and finance.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Sustainability and renewable energy design &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn about climate change, sustainability and renewable energy design, and join a multidisciplinary team on a renewable energy project.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Systems modelling &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop your modelling skills using software tools such as MATLAB and Simulink. Model and investigate engineering systems related to a broad range of real-world engineering systems.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Engineering design and problem solving &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Examine current engineering practices and develop your creative engineering design skills through an industry research project.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 6 - Associate Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/li&gt;&lt;li&gt;Units 3 and 4: a study score of at least 20 in any Mathematics.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>106836H</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Data Science Fundamentals</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="C109" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-data-science-fundamentals</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>26</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>21900</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>May, March, July, September</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Every data scientist must become a master of mathematics, modelling and database design. With La Trobe's Graduate Certificate in Data Science Fundamentals, you'll take your first big steps towards this important goal.&lt;/p&gt;&lt;p&gt;Gain valuable skills and knowledge, learn from industry experts and build your professional networks. Whether you have existing experience in data science or not, this course is your pathway to start or progress your career in this exciting domain.&lt;/p&gt;&lt;p&gt;Build your skills using real data sets from our industry partners and learn how to solve data challenges facing businesses and organisations. Learn how to create complex models and use powerful tools for advanced analysis and problemsolving. Designed in collaboration with our industry partners, this degree gives you the knowledge, skills and hands-on experience to transition from university to the workplace.&lt;/p&gt;&lt;p&gt;Learn from leading academics and industry practitioners via our flexible online learning platform. You'll be immersed in a fascinating curriculum and develop strong connections with fellow students that will support your career and widen your networks.&lt;/p&gt;&lt;p&gt;Graduate prepared to kickstart a career in data science or transfer directly into the second semester of La Trobe's&lt;br/&gt;Master of Data Science, should you decide to further your studies.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Programming&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn the language of computers. Understand how to analyse problems and use Python to build software-based solutions.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Database fundamentals&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand how to design, build and implement databases, and explore advanced concepts relating to database design.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Mathematics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the mathematical ideas underpinning the theory and techniques of data science. Learn how to use matrices to manipulate data.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Statistics and probability&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn important statistical techniques. Understand how to make sense of data, find trends and predict probable outcomes using R.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Offshore applicants are considered for admission based on the stated course entry requirements.&lt;/li&gt;&lt;li&gt;IELTS may be considered.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>106838F</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>Bachelor of Arts/Bachelor of Science</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-arts-bachelor-of-science</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>208</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>172000</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>43000</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Develop the scientific expertise, critical thinking and creativity to tackle complex global challenges with La Trobe University's Bachelor of Arts/Bachelor of Science. &lt;/p&gt;&lt;p&gt;In this double degree, you will divide your studies between arts and science, tailoring your degree with arts disciplines such as anthropology, languages, archaeology and philosophy, alongside biological sciences such as botany, zoology and biochemistry, or physical sciences such as physics, chemistry and data science. You will develop technical knowledge alongside the communication, creativity, critical thinking and ethical awareness needed to understand issues from multiple perspectives. &lt;/p&gt;&lt;p&gt;You will build capability in data analytics, digital literacy and emerging technologies while examining their social, political and ethical implications. Through theoretical and practical learning, a dedicated career development subject, and opportunities to undertake industry projects or placements, you will develop the skills to address challenges such as climate change, biodiversity conservation, public health and the communication of scientific knowledge. &lt;/p&gt;&lt;p&gt;By studying the Bachelor of Arts/Bachelor of Science, you will learn how to: &lt;/p&gt;&lt;ul&gt;&lt;li&gt;analyse complex environmental, social, political and scientific challenges &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;apply scientific methods to investigate questions and interpret evidence &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;evaluate the social, ethical and cultural implications of emerging technologies &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;communicate ideas and research findings to diverse audiences &lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;collect, analyse and interpret data in laboratory, field and digital environments. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 20 in any Mathematics.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/p&gt; English Language Requirements&lt;p&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>107088J</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Business Analytics</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-business-analytics</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>26</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>21900</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>May, March, July, September</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're keen to give your business career a boost, La Trobe's Graduate Certificate in Business Analytics is the perfect place to learn how to build smarter, more resilient business solutions with data. Designed in consultation with industry leaders, this course equips you with practical, future-ready skills to thrive in the rapidly evolving digital economy.&lt;/p&gt;&lt;p&gt;Explore how artificial intelligence is transforming business decisionmaking. Understand the fundamentals of cybersecurity and how to safeguard digital systems. Get hands-on with prototyping and low-code development through innovative coding tools. Develop your analytical mindset and learn how to utilise business data to create a real impact. &lt;/p&gt;&lt;p&gt;You'll learn through applied, team-based projects and gain experience with technologies and practices used across sectors. Plus, through guest lectures and industry connections, you'll hear directly from experts from leading organisations.&lt;/p&gt;&lt;p&gt;After successfully completing the Graduate Certificate in Business Analytics, you may be eligible for up to one semester of advanced standing toward La Trobe's &lt;strong&gt;Master of Business Analytics&lt;/strong&gt;, allowing you to fast-track your studies.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You will learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;AI for Business&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the fundamentals of AI and how it's transforming industries. Learn how to apply AI tools ethically to create smarter, data-driven business solutions.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Principles of Business Analytics &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build foundational skills in data interpretation, visualisation, and decision-making. Learn how to turn business data into insights that drive strategy and performance.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cybersecurity for Business &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand the key principles, risks, and frameworks that protect digital business systems. Learn how to identify threats, ensure compliance, and build cyber-resilient organisations.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Vibe Coding for Startups&lt;/strong&gt; &lt;br/&gt;&lt;ul&gt;&lt;li&gt;Develop rapid prototypes and innovative solutions using low-code tools. Learn how to bring digital ideas to life in business-focused, agile team environments.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>107090D</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>Bachelor of Laws (Honours)/Bachelor of Arts</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours-bachelor-of-arts</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>260</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>218000</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;La Trobe's Bachelor of Laws (Honours)/Bachelor of Arts lets you enrich your legal education by pursuing your interests and passions. Open doors to a diverse range of rewarding careers, while exploring how to make a difference in your community.&lt;/p&gt;&lt;p&gt;Learn the fundamentals of criminal, constitutional, property and company law. Explore the legal system and understand how it can be used as a powerful and positive force in society. Develop key skills in advocacy, negotiation and dispute resolution.&lt;/p&gt;&lt;p&gt;You'll also choose from our list of arts majors and explore your area of interest. Broaden your knowledge and experience by studying areas like politics, languages, sociology, history, philosophy and media studies. Learn how to communicate effectively and think critically, analytically and creatively.&lt;/p&gt;&lt;p&gt;You can also choose to complete law electives that complement your arts specialisation. For example, a politics major can be matched with related subjects like public international law and human rights law. While a language or philosophy major could be augmented by subjects in areas like Indigenous Australians and the law, intellectual property law or family, society and law.&lt;/p&gt;&lt;p&gt;Enhance your classroom learning by taking advantage of optional internships, work experience, and our study abroad program*. Gain hands-on experience working with community legal centres, law firms and government agencies. Find out what it takes to interview clients, prepare legal advice and work with senior lawyers to develop legal solutions.&lt;/p&gt;&lt;p&gt;Graduate ready to make a positive difference. With combined expertise in law and arts, you can build a career as a solicitor or barrister, in-house counsel or corporate consultant, working in commercial law firms or community legal centres. You could also work in the public service as a government lawyer or support social justice initiatives in the not-for-profit sector.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Evidence and criminal procedure &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build your understanding of the criminal legal system and process. Learn how to apply the law to factual scenarios and provide legal advice.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;&lt;strong&gt;Contract law and company law&lt;/strong&gt;&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to apply the legal principles governing the creation, interpretation and termination of a contract. Develop the skills to specialise as a corporate legal expert through studies in incorporation, corporate governance and the various methods of financing.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Constitutional law&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover how government power is distributed, exercised, and controlled. Learn about federalism, the €˜external affairs' power, and express and implied constitutional rights.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Dispute resolution &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build key skills in negotiation and mediation to support your future practice. Learn about the processes of arbitration, conciliation, mediation, and negotiation in private and commercial disputes.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Critical and creative thinking&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Delve into complex problems. Learn how to see new possibilities and turn them into reality.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Communication&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to connect, communicate and collaborate with your university peers and future colleagues.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;*Please note: overseas programs may be impacted by travel restrictions.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>107091C</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>Bachelor of Laws (Honours)/Bachelor of Politics, Philosophy and Economics</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours-bachelor-of-politics-philosophy-and-economics</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>260</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>218000</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Combine practical, progressive and multidisciplinary legal skills with a unique social and ethical perspective on how the law works with La Trobe's Bachelor of Laws (Honours)/Bachelor of Politics, Philosophy and Economics.&lt;/p&gt;&lt;p&gt;Gain a powerful skillset in dispute resolution, evidence and criminal procedure, contract law, company law and public law. Enhance your political expertise by learning how governments manage the economy and achieve important social objectives. Gain first-hand experience with work placement opportunities in law firms, community legal centres, courts and other government agencies.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Bachelor of Laws (Honours)/Bachelor of Politics, Philosophy and Economics, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop key skills in negotiation and examine the processes of arbitration, conciliation and mediation in private and commercial disputes&lt;/li&gt;&lt;li&gt;understand constitutional law and how government power is distributed, exercised and controlled&lt;/li&gt;&lt;li&gt;explore philosophy and critical thinking, improve your ability to reason empathetically and reflect clearly on complex issues&lt;/li&gt;&lt;li&gt;build your knowledge of political systems, how countries are governed, and the forces and players that influence policy&lt;/li&gt;&lt;li&gt;complete the subjects required by the Victorian Legal Admissions Board (VLAB) to meet the requirements for admission to the legal profession in Victoria&lt;/li&gt;&lt;li&gt;graduate with two degrees in only five years to gain a competitive career edge, with options in a wide range of industries.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Bachelor of Laws(Honours)/Bachelor of Science</t>
+          <t>107092B</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
+          <t>Bachelor of Laws (Honours)/Bachelor of Science</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours-bachelor-of-science</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>260</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>218000</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;In La Trobe's Bachelor of Laws(Honours)/Bachelor of Science, you can pursue multiple interests and gain a powerful combination of legal skills and cutting-edge scientific knowledge.&lt;/p&gt;&lt;p&gt;From stem cell research to how personal information is collected, stored and shared, advances in science and technology have real human impacts. This double degree uniquely prepares you to address contemporary challenges from a scientific, legal and ethical perspective.&lt;/p&gt;&lt;p&gt;Benefit from our progressive approach to legal education with a law degree you can shape to your own career goals. You'll get a solid grounding in the basics of law and hone your expertise in advocacy, negotiation and dispute resolution – skills valued by employers across industries.&lt;/p&gt;&lt;p&gt;Your science degree offers you huge flexibility, with an extensive range of majors to choose from. Follow your interests in emerging areas like cybersecurity, artificial intelligence and data science or traditional fields including chemistry, botany and genetics. Bring knowledge to life in world-class facilities, including the La Trobe Institute for Molecular Science (LIMS), and learn from academics who are leaders in their fields.&lt;/p&gt;&lt;p&gt;Take your skills into the real world while you study. You'll have the opportunity to do placements in a range of legal settings, including community legal centres, law firms, government agencies, and judges and magistrates (subject to availability). On the science side, you could complete a placement with one of our industry partners – previous students have worked with CSIRO, Bayer Crop Science, and various government departments.&lt;/p&gt;&lt;p&gt;You will graduate ready to start your career as an expert legal practitioner, with an advanced understanding of scientific concepts or a science professional with a solid understanding of regulatory environments and how they impact scientific work.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Dispute resolution&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build key skills in negotiation and mediation to support your future practice. Learn about the processes of arbitration, conciliation, mediation, and negotiation in commercial disputes.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Private and public law&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn to apply the legal principles underpinning contract law, develop the skills to specialise as a corporate legal expert, and discover how government power is distributed, exercised and controlled.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Discipline-specific legal expertise&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Align your legal education to your area of scientific specialisation by choosing law electives from fields including environmental law, international law, intellectual property law, cyber law, and policy.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Professional scientific thinking&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how science contributes new knowledge and finds solutions to problems in our society.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Lab and fieldwork skills&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to collect data and use specialist technical skills to develop new findings in the laboratory and in the field. Learn to find solutions to complex scientific problems.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Academic Requirements&lt;p&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/p&gt;&lt;p&gt;Units 3 and 4: a study score of at least 20 in any Mathematics.&lt;/p&gt; English Language Requirements&lt;p&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>107139C</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>Graduate Diploma of Archaeology</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-of-archaeology</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>52</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>40200</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>40200</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're looking to quickly develop specialist skills in contemporary archaeological practice, La Trobe's Graduate Diploma of Archaeology will give you solid foundations for a career in archaeology and heritage management.&lt;/p&gt;&lt;p&gt;You'll acquire comprehensive knowledge of Australian and Indigenous Australian archaeology, and you'll learn from renowned researchers in La Trobe's world-class facilities.&lt;/p&gt;&lt;p&gt;You'll get hands-on experience as you choose from a wide range of subjects, including specialist studies such as heritage planning, community consultation, field techniques and more. As part of your studies, you could also record and analyse archaeological artefacts, learn to identify materials, and catalogue and manage artefacts.&lt;/p&gt;&lt;p&gt;Upon successful completion of the Graduate Diploma of Archaeology, you may be eligible for advanced standing for eight subjects in the Master of Archaeology, should you choose to continue your studies.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Indigenous and historic archaeology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Delve into Indigenous Australian and historic archaeology. Examine past practice and contemporary advances and findings.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cultural heritage management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn to navigate and guide others in the ethical and regulatory requirements of managing sites and objects of cultural importance.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Archaeological field methods&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build the practical skills and knowledge you need to conduct archaeological fieldwork in Australia and overseas.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>107140K</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>Master of Archaeology</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-archaeology</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>104</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>80400</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>40200</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're looking to pursue a rewarding career in the field of archaeology, La Trobe's Master of Archaeology will prepare you for a career as a professional archaeologist, heritage manager or researcher.&lt;/p&gt;&lt;p&gt;You'll develop specialist skills in contemporary archaeological practice and acquire comprehensive knowledge of Australian and Australian Indigenous archaeology.&lt;/p&gt;&lt;p&gt;You'll learn from renowned researchers in La Trobe's world-class facilities and benefit from both a hands-on and academic perspective.&lt;/p&gt;&lt;p&gt;For students interested in a global career in archaeology, the Master of Archaeology can be tailored to meet your needs. Develop strong field skills applicable anywhere in the world while undertaking specialist research into your preferred region and time period.&lt;/p&gt;&lt;p&gt;Choose from a wide range of subjects and undertake specialist studies in heritage planning, community consultation, field techniques, analysis of human and animal bone, site identification and recording using digital technologies.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Aboriginal and historic archaeology&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Delve into Indigenous Australian and historic archaeology. Examine past practice and contemporary advances and findings.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cultural heritage management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn to navigate and guide others in the ethical and regulatory requirements of managing sites and objects of cultural importance.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Archaeological field methods&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Build the practical skills and knowledge you need to conduct archaeological fieldwork in Australia and overseas.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>107148B</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Professional Accounting</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-professional-accounting</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>26</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Designed as a direct pathway to further study in professional accounting, La Trobe's Graduate Certificate in Professional Accounting will teach you essential fundamentals in this in-demand field.&lt;/p&gt;&lt;p&gt;Enjoy the opportunity for quick upskilling in this six-month program, where you'll learn from leading academics and hear guest lectures from industry experts. Explore a mix of accounting, finance, economics and other business-related studies.&lt;/p&gt;&lt;p&gt;Once you've completed this course, you'll have the knowledge you need to study advanced accounting topics. You can use this as a pathway to our Master of Professional Accounting and Master of Extended Professional Accounting. You'll be eligible for credit (also known as advanced standing) for the subjects you've already completed, taking you one step closer to your next qualification.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Accounting principles and practices&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to record business transactions, prepare financial statements and assess performance. Develop your professional judgment through real-world business scenarios.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Economics &lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand fundamental principles of microeconomics and macroeconomics. Explore the roles of individuals and businesses in different market structures and the impact of regulatory and political environments on business.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Finance&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand financial concepts and their application in business. Explore how organisations are financed, how they make investment decisions and how they develop dividend policies.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Business law or data analytics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop general knowledge relating to businesses, such as their responsibilities and risks they face – or study how to apply data analytics methods and tools in a business context to support data-driven decision-making.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>107439B</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>Master of Business Information Systems</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-business-information-systems</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>104</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>87600</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Step into the future of work with the Master of Business Information Systems, where you'll gain the advanced skills and knowledge to shape how intelligent information systems are designed, developed, and deployed in future-ready workplaces. This forward-thinking program is intended for those who want to be at the intersection of modern business, emerging technologies, and innovation.&lt;/p&gt;&lt;p&gt;The Master of Business Information Systems is co-designed with leading industry experts, specifically focused on equipping you with the technical, analytical, and business skills required to excel in modern business environments. This course provides you with core knowledge in modern information systems, artificial intelligence, design thinking, data analytics, cloud platforms, cybersecurity, and digital strategy, enabling you to transform information systems into innovative, user-centred digital solutions.&lt;/p&gt;&lt;p&gt;The teaching team draws on their industry and research expertise in building modern information systems and AI solutions to deliver a future-focused learning experience. Throughout the course, you will work on real-world industry projects and collaborate with professionals on practical business challenges. You will also learn to manage IT projects, develop business intelligence solutions, and shape digital strategies that balance innovation, return on investment, and social responsibility.&lt;/p&gt;&lt;p&gt;When you graduate, you will be equipped to lead digital initiatives, design AI-enabled enterprise systems, and bring a strategic edge to roles in project management, business analytics, information management, systems design, and digital strategy, in industries where data and AI are redefining what's possible.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You will learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Modern Information Systems: professional knowledge and skills in enterprise information systems for addressing real-world business problems&lt;/li&gt;&lt;li&gt;Analytics and AI: Analytics and AI capabilities that drive business decisions and improve organisational productivity&lt;/li&gt;&lt;li&gt;Business Innovation: Innovations and applications of information systems and data-driven decision-making in diverse business settings&lt;/li&gt;&lt;li&gt;ICT Ethics and Cybersecurity: knowledge of local and international regulatory frameworks and guidelines for addressing enterprise ethics and cybersecurity challenges&lt;/li&gt;&lt;li&gt;Professional ICT Practice: power skills essential for collaboration and teamwork in modern workplaces, including communication, critical thinking, emotional intelligence, and adaptability.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Master of Nursing</t>
+          <t>107440J</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
+          <t xml:space="preserve">Master of Nursing </t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/master-of-nursing</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>104</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>40000</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Tailor your studies to your career aspirations with La Trobe's Master of Nursing.&lt;/p&gt;&lt;p&gt;Pursue clinical specialisations in relevant hospital settings with our prestigious health partners, or complete non-clinical specialisations to develop advanced knowledge of nursing research along with the critical thinking, problem-solving and communication skills you need to thrive as a nursing researcher, educator or leader.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;By completing La Trobe's Master of Nursing, you will:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;learn to effectively plan, implement and evaluate practice in your specialised context, make high-level independent judgements, and function effectively as a member of a multidisciplinary team&lt;/li&gt;&lt;li&gt;benefit from a flexible, blended learning approach that offers face-to-face or fully online study options that you can fit around your work commitments&lt;/li&gt;&lt;li&gt;choose from clinical specialisations in acute care, cardiac care, critical care, medical imaging, neonatal care, neonatal special care, and perioperative practices; or non-clinical specialisations in health management, leadership or public health&lt;/li&gt;&lt;li&gt;explore the introduction to nursing in the Australian context, including an understanding of professional standards and the healthcare organisational system&lt;/li&gt;&lt;li&gt;investigate legal and ethical issues pertinent to nursing practice.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>108004K</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
           <t>Graduate Diploma in Engineering Management</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-in-engineering-management</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>52</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>47200</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>47200</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're determined to create sustainable change in the world of engineering, La Trobe's Graduate Diploma in Engineering Management will give you the advanced skills and experience to take the next step in your career. Develop the commercial expertise to set yourself apart in this evolving industry.&lt;/p&gt;&lt;p&gt;Update your core knowledge in modern engineering practice and advance your career as a leader in a wide range of engineering disciplines. Delve into specialist subjects in management, innovation and sustainability – designed specifically for engineers – while you develop your understanding of core business principles in marketing, finance, organisational behaviour and business statistics.&lt;/p&gt;&lt;p&gt;In this interdisciplinary course, you'll learn from experienced engineers and business professionals at the top of their fields. All your teachers have extensive industry experience and up-to-date knowledge of best practice. &lt;/p&gt;&lt;p&gt;After successfully completing the Graduate Diploma in Engineering Management, you'll be eligible to apply for La Trobe's Master of Engineering Management. You'll gain up to one year of advanced standing for the Master's, so you could commence studying in second year. &lt;/p&gt;&lt;p&gt;Want to create a career in sustainable engineering? Graduate ready to become an engineering leader. &lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Advanced engineering management skills&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop specialist skills in innovation, environmental sustainability, computer-aided engineering, and risk and cost engineering.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Australian engineering environment and sustainability practices&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand the sustainability practices used in the Australian engineering industry. Gain the skills to take the next big step in your career.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Transferable skills in business and management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to lead and develop organisations, teams and individuals. Understand how to develop financial documents and take a strategic approach to management decisions.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>110457G</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>Bachelor of Visual Arts</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-visual-arts</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>156</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>114000</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>38000</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're creative and want to pursue your artistic passion, La Trobe's Bachelor of Visual Arts will give you the knowledge, experiences and connections to realise your dream career. Gain valuable skills in a range of visual mediums, then dive into your art practice with access to our purpose-built studios and workshops.&lt;/p&gt;&lt;p&gt;Develop your art practice in a professional environment. Access specialised facilities including painting and drawing studios, a digital lighting studio, photographic darkrooms, and sculpture and printmaking workshops. You'll also get your own personal studio space from day one of your degree – right through to graduation – where you can hone your skills and collaborate with other artists.&lt;/p&gt;&lt;p&gt;Gain insights into what contemporary art can tell us about the world and our place within it. Discover how the arts contribute to the significant historical, cultural, ecological and ethical issues of our time and gain a deeper understanding of the relationship between art and other visual cultures such as fashion, film and design.&lt;/p&gt;&lt;p&gt;Connect with like-minded people who are pursuing their creative passion. Join a vibrant, close and supportive creative community, with motivated students, supportive teachers and an engaged alumni network. You'll benefit from our close-knit campus, where you'll feel like part of a family.&lt;/p&gt;&lt;p&gt;Pursue your passion for visual arts while exploring other specialisations. You'll study core visual arts subjects and develop your practice, then explore your interests or build an essential skill when you choose from open access majors, minors and electives from across the university. You can graduate with your additional major on your academic transcript, so future employers can recognise your expertise.&lt;/p&gt;&lt;p&gt;Create your own path. Want to add an optional major in creative and professional writing, or in digital media? Go for it. Or perhaps you'd like to explore anthropology, history or crime, justice and legal studies? No matter what you choose to explore, you'll learn from world-class academics and leading researchers, including established artists and published art historians. &lt;/p&gt;&lt;p&gt;Live in regional Australia and pursue your passion. Study at one of Australia's biggest regional centres, which enjoys a thriving arts scene with an established creative community. You'll also have the opportunity to take the next step in your career and exhibit your work at La Trobe's Phyllis Palmer Gallery and at our student-run gallery, Rookie.&lt;/p&gt;&lt;p&gt;Get the industry experience that'll set you apart. Build your skills and experience through an industry placement at organisations like Bendigo Art Gallery and La Trobe Art Institute. Or get a global perspective when you travel overseas for an international sustainability experience or study abroad through our exchange program. You will also be able to build your professional network through the university's partnerships with major cultural institutions.&lt;/p&gt;&lt;p&gt;Looking to keep your options open? You can also choose to graduate with a &lt;a href="https://www.latrobe.edu.au/courses/diploma-of-arts"&gt;Diploma of Arts&lt;/a&gt; after one year of study.&lt;/p&gt;&lt;p&gt;Graduate ready to make your mark in the art world.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Creative practice&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop skills in a range of artistic mediums, including painting, drawing, ceramics, photography and printmaking.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Art theory and visual culture&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the major arts movements and individuals that have shaped the contemporary art world while learning how to critically analyse and interpret works.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Industry experience&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Uncover how to build your career as an artist. Learn how to plan and run an exhibition, write about your practice, promote your work, build your creative network and more. Get experience in the galleries, libraries, archives and museums (GLAM) sector and gain key skills for working in the arts.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Scraped from data API (be/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>110805C</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>Master of Dietetics</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-dietetics</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>78</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>83200</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>51200</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you're passionate about healthy eating and well-being, and want to promote better understanding of the benefits of nutrition in diverse communities and settings, La Trobe's Master of Dietetics has been established to reflect the emerging needs of this changing profession.&lt;/p&gt;&lt;p&gt;La Trobe has a long history of nutrition education, and our new contemporary Master of Dietetics both builds on that history and embraces newfound developments and changing ideologies. Our person-centred, socially conscious approach to nutrition science favours the teaching of flexible concepts over dogmatic facts, and aids you in establishing a strong professional approach and individual identity.&lt;/p&gt;&lt;p&gt;Applying your research skills in diverse practice settings, utilise La Trobe's long-term industry partnerships to gain on-the-ground experience in clinical and community spaces. Your experience will prepare you for work in priority sectors, with focus on diversity, community inclusion and counselling.&lt;/p&gt;&lt;p&gt;Our approach to dietetics values the importance of life-long learning, and teaches you how to incorporate novel technologies, cutting-edge science and emerging evidence into your developing practice. Graduate ready to succeed in your career, and ready to help people.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;With La Trobe's Master of Dietetics, you'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Care, counselling, medical nutrition&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn essential skills in nutrition assessment, diagnosis and counselling. Understanding medical nutrition therapy and patient support.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Individual case management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;During 50 days of placement, you'll apply your clinical knowledge, counselling skills and the nutrition care process to support the health of individuals and groups.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Food service&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Through placement and practical classes, you'll explore the food systems utilised in clinical settings, and support vulnerable and disadvantaged populations.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Entrepreneurship&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Get the skills to succeed as a professional dietitian. Learn how to set up your own business and explore professional ethics, leadership and management.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Future-focused topics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore future-ready issues (sustainability, indigenous health) and specialist areas of dietetic practice. Use emerging, priority areas (mental health, disability, aged care) as a conceptual framework to explore interdisciplinary practice. Work with carers and translators, learn community impact and advocacy.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Professional identity and diversity&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover the scope and diversity of dietetic roles, from professional practice and standards through to the impact of colonisation and hierarchical systems on healthcare.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>112624C</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>Global Master of Business Administration</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/global-master-of-business-administration</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>104</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>98400</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>49200</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Wherever you are in your career – and wherever you want to go next – La Trobe's Global Master of Business Administration (GMBA) can help you reach your goals.&lt;/p&gt;&lt;p&gt;Specifically designed for early-career and emerging professionals from diverse international backgrounds, you'll accelerate your professional development and broaden your career opportunities – both domestically and internationally – when you build global business acumen, get hands-on experience, and grow your professional network.&lt;/p&gt;&lt;p&gt;To help launch your career, you'll cultivate a deep understanding of best-practice management and strategic business knowledge. With globally orientated subjects, you'll focus on cross-cultural awareness, organisational effectiveness, sustainability, and emerging technologies in business such as artificial intelligence (AI). You'll further enhance your expertise with options to specialise in the business field you're interested in.&lt;/p&gt;&lt;p&gt;Learn in dynamic and collaborative workshops, enriched by exposure to industry-informed, real-world learning activities strategically designed to get you career-ready. Aligned to current – and future – industry demands, you'll gain invaluable understanding of contemporary and emerging businesses through interaction with academics, peers and industry experts, as well as hands-on, practical experience through an industry placement.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Global strategic thinking, global marketing and consumer behaviour&lt;/li&gt;&lt;li&gt;&lt;ul&gt;&lt;li&gt;Develop strategies that can be adapted to diverse cultural, economic, and political environments. Adapt marketing strategies to diverse cultural, demographic, and economic conditions.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;Financial management&lt;/li&gt;&lt;li&gt;&lt;ul&gt;&lt;li&gt;Acquire financial skills, including financial analysis, introductory accounting, and investment strategies.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;Supply chain and operations management&lt;/li&gt;&lt;li&gt;&lt;ul&gt;&lt;li&gt;Gain knowledge of global supply chain management, logistics, and operations in a global context.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;Ethics, sustainability, and corporate social responsibility (CSR)&lt;/li&gt;&lt;li&gt;&lt;ul&gt;&lt;li&gt;Understand the importance of ethical practices in a global business environment and analyse sustainable business practices and their implementation internationally.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;Leadership and organisational behaviour&lt;/li&gt;&lt;li&gt;&lt;ul&gt;&lt;li&gt;Understand organisational behaviour in a global context, including team dynamics, conflict resolution, and motivation strategies.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;Digital transformation, business analytics and technology&lt;/li&gt;&lt;li&gt;&lt;ul&gt;&lt;li&gt;Explore the role and impact of emerging technologies and automation in modern business management, and learn how to use data analytics, business intelligence and AI tools to inform decisions.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>113592J</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
           <t>Master of Strength and Conditioning</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-strength-and-conditioning</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>78</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>69900</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>113593H</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>Bachelor of Food and Nutrition</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
+      <c r="C125" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-food-and-nutrition</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>156</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>127200</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>9513</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>March, June, August, November</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Gain the skills to make a difference in people's lives through food and nutrition. La Trobe's Bachelor of Food and Nutrition will equip you with the skills and knowledge to work with people, communities and organisations to prevent many chronic diseases.&lt;/p&gt;&lt;p&gt;Designed by leading nutrition experts and in collaboration with industry, you'll get a practical hands-on experience while exploring a range of topics such as environmental sustainability of our food system, sustainable diets, food product development, culture and food, and nutrition and disease. You'll have the opportunity to study in modern science labs and commercial kitchens.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Food and Nutrition, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;build expertise in chemistry and nutrition science, analysis, physiology and biochemistry, epidemiology, and research and communication&lt;/li&gt;&lt;li&gt;have the flexibility to study online or on campus, or even choose an accelerated option to finish your degree in 2.5 years&lt;/li&gt;&lt;li&gt;prepare for your career at every stage of the degree, with the option to exit early via the Diploma or Associate Degree in Food and Nutrition&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership with the Nutrition Society of Australia, or pursue postgraduate studies through the Master of Dietetics or our Honours research program.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Note:&lt;em&gt; Completion of this course is subject to core participation requirements, essential requirements, and additional costs. Please see the &lt;a href="https://www.latrobe.edu.au/courses/bachelor-of-food-and-nutrition#/entry-requirements"&gt;Entry requirements &amp;amp; pathways&lt;/a&gt; and &lt;a href="https://www.latrobe.edu.au/courses/bachelor-of-food-and-nutrition#/fees"&gt;Fees &amp;amp; scholarships&lt;/a&gt; tabs for more information.&lt;/em&gt;&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;VCE: Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>113662M</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>Bachelor of Nursing/Bachelor of Psychological Science</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-nursing-bachelor-of-psychological-science</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>208</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>178400</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>44600</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Develop the clinical understanding to care for people across the lifespan while building expertise in human behaviour and psychological science with La Trobe's Bachelor of Nursing/Bachelor of Psychological Science. &lt;/p&gt;&lt;p&gt;In this double degree, you will combine nursing practice with psychological science to understand how health, behaviour, communication and wellbeing interact in real-world care. &lt;/p&gt;&lt;p&gt;You will learn through clinical simulation and 800 hours of supervised placement, with potential (but not guaranteed) settings including hospitals, community health services, aged care, rehabilitation and mental health. &lt;/p&gt;&lt;p&gt;By studying the Bachelor of Nursing/Bachelor of Psychological Science, you will learn how to: &lt;/p&gt;&lt;ul&gt;&lt;li&gt;apply nursing knowledge across acute care, chronic illness, rehabilitation, community health, emergency care, mental health and Indigenous health &lt;/li&gt;&lt;li&gt;analyse cognitive, developmental, social, abnormal, clinical and health psychology in healthcare and wellbeing contexts &lt;/li&gt;&lt;li&gt;evaluate evidence, health information and psychological assessment information to support person-centred care &lt;/li&gt;&lt;li&gt;interpret behavioural, psychosocial and cultural factors that shape health, communication and therapeutic engagement &lt;/li&gt;&lt;li&gt;develop clinical reasoning, teamwork, leadership and decision-making skills through simulation and supervised placement &lt;/li&gt;&lt;li&gt;communicate with patients, families and healthcare teams in complex clinical and community environments. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;Please note: &lt;/strong&gt;Clinical placements are allocated solely in accordance with the Bachelor of Nursing course structure and placement requirements, as there are no clinical placements associated with the Bachelor of Psychological Science. &lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;IELTS of 7.0 with no individual band score less than 7.0 (can be across 2 sittings in a 6-month period, but no score can be below 6.5 and overall score must be 7 in both sittings)&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>113897C</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Marketing</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-marketing</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>26</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Build marketing knowledge and skills needed to expand your career opportunities and become a marketing leader with La Trobe's Graduate Certificate in Marketing.&lt;/p&gt;&lt;p&gt;To thrive in today's digital and data-driven environment, marketers need more than creative instinct: they need strategic insight, technological fluency, and an understanding of the risks and opportunities shaping modern business. In six months, this short postgraduate course equips you with the foundational tools and emerging knowledge to navigate contemporary marketing practice with confidence.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Graduate Certificate in Marketing, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop a strong grounding in marketing management, including how to evaluate marketing strategies and make evidence-based decisions&lt;/li&gt;&lt;li&gt;gain insight into digital marketing tools, platforms and performance metrics to design and manage high-impact campaigns&lt;/li&gt;&lt;li&gt;explore the potential of artificial intelligence in transforming marketing practices and customer engagement&lt;/li&gt;&lt;li&gt;understand how cybersecurity and data governance shape trust, privacy, and brand integrity in digital marketplaces.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Successfully completing the Graduate Certificate in Marketing allows you to pursue further postgraduate study with credit, including our Master of Marketing.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>113898B</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>Master of Manufacturing Engineering</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-manufacturing-engineering</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>104</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>92000</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Get the right mix of engineering know-how and business acumen to drive innovation across industries with La Trobe's accredited Master of Manufacturing Engineering.&lt;/p&gt;&lt;p&gt;Designed and delivered in consultation with industry leaders, our Master's equips you to meet contemporary manufacturing challenges using revolutionary technologies like artificial intelligence, robotics and machine learning. You'll gain proficiency in system design, materials processing and sustainable engineering while enhancing your employability with enterprise skills in consultation, negotiation, risk and project management. You'll also have the opportunity to experience engineering practice first-hand and build valuable industry connections with the option of an 800-hour work-integrated learning (WIL) program.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Master of Manufacturing Engineering, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;gain an understanding of Australian engineering industry sustainability practices&lt;/li&gt;&lt;li&gt;build capabilities in aerospace, defence, industrial automation and robotics, automotive and precision engineering&lt;/li&gt;&lt;li&gt;master the design of automated production lines to improve quality and reduce costs&lt;/li&gt;&lt;li&gt;hone your skills in computer-aided engineering (CAE) software and tech to improve design, modelling, manufacturing, and control&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership of Engineers Australia.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>113899A</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
           <t>Master of Civil Engineering</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-civil-engineering</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>104</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>92000</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Get the skills and knowledge to meet the challenges of disruptive technologies that are reshaping industries and the engineering profession globally with La Trobe's accredited Master of Civil Engineering.&lt;/p&gt;&lt;p&gt;Designed and delivered in consultation with industry leaders, our Master's builds the capabilities and specialist expertise to meet society and industry demands to develop infrastructure faster, better and more sustainably. You'll learn to analyse real-world problems and design modern infrastructure, developing valuable skills transferable across industries. You'll also have the opportunity to experience engineering practice first hand and build valuable industry connections with the option of an 800-hour work-integrated learning (WIL) program.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Master of Civil Engineering, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;gain an understanding of Australian engineering industry sustainability practices&lt;/li&gt;&lt;li&gt;learn to analyse real-world problems and design modern infrastructure, developing valuable skills transferable across industries.&lt;/li&gt;&lt;li&gt;master the mechanics of the quality and nature of materials to guide appropriate selection&lt;/li&gt;&lt;li&gt;discover how to use soil improvement techniques to make infrastructure stronger and more reliable&lt;/li&gt;&lt;li&gt;develop capabilities in structural dynamics to ensure structures are safe and long-lasting&lt;/li&gt;&lt;li&gt;discover how water and waste technology can be used as sustainable engineering solutions&lt;/li&gt;&lt;li&gt;graduate ready to apply for membership of Engineers Australia.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>114007A</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>Master of Counselling, Rehabilitation and Mental Health</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-counselling-rehabilitation-and-mental-health</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>104</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>86000</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>33000</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;If you'd like to build a career that makes a meaningful difference, La Trobe's accredited Master of Counselling, Rehabilitation and Mental Health will give you the foundations for a rewarding career that supports others through huge life changes.&lt;/p&gt;&lt;p&gt;Develop your professional knowledge, skills and expertise with this unique combination of rehabilitation counselling and mental health subjects.&lt;/p&gt;&lt;p&gt;You'll get hands-on experience and will graduate prepared to work in rehabilitation counselling, as well as broader counselling settings such as mental health and Employee Assistance Program (EAP) counselling.&lt;/p&gt;&lt;p&gt;Explore a diverse range of workplaces and cultures. You'll learn how to support individuals and communities through disability, disadvantage and injury – helping them to reach their full potential and reintegrate into work and the community.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Professional counselling practice&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Acquire skills that are essential for effective counselling practice through examining professional, ethical and legal issues that affect counselling practice in Australia.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Mental health counselling&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand the different types of mental health conditions and how they're diagnosed. Learn how to effectively treat clinical and sub-clinical mental health conditions.&lt;br/&gt;&lt;br/&gt;&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Rehabilitation counselling&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Understand the interpersonal helping process, especially as it applies to rehabilitation and behaviour change. Explore different counselling models and techniques (e.g. Motivational Interviewing).&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Employee Assistance Program counselling&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Develop specialised skills to work effectively and ethically as a counsellor in workplace settings.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;strong&gt;*Please be aware that this course includes mandatory in-person placement requirements. Students are expected to complete these placements in Australia.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>116675D</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>Bachelor of Commerce/Bachelor of Biomedicine</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
+      <c r="C131" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-commerce-bachelor-of-biomedicine</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>234</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>202500</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Learn how to navigate rapidly evolving environments in biotechnology, health, commercial practice and public policy with La Trobe's Bachelor of Commerce/Bachelor of Biomedicine.&lt;/p&gt;&lt;p&gt;Co-designed with industry leaders, our double degree gives you a multidisciplinary set of skills and knowledge sought-after by employers and policymakers. You'll learn to take advantage of the synergies between the two disciplines and how to solve complex problems by merging technical know-how and strategic analysis with an in-depth knowledge of innovations in the medical field.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Bachelor of Commerce/Bachelor of Biomedicine, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;learn how to identify practical solutions to real-world challenges, improve your ability to negotiate with stakeholders and communicate your solutions&lt;/li&gt;&lt;li&gt;develop critical skills in independent research, innovative thinking, cultural intelligence, oral and written communication, and teamwork&lt;/li&gt;&lt;li&gt;prepare to become an effective leader who can meet the challenges of automation, AI-driven technologies and big data&lt;/li&gt;&lt;li&gt;build fundamental knowledge in chemistry, bioscience and health before delving into infectious diseases, epidemics and pandemics&lt;/li&gt;&lt;li&gt;gain real-world experience through industry placements, work-integrated learning projects and overseas student exchange opportunities.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>116914E</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>Bachelor of Laws (Honours)/Bachelor of Biomedicine</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-laws-honours-bachelor-of-biomedicine</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>286</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>239800</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Get the skills, knowledge and industry you need to launch a legal career in the world of scientific advancement with La Trobe's Bachelor of Laws (Honours)/Bachelor of Biomedicine.&lt;/p&gt;&lt;p&gt;In this double degree, you'll develop a solid legal grounding in the fundamentals of legal practice, and hone your skillset in advocacy, negotiation and dispute resolution through intellectual and skills-based training. At the same time, you'll explore how the body works as you build essential knowledge in chemistry, bioscience and health.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Bachelor of Laws (Honours)/Bachelor of Biomedicine, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;explore legal topics such as dispute resolution, evidence and criminal procedure, contract law and company law, and public law&lt;/li&gt;&lt;li&gt;develop foundational knowledge in biochemistry, molecular and cell biology, human physiology, infectious and non-communicable disease&lt;/li&gt;&lt;li&gt;choose a biomedicine major in cancer, heart and brain diseases; immunology and infectious disease; physiology and pharmacology; or molecular and cellular biochemistry&lt;/li&gt;&lt;li&gt;get hands-on experience through legal placements in community legal centres, law firms, government agencies and more, and build relationships with judges, magistrates and coroners&lt;/li&gt;&lt;li&gt;gain practical biomedical experience with lab work, field work, internship opportunities and overseas exchange opportunities.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 – Bachelor Degree Honours.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 30 in English (EAL) or at least 25 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Graduate Diploma in Cybersecurity</t>
+          <t>116915D</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
+          <t xml:space="preserve">Graduate Diploma in Cybersecurity </t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-in-cybersecurity</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>52</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>43800</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>May, March, July, September</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;The Graduate Diploma in Cybersecurity allows you to study from anywhere and have the flexibility to accommodate your work and life commitments.&lt;/p&gt;&lt;p&gt;Some of the specialised subjects chosen for this course include €˜Inside the Mind of a Hacker', where you'll learn the psychology behind cybercrime so you can prepare defensively, €˜Programming Skills', where you'll learn to program securely for the future, and €˜Database Skills' where you'll learn future cyber analytics.&lt;/p&gt;&lt;p&gt;You may be eligible to continue into the Master of Cybersecurity upon completion of this Graduate Diploma. The Master of Cybersecurity provides industry-based learning, so you'll get the skills employers need.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Cybersecurity fundamentals&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the aims, methods, and outcomes of cybersecurity practice.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cyber risk management&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Cyber risk management based on business strategy and risk appetite.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;The mindset and motivation of hackers&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Cybersecurity is about people as much as &lt;strong&gt;t&lt;/strong&gt;echnology. Understanding what drives cybercriminals helps you create strategies to defend against them.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Cyber analytics&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Analyse and design cybersecurity algorithms using a visual modelling language such as Python.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Offshore applicants are considered for admission based on the stated course entry requirements.&lt;/li&gt;&lt;li&gt;IELTS may be considered.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>117009H</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>Master of Nursing Practice</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-nursing-practice</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>104</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Gain the clinical skills and experience you need to become a registered nurse (RN) in just two years with La Trobe's Master of Nursing Practice.&lt;/p&gt;&lt;p&gt;In this degree, you'll build on your existing Bachelor's degree qualification – in any discipline – and develop the clinical knowledge and skills you'll need to upskill or change careers in the health sector. You'll learn the theory from leading clinicians and academics at the La Trobe Rural Health School and then apply it in the real world with clinical placements (800 hours) in leading regional and rural hospitals and healthcare providers.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Master of Nursing Practice, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;develop foundational knowledge in primary care, acute care, chronic illness, Indigenous health, mental health, rehabilitation, community and emergency care, biosciences and research&lt;/li&gt;&lt;li&gt;gain in-demand skills in leadership, time management, critical thinking and communication&lt;/li&gt;&lt;li&gt;apply what you've learned in our state-of-the-art nursing simulation labs&lt;/li&gt;&lt;li&gt;study closer to home at our Albury-Wodonga, Bendigo and Mildura Campuses&lt;/li&gt;&lt;li&gt;graduate ready to support and strengthen your local community as a registered nurse (RN).&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>English Language Requirements&lt;p&gt;7.0 IELTS (Academic) with no individual band less than 7.0.&lt;/p&gt;&lt;br/&gt;&lt;p&gt;IELTS, TOEFL and PTE are the only English Proficiency tests accepted for entry into this course.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Please note:&lt;br/&gt;&lt;/strong&gt;&lt;a href="http://pearsonpte.com/"&gt;&lt;strong&gt;Pearson Test of English &lt;/strong&gt;&lt;/a&gt;(PTE) Academic. &lt;br/&gt;Applicants must achieve a minimum overall score of 65 and a minimum score of 65 in each of the four communicative skills (listening, reading, writing and speaking).&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;em&gt;NOTE:&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;We will only accept test results:&lt;/strong&gt;&lt;/p&gt;&lt;ol&gt;&lt;li&gt;&lt;em&gt;from one test sitting, or&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;a maximum of two test sittings in a six month period only if:&lt;/em&gt;&lt;/li&gt;&lt;/ol&gt;&lt;ul&gt;&lt;li&gt;&lt;em&gt;a minimum overall score of 65 is achieved in each sitting, and&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;you achieve a minimum score of 65 in each of the communicative skills across the two sittings, and&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;no score in any of the communicative skills is below 58&lt;/em&gt;&lt;/li&gt;&lt;/ul&gt;</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>117010D</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>Master of Construction Engineering and Management</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-construction-engineering-and-management</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>104</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>92000</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>46000</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>March, July, November</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Gain advanced skills and knowledge to capitalise on the unprecedented growth in Australia's construction sector with La Trobe's Master of Construction Engineering and Management.&lt;/p&gt;&lt;p&gt;You'll be equipped to manage complex projects while addressing social, environmental, and occupational health and safety challenges in Australia's first master's degree accredited by Engineers Australia in the construction engineering area.&lt;/p&gt;&lt;p&gt;You'll also have the opportunity to experience engineering practice first-hand with 800 hours of work-integrated learning, then put theory into practice with research-based learning or an industry-based capstone research project.&lt;/p&gt;&lt;p&gt;By completing La Trobe's Master of Construction Engineering and Management, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Utilise modern digital tools and technologies such as Building Information Modelling (BIM), digital twins, and extended reality to enhance design efficiency, visualisation, collaboration, cost control, scheduling, and overall project management.&lt;/li&gt;&lt;li&gt;Apply the latest construction engineering techniques to effectively deliver building and infrastructure projects.&lt;/li&gt;&lt;li&gt;Develop technical expertise in project planning and execution, construction systems (including quality, safety, and environmental management systems), modern procurement methods (including procurement models, contract, tenders and bids, and supply chain management), cost estimating and control, risk management, and sustainable construction practices.&lt;/li&gt;&lt;li&gt;Master key business concepts including business models, competitive strategies, engineering innovation and management, professionalism and leadership, entrepreneurship, and financial analysis.&lt;/li&gt;&lt;li&gt;Access opportunities to support your studies with a $12,000 placement grant or La Trobe's range of scholarships.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2026/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>117169C</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>Bachelor of Sport and Recreation Management</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/bachelor-of-sport-and-recreation-management</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>156</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>130800</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>43600</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>March</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Learn how to manage community sport and recreation services with La Trobe's Bachelor of Sport and Recreation Management. &lt;/p&gt;&lt;p&gt;In this degree, you will explore topics such as program design, sport coaching, human resource management, marketing, delivery and evaluation, government policy and funding, facility and venue management, sport law, professional communication and more. &lt;/p&gt;&lt;p&gt;Build the skills to engage with communities, work with volunteers and support physical activity, community development and wellbeing. You'll apply your learning in the real world through placement opportunities with organisations such as local councils, sport associations, community groups and clubs. &lt;/p&gt;&lt;p&gt;If your goals or circumstances change, you may have the flexibility to complete an earlier qualification after one year with the Diploma of Sport and Recreation Management, or after two years with the Associate Degree of Sport and Recreation Management. &lt;/p&gt;&lt;p&gt;By studying the Bachelor of Sport and Recreation Management, you will learn how to: &lt;/p&gt;&lt;ul&gt;&lt;li&gt;design, deliver and evaluate community sport and recreation programs &lt;/li&gt;&lt;li&gt;assess community needs and plan services that support participation and wellbeing &lt;/li&gt;&lt;li&gt;interpret policy, funding, safety and legal requirements in sport and recreation &lt;/li&gt;&lt;li&gt;apply marketing and branding principles to sport and recreation programs &lt;/li&gt;&lt;li&gt;manage facility and venue operations for sport and recreation settings &lt;/li&gt;&lt;li&gt;engage with community groups, clubs, volunteers and local sport organisations. &lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 7 - Bachelor Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;Academic Requirements&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;Units 3 and 4: a study score of at least 25 in English (EAL) or at least 20 in English other than EAL.&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.0 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>117350F</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>Master of Professional Engineering</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/master-of-professional-engineering</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>52</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>47000</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>47000</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Build on your existing Bachelor's degree while gaining the technical expertise, critical-thinking ability and management skills to thrive in a competitive global workforce with La Trobe's Master of Professional Engineering.&lt;/p&gt;&lt;p&gt;Co-designed with our prestigious industry partners, our unique and versatile Master's offers a one-year fast track to an Australian engineering career by blending traditional and online learning with hands-on industry experience at leading engineering companies, including Siemens, John Holland and Acciona.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Master of Professional Engineering, you will:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;combine theoretical knowledge of sustainable engineering practice in Australia with transferable skills in project management and leadership&lt;/li&gt;&lt;li&gt;master the economics of engineering, including business strategy and development, management tools and resources, commercial and industrial relations law, and financing and marketing&lt;/li&gt;&lt;li&gt;discover how engineering research is planned, executed ethically and sustainably, and reported&lt;/li&gt;&lt;li&gt;develop skills in ethical and moral decision-making and evaluate its social implications&lt;/li&gt;&lt;li&gt;experience engineering practice first-hand and build valuable industry connections via an 800-hour industry-based learning placement&lt;/li&gt;&lt;li&gt;graduate with a range of pathways into further study or diverse career opportunities across multiple sectors and industries.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 9 - Masters Degree.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>119013G</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>Graduate Certificate in Public Health</t>
         </is>
       </c>
-      <c r="B138" t="inlineStr">
+      <c r="C138" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-public-health</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>26</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>22100</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>May, March, July, September, November</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;&lt;strong&gt;Make a difference. Start a career in public health.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;As we've all seen, public health professionals are in high demand around the world. They provide health education and information. Prevent the outbreak of diseases. Protect and improve community health.&lt;/p&gt;&lt;p&gt;La Trobe's Graduate Certificate of Public Health gives you vital skills and up-to-date insights into public health. After you graduate, build on your expertise with further study and expand your career pathways to include health roles in government organisations and community health services.&lt;/p&gt;&lt;p&gt;Graduate with an internationally-recognised qualification enabling you to work anywhere in the world.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;You'll learn:&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Public health practice&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the theoretical principles and foundational skills for public health practice.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Approaches to public health problems&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Critique and explain complex local and global public health problems using different knowledge models.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Public health initiatives&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Discover how to conceive, create and evaluate achievable public health initiatives.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Social and cultural perspectives&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Learn how to engage and communicate effectively with individuals, communities, agencies, the private sector and government decision makers.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;&lt;ul&gt;&lt;li&gt;Offshore applicants are considered for admission based on the stated course entry requirements.&lt;/li&gt;&lt;li&gt;IELTS may be considered.&lt;/li&gt;&lt;/ul&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>register</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>CRICOS + fees from register fallback | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>119321F</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>Graduate Diploma in Early Childhood Education</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr">
+      <c r="C139" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-diploma-in-early-childhood-education</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>52</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>36800</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>36800</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>July</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Learn from highly experienced teachers with an industry-connected curriculum designed in consultation with industry partners and delivered by La Trobe's award-winning School of Education*. You'll gain the skills and knowledge to support the next generation of pre-school children develop foundational skills across social, emotional, physical and academic areas.&lt;/p&gt;&lt;p&gt;Explore key areas of early childhood education through core subjects exploring early childhood development, assessment and reporting, teaching strategies, and safety and ethics as you put your knowledge to work in the real world with work-based learning, integrated placement and an embedded professional mentoring program.&lt;/p&gt;&lt;p&gt;You'll graduate ready to start your career in early childhood education environments or advance directly into La Trobe's Master of Education, further preparing you for leadership or specialist positions within the sector.&lt;/p&gt;&lt;p&gt;By studying La Trobe's Graduate Diploma in Early Childhood Education, you'll learn:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;strong&gt;Foundations of child development &lt;/strong&gt;&lt;br/&gt;&lt;ul&gt;&lt;li&gt;Investigate the social, emotional and educational needs of children and gain a core understanding of child development and evidence-based pedagogies to develop teaching strategies.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Early childhood leadership&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Explore the complexities of early childhood leadership, such as policy, legal requirements, political influences, professional ethics and operational management.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Theories of cognition and play&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Examine the role of fundamental role of play and play-based learning in the development of skills in science, creativity, literacy development and mathematical thinking.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Assessment and reporting&lt;/strong&gt;&lt;ul&gt;&lt;li&gt;Investigate the authentic use of assessment in early childhood education, including examining the way that assessment is used to inform understanding.&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;* &lt;em&gt;Australian Financial Review (AFR), 2022, AFR Higher Education Awards show universities at their creative best&lt;/em&gt;&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Diploma.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.5.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>119325B</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>Graduate Certificate in International Business</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr">
+      <c r="C140" t="inlineStr">
         <is>
           <t>https://www.latrobe.edu.au/courses/graduate-certificate-in-international-business</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>26</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>23600</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>March, July</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;With the ongoing expansion and transformation of international markets, there is a rising demand for professionals who can navigate complex business environments across borders. If you are looking to accelerate your career in international business, La Trobe's Graduate Certificate in International Business is designed to give you a competitive advantage.&lt;/p&gt;&lt;p&gt;Throughout the duration of this course, you will develop effective communication skills for cross-cultural settings and formulate strategies to lead diverse teams and organisations across various international business contexts. Alongside core business competencies, you will examine how emerging technologies are shaping the international landscape. The course provides key insights into artificial intelligence (AI) and cybersecurity, helping you understand the opportunities and challenges presented by digital transformation.&lt;/p&gt;&lt;p&gt;You will also benefit from opportunities to engage with industry professionals and gain practical perspectives from experienced experts. By the end of the course, you will be equipped with a solid understanding of international business, digital consciousness and cross-cultural leadership, positioning you to lead competently in today's interconnected business environment.&lt;/p&gt;&lt;p&gt;Upon successful completion of the course, you will be awarded the Graduate Certificate in International Business. If you wish to pursue further postgraduate study, you can continue your education with credit by joining our Master of International Business.&lt;/p&gt;&lt;p&gt;The qualification awarded on graduation is recognised in the Australian Qualifications Framework (AQF) as Level 8 - Graduate Certificate.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>&lt;table&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;strong&gt;English Proficiency&lt;/strong&gt;&lt;/td&gt;&lt;td&gt;6.5 IELTS (Academic) with no individual band less than 6.0.&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Scraped from data API (bu/2027/international) | fees &amp; duration updated from CRICOS register</t>
         </is>
       </c>
     </row>
